--- a/research/traditional_assets/database/data/jamaica/jamaica_education.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_education.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.2346938775510204</v>
+        <v>-0.1762237762237762</v>
       </c>
       <c r="H2">
-        <v>-0.2346938775510204</v>
+        <v>-0.1762237762237762</v>
       </c>
       <c r="I2">
-        <v>-0.1564625850340136</v>
+        <v>-0.05734265734265735</v>
       </c>
       <c r="J2">
-        <v>-0.1564625850340136</v>
+        <v>-0.05734265734265735</v>
       </c>
       <c r="K2">
-        <v>-0.157</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="L2">
-        <v>-0.5340136054421769</v>
+        <v>-0.1174825174825175</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>-0.007</v>
+        <v>0.037</v>
       </c>
       <c r="V2">
-        <v>-0.006481481481481481</v>
+        <v>0.01697247706422018</v>
       </c>
       <c r="W2">
-        <v>26.16666666666667</v>
+        <v>0.5316455696202532</v>
       </c>
       <c r="X2">
-        <v>0.1100035060207046</v>
+        <v>0.1949334445017888</v>
       </c>
       <c r="Y2">
-        <v>26.05666316064596</v>
+        <v>0.3367121251184644</v>
       </c>
       <c r="Z2">
-        <v>-18.375</v>
+        <v>5.218978102189782</v>
       </c>
       <c r="AA2">
-        <v>2.875</v>
+        <v>-0.2992700729927008</v>
       </c>
       <c r="AB2">
-        <v>0.1095088983842122</v>
+        <v>0.1679919496413862</v>
       </c>
       <c r="AC2">
-        <v>2.765491101615788</v>
+        <v>-0.4672620226340869</v>
       </c>
       <c r="AD2">
-        <v>0.01</v>
+        <v>0.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.01</v>
+        <v>0.8</v>
       </c>
       <c r="AG2">
-        <v>0.017</v>
+        <v>0.763</v>
       </c>
       <c r="AH2">
-        <v>0.009174311926605503</v>
+        <v>0.2684563758389262</v>
       </c>
       <c r="AI2">
-        <v>-0.06756756756756757</v>
+        <v>0.7858546168958743</v>
       </c>
       <c r="AJ2">
-        <v>0.0154968094804011</v>
+        <v>0.2592592592592592</v>
       </c>
       <c r="AK2">
-        <v>-0.1205673758865248</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="AL2">
-        <v>0.059</v>
+        <v>0.035</v>
       </c>
       <c r="AM2">
-        <v>0.059</v>
+        <v>0.035</v>
       </c>
       <c r="AN2">
-        <v>-0.8333333333333334</v>
+        <v>-30.76923076923077</v>
       </c>
       <c r="AO2">
-        <v>-0.7796610169491526</v>
+        <v>-1.171428571428571</v>
       </c>
       <c r="AP2">
-        <v>-1.416666666666667</v>
+        <v>-29.34615384615385</v>
       </c>
       <c r="AQ2">
-        <v>-0.7796610169491526</v>
+        <v>-1.171428571428571</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.2346938775510204</v>
+        <v>-0.1762237762237762</v>
       </c>
       <c r="H3">
-        <v>-0.2346938775510204</v>
+        <v>-0.1762237762237762</v>
       </c>
       <c r="I3">
-        <v>-0.1564625850340136</v>
+        <v>-0.05734265734265735</v>
       </c>
       <c r="J3">
-        <v>-0.1564625850340136</v>
+        <v>-0.05734265734265735</v>
       </c>
       <c r="K3">
-        <v>-0.157</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="L3">
-        <v>-0.5340136054421769</v>
+        <v>-0.1174825174825175</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>-0.007</v>
+        <v>0.037</v>
       </c>
       <c r="V3">
-        <v>-0.006481481481481481</v>
+        <v>0.01697247706422018</v>
       </c>
       <c r="W3">
-        <v>26.16666666666667</v>
+        <v>0.5316455696202532</v>
       </c>
       <c r="X3">
-        <v>0.1100035060207046</v>
+        <v>0.1949334445017888</v>
       </c>
       <c r="Y3">
-        <v>26.05666316064596</v>
+        <v>0.3367121251184644</v>
       </c>
       <c r="Z3">
-        <v>-18.375</v>
+        <v>5.218978102189782</v>
       </c>
       <c r="AA3">
-        <v>2.875</v>
+        <v>-0.2992700729927008</v>
       </c>
       <c r="AB3">
-        <v>0.1095088983842122</v>
+        <v>0.1679919496413862</v>
       </c>
       <c r="AC3">
-        <v>2.765491101615788</v>
+        <v>-0.4672620226340869</v>
       </c>
       <c r="AD3">
-        <v>0.01</v>
+        <v>0.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.01</v>
+        <v>0.8</v>
       </c>
       <c r="AG3">
-        <v>0.017</v>
+        <v>0.763</v>
       </c>
       <c r="AH3">
-        <v>0.009174311926605503</v>
+        <v>0.2684563758389262</v>
       </c>
       <c r="AI3">
-        <v>-0.06756756756756757</v>
+        <v>0.7858546168958743</v>
       </c>
       <c r="AJ3">
-        <v>0.0154968094804011</v>
+        <v>0.2592592592592592</v>
       </c>
       <c r="AK3">
-        <v>-0.1205673758865248</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="AL3">
-        <v>0.059</v>
+        <v>0.035</v>
       </c>
       <c r="AM3">
-        <v>0.059</v>
+        <v>0.035</v>
       </c>
       <c r="AN3">
-        <v>-0.8333333333333334</v>
+        <v>-30.76923076923077</v>
       </c>
       <c r="AO3">
-        <v>-0.7796610169491526</v>
+        <v>-1.171428571428571</v>
       </c>
       <c r="AP3">
-        <v>-1.416666666666667</v>
+        <v>-29.34615384615385</v>
       </c>
       <c r="AQ3">
-        <v>-0.7796610169491526</v>
+        <v>-1.171428571428571</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jamaica/jamaica_education.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_education.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="jmse_one" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,31 +590,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.1762237762237762</v>
+        <v>-0.2199270959902795</v>
       </c>
       <c r="H2">
-        <v>-0.1762237762237762</v>
+        <v>-0.2199270959902795</v>
       </c>
       <c r="I2">
-        <v>-0.05734265734265735</v>
+        <v>-0.2206561360874848</v>
       </c>
       <c r="J2">
-        <v>-0.05734265734265735</v>
+        <v>-0.2206561360874848</v>
       </c>
       <c r="K2">
-        <v>-0.08400000000000001</v>
+        <v>-2.002</v>
       </c>
       <c r="L2">
-        <v>-0.1174825174825175</v>
+        <v>-0.486512758201701</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.117</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.005622296972609324</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.05844155844155845</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,76 +626,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.117</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>0.037</v>
+        <v>0.802</v>
       </c>
       <c r="V2">
-        <v>0.01697247706422018</v>
+        <v>0.03853916386352715</v>
       </c>
       <c r="W2">
-        <v>0.5316455696202532</v>
+        <v>-0.4964601769911505</v>
       </c>
       <c r="X2">
-        <v>0.1949334445017888</v>
+        <v>0.1380030519791756</v>
       </c>
       <c r="Y2">
-        <v>0.3367121251184644</v>
+        <v>-0.634463228970326</v>
       </c>
       <c r="Z2">
-        <v>5.218978102189782</v>
+        <v>0.8562213899292551</v>
       </c>
       <c r="AA2">
-        <v>-0.2992700729927008</v>
+        <v>-0.1599808978032474</v>
       </c>
       <c r="AB2">
-        <v>0.1679919496413862</v>
+        <v>0.1261812675351765</v>
       </c>
       <c r="AC2">
-        <v>-0.4672620226340869</v>
+        <v>-0.2861621653384239</v>
       </c>
       <c r="AD2">
-        <v>0.8</v>
+        <v>2.572</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.8</v>
+        <v>2.572</v>
       </c>
       <c r="AG2">
-        <v>0.763</v>
+        <v>1.77</v>
       </c>
       <c r="AH2">
-        <v>0.2684563758389262</v>
+        <v>0.109999144641177</v>
       </c>
       <c r="AI2">
-        <v>0.7858546168958743</v>
+        <v>0.3150802401078035</v>
       </c>
       <c r="AJ2">
-        <v>0.2592592592592592</v>
+        <v>0.07838795394154119</v>
       </c>
       <c r="AK2">
-        <v>0.7777777777777778</v>
+        <v>0.2404564597201467</v>
       </c>
       <c r="AL2">
-        <v>0.035</v>
+        <v>0.366</v>
       </c>
       <c r="AM2">
-        <v>0.035</v>
+        <v>0.362</v>
       </c>
       <c r="AN2">
-        <v>-30.76923076923077</v>
+        <v>-3.268106734434562</v>
       </c>
       <c r="AO2">
-        <v>-1.171428571428571</v>
+        <v>-2.480874316939891</v>
       </c>
       <c r="AP2">
-        <v>-29.34615384615385</v>
+        <v>-2.249047013977128</v>
       </c>
       <c r="AQ2">
-        <v>-1.171428571428571</v>
+        <v>-2.50828729281768</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +709,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iCreate Limited (JMSE:ICREATE)</t>
+          <t>One on One Educational Services Limited (JMSE:ONE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,22 +718,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.1762237762237762</v>
+        <v>0.1132275132275132</v>
       </c>
       <c r="H3">
-        <v>-0.1762237762237762</v>
+        <v>0.1132275132275132</v>
       </c>
       <c r="I3">
-        <v>-0.05734265734265735</v>
+        <v>0.004232804232804233</v>
       </c>
       <c r="J3">
-        <v>-0.05734265734265735</v>
+        <v>0.004232804232804233</v>
       </c>
       <c r="K3">
-        <v>-0.08400000000000001</v>
+        <v>-0.041</v>
       </c>
       <c r="L3">
-        <v>-0.1174825174825175</v>
+        <v>-0.02169312169312169</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +757,9098 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.037</v>
+        <v>0.618</v>
       </c>
       <c r="V3">
-        <v>0.01697247706422018</v>
+        <v>0.04611940298507462</v>
       </c>
       <c r="W3">
-        <v>0.5316455696202532</v>
+        <v>-0.04475982532751092</v>
       </c>
       <c r="X3">
-        <v>0.1949334445017888</v>
+        <v>0.1240514464366324</v>
       </c>
       <c r="Y3">
-        <v>0.3367121251184644</v>
+        <v>-0.1688112717641434</v>
       </c>
       <c r="Z3">
-        <v>5.218978102189782</v>
+        <v>1.091854419410745</v>
       </c>
       <c r="AA3">
-        <v>-0.2992700729927008</v>
+        <v>0.004621606008087809</v>
       </c>
       <c r="AB3">
-        <v>0.1679919496413862</v>
+        <v>0.1231481081914284</v>
       </c>
       <c r="AC3">
-        <v>-0.4672620226340869</v>
+        <v>-0.1185265021833406</v>
       </c>
       <c r="AD3">
+        <v>0.251</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0.251</v>
+      </c>
+      <c r="AG3">
+        <v>-0.367</v>
+      </c>
+      <c r="AH3">
+        <v>0.0183869313603399</v>
+      </c>
+      <c r="AI3">
+        <v>0.07792610990375659</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.02815928796132893</v>
+      </c>
+      <c r="AK3">
+        <v>-0.1409911640414906</v>
+      </c>
+      <c r="AL3">
+        <v>0.042</v>
+      </c>
+      <c r="AM3">
+        <v>0.042</v>
+      </c>
+      <c r="AN3">
+        <v>14.76470588235294</v>
+      </c>
+      <c r="AO3">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="AP3">
+        <v>-21.58823529411764</v>
+      </c>
+      <c r="AQ3">
+        <v>0.1904761904761905</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EduFocal Limited (JMSE:LEARN)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>-0.4659459459459459</v>
+      </c>
+      <c r="H4">
+        <v>-0.4659459459459459</v>
+      </c>
+      <c r="I4">
+        <v>-0.1810810810810811</v>
+      </c>
+      <c r="J4">
+        <v>-0.1810810810810811</v>
+      </c>
+      <c r="K4">
+        <v>-0.5610000000000001</v>
+      </c>
+      <c r="L4">
+        <v>-0.3032432432432433</v>
+      </c>
+      <c r="M4">
+        <v>0.117</v>
+      </c>
+      <c r="N4">
+        <v>0.01733333333333334</v>
+      </c>
+      <c r="O4">
+        <v>-0.2085561497326203</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0.117</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>0.122</v>
+      </c>
+      <c r="V4">
+        <v>0.01807407407407407</v>
+      </c>
+      <c r="W4">
+        <v>-0.4964601769911505</v>
+      </c>
+      <c r="X4">
+        <v>0.1380030519791756</v>
+      </c>
+      <c r="Y4">
+        <v>-0.634463228970326</v>
+      </c>
+      <c r="Z4">
+        <v>0.8834765998089781</v>
+      </c>
+      <c r="AA4">
+        <v>-0.1599808978032474</v>
+      </c>
+      <c r="AB4">
+        <v>0.1261812675351765</v>
+      </c>
+      <c r="AC4">
+        <v>-0.2861621653384239</v>
+      </c>
+      <c r="AD4">
+        <v>1.62</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>1.62</v>
+      </c>
+      <c r="AG4">
+        <v>1.498</v>
+      </c>
+      <c r="AH4">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="AI4">
+        <v>0.7531380753138075</v>
+      </c>
+      <c r="AJ4">
+        <v>0.181619786614937</v>
+      </c>
+      <c r="AK4">
+        <v>0.7382947264662395</v>
+      </c>
+      <c r="AL4">
+        <v>0.169</v>
+      </c>
+      <c r="AM4">
+        <v>0.165</v>
+      </c>
+      <c r="AN4">
+        <v>-6.159695817490494</v>
+      </c>
+      <c r="AO4">
+        <v>-1.982248520710059</v>
+      </c>
+      <c r="AP4">
+        <v>-5.695817490494298</v>
+      </c>
+      <c r="AQ4">
+        <v>-2.03030303030303</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>iCreate Limited (JMSE:ICREATE)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>-0.6853333333333333</v>
+      </c>
+      <c r="H5">
+        <v>-0.6853333333333333</v>
+      </c>
+      <c r="I5">
+        <v>-1.549333333333333</v>
+      </c>
+      <c r="J5">
+        <v>-1.549333333333333</v>
+      </c>
+      <c r="K5">
+        <v>-1.4</v>
+      </c>
+      <c r="L5">
+        <v>-3.733333333333333</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.062</v>
+      </c>
+      <c r="V5">
+        <v>0.09393939393939393</v>
+      </c>
+      <c r="W5">
+        <v>-6.422018348623853</v>
+      </c>
+      <c r="X5">
+        <v>0.189840085881237</v>
+      </c>
+      <c r="Y5">
+        <v>-6.61185843450509</v>
+      </c>
+      <c r="Z5">
+        <v>0.382262996941896</v>
+      </c>
+      <c r="AA5">
+        <v>-0.5922528032619775</v>
+      </c>
+      <c r="AB5">
+        <v>0.131681163233109</v>
+      </c>
+      <c r="AC5">
+        <v>-0.7239339664950866</v>
+      </c>
+      <c r="AD5">
+        <v>0.701</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0.701</v>
+      </c>
+      <c r="AG5">
+        <v>0.639</v>
+      </c>
+      <c r="AH5">
+        <v>0.5150624540778839</v>
+      </c>
+      <c r="AI5">
+        <v>0.2511644571838051</v>
+      </c>
+      <c r="AJ5">
+        <v>0.4919168591224019</v>
+      </c>
+      <c r="AK5">
+        <v>0.2341517039208501</v>
+      </c>
+      <c r="AL5">
+        <v>0.155</v>
+      </c>
+      <c r="AM5">
+        <v>0.155</v>
+      </c>
+      <c r="AN5">
+        <v>-1.295748613678373</v>
+      </c>
+      <c r="AO5">
+        <v>-3.748387096774193</v>
+      </c>
+      <c r="AP5">
+        <v>-1.181146025878004</v>
+      </c>
+      <c r="AQ5">
+        <v>-3.748387096774193</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>One on One Educational Services Limited (JMSE:ONE)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>JMSE:ONE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.19047619047619</v>
+      </c>
+      <c r="F2">
+        <v>3.00717186432266</v>
+      </c>
+      <c r="G2">
+        <v>14.7647058823529</v>
+      </c>
+      <c r="H2">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="I2">
+        <v>0.0183869313603399</v>
+      </c>
+      <c r="J2">
+        <v>0.01</v>
+      </c>
+      <c r="K2">
+        <v>13.4</v>
+      </c>
+      <c r="L2">
+        <v>13.5795783399808</v>
+      </c>
+      <c r="M2">
+        <v>13.033</v>
+      </c>
+      <c r="N2">
+        <v>13.0980883399808</v>
+      </c>
+      <c r="O2">
+        <v>0.251</v>
+      </c>
+      <c r="P2">
+        <v>0.13651</v>
+      </c>
+      <c r="Q2">
+        <v>0.123148108191428</v>
+      </c>
+      <c r="R2">
+        <v>0.122728957075617</v>
+      </c>
+      <c r="S2">
+        <v>0.0749220823518473</v>
+      </c>
+      <c r="T2">
+        <v>0.045675</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.124051446436632</v>
+      </c>
+      <c r="X2">
+        <v>0.12350727987436</v>
+      </c>
+      <c r="Y2">
+        <v>0.762298514807865</v>
+      </c>
+      <c r="Z2">
+        <v>0.757432704554</v>
+      </c>
+      <c r="AA2">
+        <v>0.251</v>
+      </c>
+      <c r="AB2">
+        <v>0.09989610980246301</v>
+      </c>
+      <c r="AC2">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="AD2">
+        <v>0.251</v>
+      </c>
+      <c r="AE2">
+        <v>0.042</v>
+      </c>
+      <c r="AF2">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="AG2">
+        <v>0.017</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>13.4</v>
+      </c>
+      <c r="AK2">
+        <v>0.1118347271844283</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.25</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>0.187</v>
+      </c>
+      <c r="AR2">
+        <v>0.042</v>
+      </c>
+      <c r="AS2">
+        <v>0.251</v>
+      </c>
+      <c r="AT2">
+        <v>0.618</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1228703830331996</v>
+      </c>
+      <c r="C2">
+        <v>13.69405430588755</v>
+      </c>
+      <c r="D2">
+        <v>13.07605430588755</v>
+      </c>
+      <c r="E2">
+        <v>-0.251</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.618</v>
+      </c>
+      <c r="H2">
+        <v>13.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.034</v>
+      </c>
+      <c r="K2">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L2">
+        <v>0.025</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.025</v>
+      </c>
+      <c r="O2">
+        <v>0.00625</v>
+      </c>
+      <c r="P2">
+        <v>0.01875</v>
+      </c>
+      <c r="Q2">
+        <v>0.02775</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1228703830331996</v>
+      </c>
+      <c r="T2">
+        <v>0.7517377218129921</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.033525</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1227289570756166</v>
+      </c>
+      <c r="C3">
+        <v>13.57957833998083</v>
+      </c>
+      <c r="D3">
+        <v>13.09808833998083</v>
+      </c>
+      <c r="E3">
+        <v>-0.11449</v>
+      </c>
+      <c r="F3">
+        <v>0.13651</v>
+      </c>
+      <c r="G3">
+        <v>0.618</v>
+      </c>
+      <c r="H3">
+        <v>13.4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.034</v>
+      </c>
+      <c r="K3">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L3">
+        <v>0.025</v>
+      </c>
+      <c r="M3">
+        <v>0.008313459</v>
+      </c>
+      <c r="N3">
+        <v>0.016686541</v>
+      </c>
+      <c r="O3">
+        <v>0.00417163525</v>
+      </c>
+      <c r="P3">
+        <v>0.01251490575</v>
+      </c>
+      <c r="Q3">
+        <v>0.02151490575</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1235072798743602</v>
+      </c>
+      <c r="T3">
+        <v>0.7574327045539997</v>
+      </c>
+      <c r="U3">
+        <v>0.0609</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.045675</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>3.00717186432266</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1262513562538932</v>
+      </c>
+      <c r="C4">
+        <v>12.91549852766372</v>
+      </c>
+      <c r="D4">
+        <v>12.57051852766372</v>
+      </c>
+      <c r="E4">
+        <v>0.02201999999999998</v>
+      </c>
+      <c r="F4">
+        <v>0.27302</v>
+      </c>
+      <c r="G4">
+        <v>0.618</v>
+      </c>
+      <c r="H4">
+        <v>13.4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.034</v>
+      </c>
+      <c r="K4">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L4">
+        <v>0.025</v>
+      </c>
+      <c r="M4">
+        <v>0.065197176</v>
+      </c>
+      <c r="N4">
+        <v>-0.04019717599999999</v>
+      </c>
+      <c r="O4">
+        <v>-0.010049294</v>
+      </c>
+      <c r="P4">
+        <v>-0.03014788199999999</v>
+      </c>
+      <c r="Q4">
+        <v>-0.02114788199999999</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1244216307859555</v>
+      </c>
+      <c r="T4">
+        <v>0.7656086167649482</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>0.09586304781053707</v>
+      </c>
+      <c r="W4">
+        <v>0.2159079041828438</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>0.3834521912421484</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1282513562538933</v>
+      </c>
+      <c r="C5">
+        <v>12.49793032901586</v>
+      </c>
+      <c r="D5">
+        <v>12.28946032901586</v>
+      </c>
+      <c r="E5">
+        <v>0.15853</v>
+      </c>
+      <c r="F5">
+        <v>0.40953</v>
+      </c>
+      <c r="G5">
+        <v>0.618</v>
+      </c>
+      <c r="H5">
+        <v>13.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.034</v>
+      </c>
+      <c r="K5">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L5">
+        <v>0.025</v>
+      </c>
+      <c r="M5">
+        <v>0.09779576400000001</v>
+      </c>
+      <c r="N5">
+        <v>-0.07279576400000001</v>
+      </c>
+      <c r="O5">
+        <v>-0.018198941</v>
+      </c>
+      <c r="P5">
+        <v>-0.05459682300000001</v>
+      </c>
+      <c r="Q5">
+        <v>-0.04559682300000001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.125304328010553</v>
+      </c>
+      <c r="T5">
+        <v>0.7735014891027312</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>0.06390869854035805</v>
+      </c>
+      <c r="W5">
+        <v>0.2235386027885625</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>0.2556347941614321</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1302513562538932</v>
+      </c>
+      <c r="C6">
+        <v>12.09265536297431</v>
+      </c>
+      <c r="D6">
+        <v>12.02069536297431</v>
+      </c>
+      <c r="E6">
+        <v>0.29504</v>
+      </c>
+      <c r="F6">
+        <v>0.54604</v>
+      </c>
+      <c r="G6">
+        <v>0.618</v>
+      </c>
+      <c r="H6">
+        <v>13.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.034</v>
+      </c>
+      <c r="K6">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L6">
+        <v>0.025</v>
+      </c>
+      <c r="M6">
+        <v>0.130394352</v>
+      </c>
+      <c r="N6">
+        <v>-0.105394352</v>
+      </c>
+      <c r="O6">
+        <v>-0.026348588</v>
+      </c>
+      <c r="P6">
+        <v>-0.07904576399999999</v>
+      </c>
+      <c r="Q6">
+        <v>-0.07004576399999998</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1262054147606629</v>
+      </c>
+      <c r="T6">
+        <v>0.7815587962808846</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>0.04793152390526854</v>
+      </c>
+      <c r="W6">
+        <v>0.2273539520914219</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>0.1917260956210741</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1322513562538933</v>
+      </c>
+      <c r="C7">
+        <v>11.69888434837082</v>
+      </c>
+      <c r="D7">
+        <v>11.76343434837082</v>
+      </c>
+      <c r="E7">
+        <v>0.43155</v>
+      </c>
+      <c r="F7">
+        <v>0.68255</v>
+      </c>
+      <c r="G7">
+        <v>0.618</v>
+      </c>
+      <c r="H7">
+        <v>13.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.034</v>
+      </c>
+      <c r="K7">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L7">
+        <v>0.025</v>
+      </c>
+      <c r="M7">
+        <v>0.16299294</v>
+      </c>
+      <c r="N7">
+        <v>-0.13799294</v>
+      </c>
+      <c r="O7">
+        <v>-0.034498235</v>
+      </c>
+      <c r="P7">
+        <v>-0.103494705</v>
+      </c>
+      <c r="Q7">
+        <v>-0.09449470500000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1271254717581436</v>
+      </c>
+      <c r="T7">
+        <v>0.7897857309785782</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>0.03834521912421483</v>
+      </c>
+      <c r="W7">
+        <v>0.2296431616731375</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>0.1533808764968593</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1342513562538932</v>
+      </c>
+      <c r="C8">
+        <v>11.31589415552618</v>
+      </c>
+      <c r="D8">
+        <v>11.51695415552618</v>
+      </c>
+      <c r="E8">
+        <v>0.56806</v>
+      </c>
+      <c r="F8">
+        <v>0.81906</v>
+      </c>
+      <c r="G8">
+        <v>0.618</v>
+      </c>
+      <c r="H8">
+        <v>13.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.034</v>
+      </c>
+      <c r="K8">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L8">
+        <v>0.025</v>
+      </c>
+      <c r="M8">
+        <v>0.195591528</v>
+      </c>
+      <c r="N8">
+        <v>-0.170591528</v>
+      </c>
+      <c r="O8">
+        <v>-0.04264788200000001</v>
+      </c>
+      <c r="P8">
+        <v>-0.127943646</v>
+      </c>
+      <c r="Q8">
+        <v>-0.118943646</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1280651044364217</v>
+      </c>
+      <c r="T8">
+        <v>0.7981877068400524</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>0.03195434927017902</v>
+      </c>
+      <c r="W8">
+        <v>0.2311693013942813</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>0.127817397080716</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1362513562538933</v>
+      </c>
+      <c r="C9">
+        <v>10.94302101809542</v>
+      </c>
+      <c r="D9">
+        <v>11.28059101809542</v>
+      </c>
+      <c r="E9">
+        <v>0.70457</v>
+      </c>
+      <c r="F9">
+        <v>0.95557</v>
+      </c>
+      <c r="G9">
+        <v>0.618</v>
+      </c>
+      <c r="H9">
+        <v>13.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.034</v>
+      </c>
+      <c r="K9">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L9">
+        <v>0.025</v>
+      </c>
+      <c r="M9">
+        <v>0.228190116</v>
+      </c>
+      <c r="N9">
+        <v>-0.203190116</v>
+      </c>
+      <c r="O9">
+        <v>-0.05079752900000001</v>
+      </c>
+      <c r="P9">
+        <v>-0.152392587</v>
+      </c>
+      <c r="Q9">
+        <v>-0.143392587</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1290249442690714</v>
+      </c>
+      <c r="T9">
+        <v>0.8067703703544616</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>0.02738944223158202</v>
+      </c>
+      <c r="W9">
+        <v>0.2322594011950982</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>0.1095577689263281</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1382513562538933</v>
+      </c>
+      <c r="C10">
+        <v>10.5796545639854</v>
+      </c>
+      <c r="D10">
+        <v>11.0537345639854</v>
+      </c>
+      <c r="E10">
+        <v>0.8410799999999999</v>
+      </c>
+      <c r="F10">
+        <v>1.09208</v>
+      </c>
+      <c r="G10">
+        <v>0.618</v>
+      </c>
+      <c r="H10">
+        <v>13.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.034</v>
+      </c>
+      <c r="K10">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L10">
+        <v>0.025</v>
+      </c>
+      <c r="M10">
+        <v>0.260788704</v>
+      </c>
+      <c r="N10">
+        <v>-0.235788704</v>
+      </c>
+      <c r="O10">
+        <v>-0.058947176</v>
+      </c>
+      <c r="P10">
+        <v>-0.176841528</v>
+      </c>
+      <c r="Q10">
+        <v>-0.167841528</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1300056501850396</v>
+      </c>
+      <c r="T10">
+        <v>0.8155396135104884</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>0.02396576195263427</v>
+      </c>
+      <c r="W10">
+        <v>0.233076976045711</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>0.09586304781053701</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1402513562538933</v>
+      </c>
+      <c r="C11">
+        <v>10.22523255231506</v>
+      </c>
+      <c r="D11">
+        <v>10.83582255231506</v>
+      </c>
+      <c r="E11">
+        <v>0.9775899999999998</v>
+      </c>
+      <c r="F11">
+        <v>1.22859</v>
+      </c>
+      <c r="G11">
+        <v>0.618</v>
+      </c>
+      <c r="H11">
+        <v>13.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.034</v>
+      </c>
+      <c r="K11">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L11">
+        <v>0.025</v>
+      </c>
+      <c r="M11">
+        <v>0.293387292</v>
+      </c>
+      <c r="N11">
+        <v>-0.2683872919999999</v>
+      </c>
+      <c r="O11">
+        <v>-0.06709682299999999</v>
+      </c>
+      <c r="P11">
+        <v>-0.201290469</v>
+      </c>
+      <c r="Q11">
+        <v>-0.192290469</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1310079100771828</v>
+      </c>
+      <c r="T11">
+        <v>0.824501587285329</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>0.02130289951345269</v>
+      </c>
+      <c r="W11">
+        <v>0.2337128675961875</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.08521159805381084</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1422513562538932</v>
+      </c>
+      <c r="C12">
+        <v>9.879236220870135</v>
+      </c>
+      <c r="D12">
+        <v>10.62633622087013</v>
+      </c>
+      <c r="E12">
+        <v>1.1141</v>
+      </c>
+      <c r="F12">
+        <v>1.3651</v>
+      </c>
+      <c r="G12">
+        <v>0.618</v>
+      </c>
+      <c r="H12">
+        <v>13.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.034</v>
+      </c>
+      <c r="K12">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L12">
+        <v>0.025</v>
+      </c>
+      <c r="M12">
+        <v>0.32598588</v>
+      </c>
+      <c r="N12">
+        <v>-0.30098588</v>
+      </c>
+      <c r="O12">
+        <v>-0.07524647</v>
+      </c>
+      <c r="P12">
+        <v>-0.22573941</v>
+      </c>
+      <c r="Q12">
+        <v>-0.21673941</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1320324424113737</v>
+      </c>
+      <c r="T12">
+        <v>0.8336627160329436</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>0.01917260956210742</v>
+      </c>
+      <c r="W12">
+        <v>0.2342215808365688</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.07669043824842969</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1442513562538933</v>
+      </c>
+      <c r="C13">
+        <v>9.54118616300145</v>
+      </c>
+      <c r="D13">
+        <v>10.42479616300145</v>
+      </c>
+      <c r="E13">
+        <v>1.25061</v>
+      </c>
+      <c r="F13">
+        <v>1.50161</v>
+      </c>
+      <c r="G13">
+        <v>0.618</v>
+      </c>
+      <c r="H13">
+        <v>13.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.034</v>
+      </c>
+      <c r="K13">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L13">
+        <v>0.025</v>
+      </c>
+      <c r="M13">
+        <v>0.358584468</v>
+      </c>
+      <c r="N13">
+        <v>-0.333584468</v>
+      </c>
+      <c r="O13">
+        <v>-0.08339611699999999</v>
+      </c>
+      <c r="P13">
+        <v>-0.250188351</v>
+      </c>
+      <c r="Q13">
+        <v>-0.241188351</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1330799979440858</v>
+      </c>
+      <c r="T13">
+        <v>0.8430297128423027</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>0.01742964505646129</v>
+      </c>
+      <c r="W13">
+        <v>0.2346378007605171</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.06971858022584521</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1462513562538932</v>
+      </c>
+      <c r="C14">
+        <v>9.21063866498479</v>
+      </c>
+      <c r="D14">
+        <v>10.23075866498479</v>
+      </c>
+      <c r="E14">
+        <v>1.38712</v>
+      </c>
+      <c r="F14">
+        <v>1.63812</v>
+      </c>
+      <c r="G14">
+        <v>0.618</v>
+      </c>
+      <c r="H14">
+        <v>13.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.034</v>
+      </c>
+      <c r="K14">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L14">
+        <v>0.025</v>
+      </c>
+      <c r="M14">
+        <v>0.391183056</v>
+      </c>
+      <c r="N14">
+        <v>-0.366183056</v>
+      </c>
+      <c r="O14">
+        <v>-0.091545764</v>
+      </c>
+      <c r="P14">
+        <v>-0.274637292</v>
+      </c>
+      <c r="Q14">
+        <v>-0.265637292</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1341513615570868</v>
+      </c>
+      <c r="T14">
+        <v>0.8526095959427833</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>0.01597717463508951</v>
+      </c>
+      <c r="W14">
+        <v>0.2349846506971406</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.06390869854035808</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1482513562538933</v>
+      </c>
+      <c r="C15">
+        <v>8.887182444944305</v>
+      </c>
+      <c r="D15">
+        <v>10.0438124449443</v>
+      </c>
+      <c r="E15">
+        <v>1.52363</v>
+      </c>
+      <c r="F15">
+        <v>1.77463</v>
+      </c>
+      <c r="G15">
+        <v>0.618</v>
+      </c>
+      <c r="H15">
+        <v>13.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.034</v>
+      </c>
+      <c r="K15">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L15">
+        <v>0.025</v>
+      </c>
+      <c r="M15">
+        <v>0.423781644</v>
+      </c>
+      <c r="N15">
+        <v>-0.398781644</v>
+      </c>
+      <c r="O15">
+        <v>-0.099695411</v>
+      </c>
+      <c r="P15">
+        <v>-0.299086233</v>
+      </c>
+      <c r="Q15">
+        <v>-0.290086233</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1352473542186625</v>
+      </c>
+      <c r="T15">
+        <v>0.8624097062409762</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>0.01474816120162109</v>
+      </c>
+      <c r="W15">
+        <v>0.2352781391050529</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.05899264480648436</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1502513562538932</v>
+      </c>
+      <c r="C16">
+        <v>8.570435742897114</v>
+      </c>
+      <c r="D16">
+        <v>9.863575742897114</v>
+      </c>
+      <c r="E16">
+        <v>1.66014</v>
+      </c>
+      <c r="F16">
+        <v>1.91114</v>
+      </c>
+      <c r="G16">
+        <v>0.618</v>
+      </c>
+      <c r="H16">
+        <v>13.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.034</v>
+      </c>
+      <c r="K16">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L16">
+        <v>0.025</v>
+      </c>
+      <c r="M16">
+        <v>0.4563802320000001</v>
+      </c>
+      <c r="N16">
+        <v>-0.431380232</v>
+      </c>
+      <c r="O16">
+        <v>-0.107845058</v>
+      </c>
+      <c r="P16">
+        <v>-0.323535174</v>
+      </c>
+      <c r="Q16">
+        <v>-0.314535174</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1363688350816702</v>
+      </c>
+      <c r="T16">
+        <v>0.8724377260809875</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>0.01369472111579101</v>
+      </c>
+      <c r="W16">
+        <v>0.2355297005975491</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.05477888446316403</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1522513562538933</v>
+      </c>
+      <c r="C17">
+        <v>8.260043718590175</v>
+      </c>
+      <c r="D17">
+        <v>9.689693718590174</v>
+      </c>
+      <c r="E17">
+        <v>1.79665</v>
+      </c>
+      <c r="F17">
+        <v>2.04765</v>
+      </c>
+      <c r="G17">
+        <v>0.618</v>
+      </c>
+      <c r="H17">
+        <v>13.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.034</v>
+      </c>
+      <c r="K17">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L17">
+        <v>0.025</v>
+      </c>
+      <c r="M17">
+        <v>0.48897882</v>
+      </c>
+      <c r="N17">
+        <v>-0.46397882</v>
+      </c>
+      <c r="O17">
+        <v>-0.115994705</v>
+      </c>
+      <c r="P17">
+        <v>-0.347984115</v>
+      </c>
+      <c r="Q17">
+        <v>-0.338984115</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1375167037296899</v>
+      </c>
+      <c r="T17">
+        <v>0.8827016993289991</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0.01278173970807161</v>
+      </c>
+      <c r="W17">
+        <v>0.2357477205577125</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.05112695883228646</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1542513562538932</v>
+      </c>
+      <c r="C18">
+        <v>7.955676119805782</v>
+      </c>
+      <c r="D18">
+        <v>9.521836119805782</v>
+      </c>
+      <c r="E18">
+        <v>1.93316</v>
+      </c>
+      <c r="F18">
+        <v>2.18416</v>
+      </c>
+      <c r="G18">
+        <v>0.618</v>
+      </c>
+      <c r="H18">
+        <v>13.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.034</v>
+      </c>
+      <c r="K18">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L18">
+        <v>0.025</v>
+      </c>
+      <c r="M18">
+        <v>0.521577408</v>
+      </c>
+      <c r="N18">
+        <v>-0.4965774079999999</v>
+      </c>
+      <c r="O18">
+        <v>-0.124144352</v>
+      </c>
+      <c r="P18">
+        <v>-0.372433056</v>
+      </c>
+      <c r="Q18">
+        <v>-0.363433056</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1386919025836147</v>
+      </c>
+      <c r="T18">
+        <v>0.8932100528924396</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0.01198288097631713</v>
+      </c>
+      <c r="W18">
+        <v>0.2359384880228555</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.04793152390526856</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1562513562538932</v>
+      </c>
+      <c r="C19">
+        <v>7.657025188896094</v>
+      </c>
+      <c r="D19">
+        <v>9.359695188896094</v>
+      </c>
+      <c r="E19">
+        <v>2.06967</v>
+      </c>
+      <c r="F19">
+        <v>2.32067</v>
+      </c>
+      <c r="G19">
+        <v>0.618</v>
+      </c>
+      <c r="H19">
+        <v>13.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.034</v>
+      </c>
+      <c r="K19">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L19">
+        <v>0.025</v>
+      </c>
+      <c r="M19">
+        <v>0.5541759960000001</v>
+      </c>
+      <c r="N19">
+        <v>-0.5291759960000001</v>
+      </c>
+      <c r="O19">
+        <v>-0.132293999</v>
+      </c>
+      <c r="P19">
+        <v>-0.396881997</v>
+      </c>
+      <c r="Q19">
+        <v>-0.387881997</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1398954194822125</v>
+      </c>
+      <c r="T19">
+        <v>0.903971619794758</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.01127800562476907</v>
+      </c>
+      <c r="W19">
+        <v>0.2361068122568052</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.04511202249907631</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1582513562538932</v>
+      </c>
+      <c r="C20">
+        <v>7.36380377962583</v>
+      </c>
+      <c r="D20">
+        <v>9.202983779625828</v>
+      </c>
+      <c r="E20">
+        <v>2.20618</v>
+      </c>
+      <c r="F20">
+        <v>2.45718</v>
+      </c>
+      <c r="G20">
+        <v>0.618</v>
+      </c>
+      <c r="H20">
+        <v>13.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.034</v>
+      </c>
+      <c r="K20">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L20">
+        <v>0.025</v>
+      </c>
+      <c r="M20">
+        <v>0.5867745839999999</v>
+      </c>
+      <c r="N20">
+        <v>-0.5617745839999999</v>
+      </c>
+      <c r="O20">
+        <v>-0.140443646</v>
+      </c>
+      <c r="P20">
+        <v>-0.4213309379999999</v>
+      </c>
+      <c r="Q20">
+        <v>-0.4123309379999999</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1411282904515078</v>
+      </c>
+      <c r="T20">
+        <v>0.9149956639385965</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.01065144975672634</v>
+      </c>
+      <c r="W20">
+        <v>0.2362564337980937</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.04260579902690542</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1602513562538933</v>
+      </c>
+      <c r="C21">
+        <v>7.075743660080237</v>
+      </c>
+      <c r="D21">
+        <v>9.051433660080237</v>
+      </c>
+      <c r="E21">
+        <v>2.34269</v>
+      </c>
+      <c r="F21">
+        <v>2.59369</v>
+      </c>
+      <c r="G21">
+        <v>0.618</v>
+      </c>
+      <c r="H21">
+        <v>13.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.034</v>
+      </c>
+      <c r="K21">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L21">
+        <v>0.025</v>
+      </c>
+      <c r="M21">
+        <v>0.6193731720000001</v>
+      </c>
+      <c r="N21">
+        <v>-0.5943731720000001</v>
+      </c>
+      <c r="O21">
+        <v>-0.148593293</v>
+      </c>
+      <c r="P21">
+        <v>-0.445779879</v>
+      </c>
+      <c r="Q21">
+        <v>-0.436779879</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1423916026793042</v>
+      </c>
+      <c r="T21">
+        <v>0.9262919067032707</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.01009084713795127</v>
+      </c>
+      <c r="W21">
+        <v>0.2363903057034573</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.0403633885518051</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1622513562538933</v>
+      </c>
+      <c r="C22">
+        <v>6.792593980537715</v>
+      </c>
+      <c r="D22">
+        <v>8.904793980537715</v>
+      </c>
+      <c r="E22">
+        <v>2.4792</v>
+      </c>
+      <c r="F22">
+        <v>2.7302</v>
+      </c>
+      <c r="G22">
+        <v>0.618</v>
+      </c>
+      <c r="H22">
+        <v>13.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.034</v>
+      </c>
+      <c r="K22">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L22">
+        <v>0.025</v>
+      </c>
+      <c r="M22">
+        <v>0.65197176</v>
+      </c>
+      <c r="N22">
+        <v>-0.62697176</v>
+      </c>
+      <c r="O22">
+        <v>-0.15674294</v>
+      </c>
+      <c r="P22">
+        <v>-0.47022882</v>
+      </c>
+      <c r="Q22">
+        <v>-0.46122882</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1436864977127955</v>
+      </c>
+      <c r="T22">
+        <v>0.9378705555370617</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.009586304781053708</v>
+      </c>
+      <c r="W22">
+        <v>0.2365107904182844</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.03834521912421485</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1642513562538933</v>
+      </c>
+      <c r="C23">
+        <v>6.514119887897445</v>
+      </c>
+      <c r="D23">
+        <v>8.762829887897444</v>
+      </c>
+      <c r="E23">
+        <v>2.61571</v>
+      </c>
+      <c r="F23">
+        <v>2.86671</v>
+      </c>
+      <c r="G23">
+        <v>0.618</v>
+      </c>
+      <c r="H23">
+        <v>13.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.034</v>
+      </c>
+      <c r="K23">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L23">
+        <v>0.025</v>
+      </c>
+      <c r="M23">
+        <v>0.6845703480000001</v>
+      </c>
+      <c r="N23">
+        <v>-0.659570348</v>
+      </c>
+      <c r="O23">
+        <v>-0.164892587</v>
+      </c>
+      <c r="P23">
+        <v>-0.494677761</v>
+      </c>
+      <c r="Q23">
+        <v>-0.485677761</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1450141748990334</v>
+      </c>
+      <c r="T23">
+        <v>0.9497423347210751</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.009129814077194006</v>
+      </c>
+      <c r="W23">
+        <v>0.2366198003983661</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.03651925630877606</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1662513562538933</v>
+      </c>
+      <c r="C24">
+        <v>6.240101270563611</v>
+      </c>
+      <c r="D24">
+        <v>8.62532127056361</v>
+      </c>
+      <c r="E24">
+        <v>2.75222</v>
+      </c>
+      <c r="F24">
+        <v>3.00322</v>
+      </c>
+      <c r="G24">
+        <v>0.618</v>
+      </c>
+      <c r="H24">
+        <v>13.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.034</v>
+      </c>
+      <c r="K24">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L24">
+        <v>0.025</v>
+      </c>
+      <c r="M24">
+        <v>0.717168936</v>
+      </c>
+      <c r="N24">
+        <v>-0.692168936</v>
+      </c>
+      <c r="O24">
+        <v>-0.173042234</v>
+      </c>
+      <c r="P24">
+        <v>-0.519126702</v>
+      </c>
+      <c r="Q24">
+        <v>-0.510126702</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1463758950900466</v>
+      </c>
+      <c r="T24">
+        <v>0.9619185184995503</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.008714822528230644</v>
+      </c>
+      <c r="W24">
+        <v>0.2367189003802585</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.03485929011292255</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1682513562538933</v>
+      </c>
+      <c r="C25">
+        <v>5.9703316196775</v>
+      </c>
+      <c r="D25">
+        <v>8.4920616196775</v>
+      </c>
+      <c r="E25">
+        <v>2.88873</v>
+      </c>
+      <c r="F25">
+        <v>3.13973</v>
+      </c>
+      <c r="G25">
+        <v>0.618</v>
+      </c>
+      <c r="H25">
+        <v>13.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.034</v>
+      </c>
+      <c r="K25">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L25">
+        <v>0.025</v>
+      </c>
+      <c r="M25">
+        <v>0.749767524</v>
+      </c>
+      <c r="N25">
+        <v>-0.724767524</v>
+      </c>
+      <c r="O25">
+        <v>-0.181191881</v>
+      </c>
+      <c r="P25">
+        <v>-0.5435756430000001</v>
+      </c>
+      <c r="Q25">
+        <v>-0.534575643</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1477729846366706</v>
+      </c>
+      <c r="T25">
+        <v>0.9744109667917523</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.008335917200916268</v>
+      </c>
+      <c r="W25">
+        <v>0.2368093829724212</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.03334366880366513</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1702513562538933</v>
+      </c>
+      <c r="C26">
+        <v>5.704616994306038</v>
+      </c>
+      <c r="D26">
+        <v>8.362856994306037</v>
+      </c>
+      <c r="E26">
+        <v>3.02524</v>
+      </c>
+      <c r="F26">
+        <v>3.27624</v>
+      </c>
+      <c r="G26">
+        <v>0.618</v>
+      </c>
+      <c r="H26">
+        <v>13.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.034</v>
+      </c>
+      <c r="K26">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L26">
+        <v>0.025</v>
+      </c>
+      <c r="M26">
+        <v>0.7823661120000001</v>
+      </c>
+      <c r="N26">
+        <v>-0.757366112</v>
+      </c>
+      <c r="O26">
+        <v>-0.189341528</v>
+      </c>
+      <c r="P26">
+        <v>-0.568024584</v>
+      </c>
+      <c r="Q26">
+        <v>-0.559024584</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1492068396976794</v>
+      </c>
+      <c r="T26">
+        <v>0.9872321637232228</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.007988587317544756</v>
+      </c>
+      <c r="W26">
+        <v>0.2368923253485703</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.03195434927017904</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1722513562538933</v>
+      </c>
+      <c r="C27">
+        <v>5.442775079680973</v>
+      </c>
+      <c r="D27">
+        <v>8.237525079680973</v>
+      </c>
+      <c r="E27">
+        <v>3.16175</v>
+      </c>
+      <c r="F27">
+        <v>3.41275</v>
+      </c>
+      <c r="G27">
+        <v>0.618</v>
+      </c>
+      <c r="H27">
+        <v>13.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.034</v>
+      </c>
+      <c r="K27">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L27">
+        <v>0.025</v>
+      </c>
+      <c r="M27">
+        <v>0.8149647</v>
+      </c>
+      <c r="N27">
+        <v>-0.7899647</v>
+      </c>
+      <c r="O27">
+        <v>-0.197491175</v>
+      </c>
+      <c r="P27">
+        <v>-0.5924735249999999</v>
+      </c>
+      <c r="Q27">
+        <v>-0.5834735249999999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1506789308936485</v>
+      </c>
+      <c r="T27">
+        <v>1.000395259239532</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.007669043824842966</v>
+      </c>
+      <c r="W27">
+        <v>0.2369686323346275</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.03067617529937194</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1742513562538933</v>
+      </c>
+      <c r="C28">
+        <v>5.184634328871205</v>
+      </c>
+      <c r="D28">
+        <v>8.115894328871205</v>
+      </c>
+      <c r="E28">
+        <v>3.29826</v>
+      </c>
+      <c r="F28">
+        <v>3.54926</v>
+      </c>
+      <c r="G28">
+        <v>0.618</v>
+      </c>
+      <c r="H28">
+        <v>13.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.034</v>
+      </c>
+      <c r="K28">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L28">
+        <v>0.025</v>
+      </c>
+      <c r="M28">
+        <v>0.847563288</v>
+      </c>
+      <c r="N28">
+        <v>-0.822563288</v>
+      </c>
+      <c r="O28">
+        <v>-0.205640822</v>
+      </c>
+      <c r="P28">
+        <v>-0.616922466</v>
+      </c>
+      <c r="Q28">
+        <v>-0.607922466</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1521908083381573</v>
+      </c>
+      <c r="T28">
+        <v>1.013914114094121</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.007374080600810544</v>
+      </c>
+      <c r="W28">
+        <v>0.2370390695525265</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.02949632240324218</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1762513562538933</v>
+      </c>
+      <c r="C29">
+        <v>4.930033179390223</v>
+      </c>
+      <c r="D29">
+        <v>7.997803179390223</v>
+      </c>
+      <c r="E29">
+        <v>3.43477</v>
+      </c>
+      <c r="F29">
+        <v>3.68577</v>
+      </c>
+      <c r="G29">
+        <v>0.618</v>
+      </c>
+      <c r="H29">
+        <v>13.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.034</v>
+      </c>
+      <c r="K29">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L29">
+        <v>0.025</v>
+      </c>
+      <c r="M29">
+        <v>0.8801618760000001</v>
+      </c>
+      <c r="N29">
+        <v>-0.855161876</v>
+      </c>
+      <c r="O29">
+        <v>-0.213790469</v>
+      </c>
+      <c r="P29">
+        <v>-0.6413714070000001</v>
+      </c>
+      <c r="Q29">
+        <v>-0.6323714070000001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1537441070825156</v>
+      </c>
+      <c r="T29">
+        <v>1.027803348533766</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.007100966504484227</v>
+      </c>
+      <c r="W29">
+        <v>0.2371042891987292</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.02840386601793699</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1782513562538933</v>
+      </c>
+      <c r="C30">
+        <v>4.678819337215622</v>
+      </c>
+      <c r="D30">
+        <v>7.883099337215623</v>
+      </c>
+      <c r="E30">
+        <v>3.57128</v>
+      </c>
+      <c r="F30">
+        <v>3.82228</v>
+      </c>
+      <c r="G30">
+        <v>0.618</v>
+      </c>
+      <c r="H30">
+        <v>13.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.034</v>
+      </c>
+      <c r="K30">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L30">
+        <v>0.025</v>
+      </c>
+      <c r="M30">
+        <v>0.9127604640000001</v>
+      </c>
+      <c r="N30">
+        <v>-0.8877604640000001</v>
+      </c>
+      <c r="O30">
+        <v>-0.221940116</v>
+      </c>
+      <c r="P30">
+        <v>-0.665820348</v>
+      </c>
+      <c r="Q30">
+        <v>-0.656820348</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1553405530142172</v>
+      </c>
+      <c r="T30">
+        <v>1.04207839504118</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.006847360557895504</v>
+      </c>
+      <c r="W30">
+        <v>0.2371648502987746</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.02738944223158202</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1802513562538932</v>
+      </c>
+      <c r="C31">
+        <v>4.430849121548749</v>
+      </c>
+      <c r="D31">
+        <v>7.771639121548748</v>
+      </c>
+      <c r="E31">
+        <v>3.70779</v>
+      </c>
+      <c r="F31">
+        <v>3.95879</v>
+      </c>
+      <c r="G31">
+        <v>0.618</v>
+      </c>
+      <c r="H31">
+        <v>13.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.034</v>
+      </c>
+      <c r="K31">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L31">
+        <v>0.025</v>
+      </c>
+      <c r="M31">
+        <v>0.9453590519999999</v>
+      </c>
+      <c r="N31">
+        <v>-0.9203590519999999</v>
+      </c>
+      <c r="O31">
+        <v>-0.230089763</v>
+      </c>
+      <c r="P31">
+        <v>-0.690269289</v>
+      </c>
+      <c r="Q31">
+        <v>-0.6812692889999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.156981969253854</v>
+      </c>
+      <c r="T31">
+        <v>1.056755555534717</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.006611244676588765</v>
+      </c>
+      <c r="W31">
+        <v>0.2372212347712306</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.02644497870635509</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1822513562538933</v>
+      </c>
+      <c r="C32">
+        <v>4.18598686438648</v>
+      </c>
+      <c r="D32">
+        <v>7.663286864386481</v>
+      </c>
+      <c r="E32">
+        <v>3.8443</v>
+      </c>
+      <c r="F32">
+        <v>4.0953</v>
+      </c>
+      <c r="G32">
+        <v>0.618</v>
+      </c>
+      <c r="H32">
+        <v>13.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.034</v>
+      </c>
+      <c r="K32">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L32">
+        <v>0.025</v>
+      </c>
+      <c r="M32">
+        <v>0.9779576400000001</v>
+      </c>
+      <c r="N32">
+        <v>-0.9529576400000001</v>
+      </c>
+      <c r="O32">
+        <v>-0.23823941</v>
+      </c>
+      <c r="P32">
+        <v>-0.71471823</v>
+      </c>
+      <c r="Q32">
+        <v>-0.70571823</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1586702831003377</v>
+      </c>
+      <c r="T32">
+        <v>1.071852063470928</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.006390869854035804</v>
+      </c>
+      <c r="W32">
+        <v>0.2372738602788563</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.02556347941614323</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1842513562538933</v>
+      </c>
+      <c r="C33">
+        <v>3.944104359629498</v>
+      </c>
+      <c r="D33">
+        <v>7.557914359629498</v>
+      </c>
+      <c r="E33">
+        <v>3.98081</v>
+      </c>
+      <c r="F33">
+        <v>4.23181</v>
+      </c>
+      <c r="G33">
+        <v>0.618</v>
+      </c>
+      <c r="H33">
+        <v>13.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.034</v>
+      </c>
+      <c r="K33">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L33">
+        <v>0.025</v>
+      </c>
+      <c r="M33">
+        <v>1.010556228</v>
+      </c>
+      <c r="N33">
+        <v>-0.9855562280000002</v>
+      </c>
+      <c r="O33">
+        <v>-0.2463890570000001</v>
+      </c>
+      <c r="P33">
+        <v>-0.7391671710000002</v>
+      </c>
+      <c r="Q33">
+        <v>-0.7301671710000002</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1604075335800528</v>
+      </c>
+      <c r="T33">
+        <v>1.087386151347318</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.006184712761970132</v>
+      </c>
+      <c r="W33">
+        <v>0.2373230905924416</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.02473885104788054</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1862513562538933</v>
+      </c>
+      <c r="C34">
+        <v>3.705080357023573</v>
+      </c>
+      <c r="D34">
+        <v>7.455400357023573</v>
+      </c>
+      <c r="E34">
+        <v>4.117319999999999</v>
+      </c>
+      <c r="F34">
+        <v>4.36832</v>
+      </c>
+      <c r="G34">
+        <v>0.618</v>
+      </c>
+      <c r="H34">
+        <v>13.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.034</v>
+      </c>
+      <c r="K34">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L34">
+        <v>0.025</v>
+      </c>
+      <c r="M34">
+        <v>1.043154816</v>
+      </c>
+      <c r="N34">
+        <v>-1.018154816</v>
+      </c>
+      <c r="O34">
+        <v>-0.254538704</v>
+      </c>
+      <c r="P34">
+        <v>-0.763616112</v>
+      </c>
+      <c r="Q34">
+        <v>-0.754616112</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1621958796621124</v>
+      </c>
+      <c r="T34">
+        <v>1.103377124161249</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.005991440488158567</v>
+      </c>
+      <c r="W34">
+        <v>0.2373692440114278</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.02396576195263422</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1882513562538933</v>
+      </c>
+      <c r="C35">
+        <v>3.468800096734222</v>
+      </c>
+      <c r="D35">
+        <v>7.355630096734222</v>
+      </c>
+      <c r="E35">
+        <v>4.25383</v>
+      </c>
+      <c r="F35">
+        <v>4.50483</v>
+      </c>
+      <c r="G35">
+        <v>0.618</v>
+      </c>
+      <c r="H35">
+        <v>13.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.034</v>
+      </c>
+      <c r="K35">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L35">
+        <v>0.025</v>
+      </c>
+      <c r="M35">
+        <v>1.075753404</v>
+      </c>
+      <c r="N35">
+        <v>-1.050753404</v>
+      </c>
+      <c r="O35">
+        <v>-0.262688351</v>
+      </c>
+      <c r="P35">
+        <v>-0.7880650530000002</v>
+      </c>
+      <c r="Q35">
+        <v>-0.7790650530000002</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.164037609209308</v>
+      </c>
+      <c r="T35">
+        <v>1.119845439447238</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.005809881685487095</v>
+      </c>
+      <c r="W35">
+        <v>0.2374126002535057</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.02323952674194829</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1902513562538933</v>
+      </c>
+      <c r="C36">
+        <v>3.235154880798575</v>
+      </c>
+      <c r="D36">
+        <v>7.258494880798575</v>
+      </c>
+      <c r="E36">
+        <v>4.39034</v>
+      </c>
+      <c r="F36">
+        <v>4.64134</v>
+      </c>
+      <c r="G36">
+        <v>0.618</v>
+      </c>
+      <c r="H36">
+        <v>13.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.034</v>
+      </c>
+      <c r="K36">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L36">
+        <v>0.025</v>
+      </c>
+      <c r="M36">
+        <v>1.108351992</v>
+      </c>
+      <c r="N36">
+        <v>-1.083351992</v>
+      </c>
+      <c r="O36">
+        <v>-0.2708379980000001</v>
+      </c>
+      <c r="P36">
+        <v>-0.8125139940000002</v>
+      </c>
+      <c r="Q36">
+        <v>-0.8035139940000002</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1659351487427824</v>
+      </c>
+      <c r="T36">
+        <v>1.136812794590378</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.005639002812384533</v>
+      </c>
+      <c r="W36">
+        <v>0.2374534061284026</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.0225560112495381</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1922513562538933</v>
+      </c>
+      <c r="C37">
+        <v>3.004041678089972</v>
+      </c>
+      <c r="D37">
+        <v>7.163891678089972</v>
+      </c>
+      <c r="E37">
+        <v>4.52685</v>
+      </c>
+      <c r="F37">
+        <v>4.777850000000001</v>
+      </c>
+      <c r="G37">
+        <v>0.618</v>
+      </c>
+      <c r="H37">
+        <v>13.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.034</v>
+      </c>
+      <c r="K37">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L37">
+        <v>0.025</v>
+      </c>
+      <c r="M37">
+        <v>1.14095058</v>
+      </c>
+      <c r="N37">
+        <v>-1.11595058</v>
+      </c>
+      <c r="O37">
+        <v>-0.2789876450000001</v>
+      </c>
+      <c r="P37">
+        <v>-0.8369629350000002</v>
+      </c>
+      <c r="Q37">
+        <v>-0.8279629350000002</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.167891074108056</v>
+      </c>
+      <c r="T37">
+        <v>1.154302222199461</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.005477888446316403</v>
+      </c>
+      <c r="W37">
+        <v>0.2374918802390197</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.02191155378526555</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1942513562538933</v>
+      </c>
+      <c r="C38">
+        <v>2.775362759777168</v>
+      </c>
+      <c r="D38">
+        <v>7.071722759777167</v>
+      </c>
+      <c r="E38">
+        <v>4.663359999999999</v>
+      </c>
+      <c r="F38">
+        <v>4.914359999999999</v>
+      </c>
+      <c r="G38">
+        <v>0.618</v>
+      </c>
+      <c r="H38">
+        <v>13.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.034</v>
+      </c>
+      <c r="K38">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L38">
+        <v>0.025</v>
+      </c>
+      <c r="M38">
+        <v>1.173549168</v>
+      </c>
+      <c r="N38">
+        <v>-1.148549168</v>
+      </c>
+      <c r="O38">
+        <v>-0.287137292</v>
+      </c>
+      <c r="P38">
+        <v>-0.861411876</v>
+      </c>
+      <c r="Q38">
+        <v>-0.852411876</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1699081221409943</v>
+      </c>
+      <c r="T38">
+        <v>1.172338194421327</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.005325724878363172</v>
+      </c>
+      <c r="W38">
+        <v>0.2375282168990469</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.02130289951345266</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1962513562538933</v>
+      </c>
+      <c r="C39">
+        <v>2.549025362566644</v>
+      </c>
+      <c r="D39">
+        <v>6.981895362566643</v>
+      </c>
+      <c r="E39">
+        <v>4.799869999999999</v>
+      </c>
+      <c r="F39">
+        <v>5.05087</v>
+      </c>
+      <c r="G39">
+        <v>0.618</v>
+      </c>
+      <c r="H39">
+        <v>13.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.034</v>
+      </c>
+      <c r="K39">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L39">
+        <v>0.025</v>
+      </c>
+      <c r="M39">
+        <v>1.206147756</v>
+      </c>
+      <c r="N39">
+        <v>-1.181147756</v>
+      </c>
+      <c r="O39">
+        <v>-0.295286939</v>
+      </c>
+      <c r="P39">
+        <v>-0.8858608170000001</v>
+      </c>
+      <c r="Q39">
+        <v>-0.8768608170000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1719892034448197</v>
+      </c>
+      <c r="T39">
+        <v>1.190946737189919</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.00518178636813714</v>
+      </c>
+      <c r="W39">
+        <v>0.2375625894152888</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.0207271454725485</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1982513562538933</v>
+      </c>
+      <c r="C40">
+        <v>2.324941377288658</v>
+      </c>
+      <c r="D40">
+        <v>6.894321377288658</v>
+      </c>
+      <c r="E40">
+        <v>4.93638</v>
+      </c>
+      <c r="F40">
+        <v>5.18738</v>
+      </c>
+      <c r="G40">
+        <v>0.618</v>
+      </c>
+      <c r="H40">
+        <v>13.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.034</v>
+      </c>
+      <c r="K40">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L40">
+        <v>0.025</v>
+      </c>
+      <c r="M40">
+        <v>1.238746344</v>
+      </c>
+      <c r="N40">
+        <v>-1.213746344</v>
+      </c>
+      <c r="O40">
+        <v>-0.3034365860000001</v>
+      </c>
+      <c r="P40">
+        <v>-0.9103097580000001</v>
+      </c>
+      <c r="Q40">
+        <v>-0.9013097580000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1741374164036071</v>
+      </c>
+      <c r="T40">
+        <v>1.210155555531693</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.005045423568975635</v>
+      </c>
+      <c r="W40">
+        <v>0.2375951528517286</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.02018169427590244</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2002513562538933</v>
+      </c>
+      <c r="C41">
+        <v>2.103027060629381</v>
+      </c>
+      <c r="D41">
+        <v>6.808917060629382</v>
+      </c>
+      <c r="E41">
+        <v>5.07289</v>
+      </c>
+      <c r="F41">
+        <v>5.32389</v>
+      </c>
+      <c r="G41">
+        <v>0.618</v>
+      </c>
+      <c r="H41">
+        <v>13.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.034</v>
+      </c>
+      <c r="K41">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L41">
+        <v>0.025</v>
+      </c>
+      <c r="M41">
+        <v>1.271344932</v>
+      </c>
+      <c r="N41">
+        <v>-1.246344932</v>
+      </c>
+      <c r="O41">
+        <v>-0.311586233</v>
+      </c>
+      <c r="P41">
+        <v>-0.9347586990000001</v>
+      </c>
+      <c r="Q41">
+        <v>-0.9257586990000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.176356062574158</v>
+      </c>
+      <c r="T41">
+        <v>1.229994171196146</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.004916053733873695</v>
+      </c>
+      <c r="W41">
+        <v>0.237626046368351</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.01966421493549475</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2022513562538933</v>
+      </c>
+      <c r="C42">
+        <v>1.883202768026596</v>
+      </c>
+      <c r="D42">
+        <v>6.725602768026596</v>
+      </c>
+      <c r="E42">
+        <v>5.2094</v>
+      </c>
+      <c r="F42">
+        <v>5.4604</v>
+      </c>
+      <c r="G42">
+        <v>0.618</v>
+      </c>
+      <c r="H42">
+        <v>13.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.034</v>
+      </c>
+      <c r="K42">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L42">
+        <v>0.025</v>
+      </c>
+      <c r="M42">
+        <v>1.30394352</v>
+      </c>
+      <c r="N42">
+        <v>-1.27894352</v>
+      </c>
+      <c r="O42">
+        <v>-0.31973588</v>
+      </c>
+      <c r="P42">
+        <v>-0.95920764</v>
+      </c>
+      <c r="Q42">
+        <v>-0.95020764</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1786486636170606</v>
+      </c>
+      <c r="T42">
+        <v>1.250494074049415</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.004793152390526854</v>
+      </c>
+      <c r="W42">
+        <v>0.2376553952091422</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.01917260956210731</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2042513562538933</v>
+      </c>
+      <c r="C43">
+        <v>1.665392705938185</v>
+      </c>
+      <c r="D43">
+        <v>6.644302705938185</v>
+      </c>
+      <c r="E43">
+        <v>5.34591</v>
+      </c>
+      <c r="F43">
+        <v>5.59691</v>
+      </c>
+      <c r="G43">
+        <v>0.618</v>
+      </c>
+      <c r="H43">
+        <v>13.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.034</v>
+      </c>
+      <c r="K43">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L43">
+        <v>0.025</v>
+      </c>
+      <c r="M43">
+        <v>1.336542108</v>
+      </c>
+      <c r="N43">
+        <v>-1.311542108</v>
+      </c>
+      <c r="O43">
+        <v>-0.3278855270000001</v>
+      </c>
+      <c r="P43">
+        <v>-0.9836565810000002</v>
+      </c>
+      <c r="Q43">
+        <v>-0.9746565810000002</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1810189799495532</v>
+      </c>
+      <c r="T43">
+        <v>1.271688888863812</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.004676246234660344</v>
+      </c>
+      <c r="W43">
+        <v>0.2376833123991631</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.01870498493864126</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2062513562538933</v>
+      </c>
+      <c r="C44">
+        <v>1.44952470186369</v>
+      </c>
+      <c r="D44">
+        <v>6.56494470186369</v>
+      </c>
+      <c r="E44">
+        <v>5.482419999999999</v>
+      </c>
+      <c r="F44">
+        <v>5.73342</v>
+      </c>
+      <c r="G44">
+        <v>0.618</v>
+      </c>
+      <c r="H44">
+        <v>13.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.034</v>
+      </c>
+      <c r="K44">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L44">
+        <v>0.025</v>
+      </c>
+      <c r="M44">
+        <v>1.369140696</v>
+      </c>
+      <c r="N44">
+        <v>-1.344140696</v>
+      </c>
+      <c r="O44">
+        <v>-0.336035174</v>
+      </c>
+      <c r="P44">
+        <v>-1.008105522</v>
+      </c>
+      <c r="Q44">
+        <v>-0.9991055220000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1834710313279938</v>
+      </c>
+      <c r="T44">
+        <v>1.293614559361464</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.004564907038597003</v>
+      </c>
+      <c r="W44">
+        <v>0.237709900199183</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.01825962815438797</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2082513562538933</v>
+      </c>
+      <c r="C45">
+        <v>1.235529990652205</v>
+      </c>
+      <c r="D45">
+        <v>6.487459990652205</v>
+      </c>
+      <c r="E45">
+        <v>5.61893</v>
+      </c>
+      <c r="F45">
+        <v>5.86993</v>
+      </c>
+      <c r="G45">
+        <v>0.618</v>
+      </c>
+      <c r="H45">
+        <v>13.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.034</v>
+      </c>
+      <c r="K45">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L45">
+        <v>0.025</v>
+      </c>
+      <c r="M45">
+        <v>1.401739284</v>
+      </c>
+      <c r="N45">
+        <v>-1.376739284</v>
+      </c>
+      <c r="O45">
+        <v>-0.344184821</v>
+      </c>
+      <c r="P45">
+        <v>-1.032554463</v>
+      </c>
+      <c r="Q45">
+        <v>-1.023554463</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1860091195969059</v>
+      </c>
+      <c r="T45">
+        <v>1.316309551630964</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.004458746409792422</v>
+      </c>
+      <c r="W45">
+        <v>0.2377352513573416</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.01783498563916963</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2102513562538933</v>
+      </c>
+      <c r="C46">
+        <v>1.023343015766742</v>
+      </c>
+      <c r="D46">
+        <v>6.411783015766741</v>
+      </c>
+      <c r="E46">
+        <v>5.755439999999999</v>
+      </c>
+      <c r="F46">
+        <v>6.00644</v>
+      </c>
+      <c r="G46">
+        <v>0.618</v>
+      </c>
+      <c r="H46">
+        <v>13.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.034</v>
+      </c>
+      <c r="K46">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L46">
+        <v>0.025</v>
+      </c>
+      <c r="M46">
+        <v>1.434337872</v>
+      </c>
+      <c r="N46">
+        <v>-1.409337872</v>
+      </c>
+      <c r="O46">
+        <v>-0.352334468</v>
+      </c>
+      <c r="P46">
+        <v>-1.057003404</v>
+      </c>
+      <c r="Q46">
+        <v>-1.048003404</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1886378538754221</v>
+      </c>
+      <c r="T46">
+        <v>1.339815079338659</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.004357411264115322</v>
+      </c>
+      <c r="W46">
+        <v>0.2377594501901293</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.01742964505646127</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2122513562538933</v>
+      </c>
+      <c r="C47">
+        <v>0.8129012442978416</v>
+      </c>
+      <c r="D47">
+        <v>6.337851244297841</v>
+      </c>
+      <c r="E47">
+        <v>5.89195</v>
+      </c>
+      <c r="F47">
+        <v>6.14295</v>
+      </c>
+      <c r="G47">
+        <v>0.618</v>
+      </c>
+      <c r="H47">
+        <v>13.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.034</v>
+      </c>
+      <c r="K47">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L47">
+        <v>0.025</v>
+      </c>
+      <c r="M47">
+        <v>1.46693646</v>
+      </c>
+      <c r="N47">
+        <v>-1.44193646</v>
+      </c>
+      <c r="O47">
+        <v>-0.360484115</v>
+      </c>
+      <c r="P47">
+        <v>-1.081452345</v>
+      </c>
+      <c r="Q47">
+        <v>-1.072452345</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1913621784913389</v>
+      </c>
+      <c r="T47">
+        <v>1.364175353508453</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.004260579902690536</v>
+      </c>
+      <c r="W47">
+        <v>0.2377825735192375</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.01704231961076208</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2142513562538933</v>
+      </c>
+      <c r="C48">
+        <v>0.6041449946293431</v>
+      </c>
+      <c r="D48">
+        <v>6.265604994629343</v>
+      </c>
+      <c r="E48">
+        <v>6.02846</v>
+      </c>
+      <c r="F48">
+        <v>6.27946</v>
+      </c>
+      <c r="G48">
+        <v>0.618</v>
+      </c>
+      <c r="H48">
+        <v>13.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.034</v>
+      </c>
+      <c r="K48">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L48">
+        <v>0.025</v>
+      </c>
+      <c r="M48">
+        <v>1.499535048</v>
+      </c>
+      <c r="N48">
+        <v>-1.474535048</v>
+      </c>
+      <c r="O48">
+        <v>-0.368633762</v>
+      </c>
+      <c r="P48">
+        <v>-1.105901286</v>
+      </c>
+      <c r="Q48">
+        <v>-1.096901286</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1941874040189563</v>
+      </c>
+      <c r="T48">
+        <v>1.389437860054906</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.004167958600458134</v>
+      </c>
+      <c r="W48">
+        <v>0.2378046914862106</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.01667183440183251</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2162513562538933</v>
+      </c>
+      <c r="C49">
+        <v>0.3970172757580954</v>
+      </c>
+      <c r="D49">
+        <v>6.194987275758096</v>
+      </c>
+      <c r="E49">
+        <v>6.16497</v>
+      </c>
+      <c r="F49">
+        <v>6.415970000000001</v>
+      </c>
+      <c r="G49">
+        <v>0.618</v>
+      </c>
+      <c r="H49">
+        <v>13.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.034</v>
+      </c>
+      <c r="K49">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L49">
+        <v>0.025</v>
+      </c>
+      <c r="M49">
+        <v>1.532133636</v>
+      </c>
+      <c r="N49">
+        <v>-1.507133636</v>
+      </c>
+      <c r="O49">
+        <v>-0.3767834090000001</v>
+      </c>
+      <c r="P49">
+        <v>-1.130350227</v>
+      </c>
+      <c r="Q49">
+        <v>-1.121350227</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1971192418306347</v>
+      </c>
+      <c r="T49">
+        <v>1.415653668735187</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.004079278630235619</v>
+      </c>
+      <c r="W49">
+        <v>0.2378258682630998</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.01631711452094242</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2182513562538933</v>
+      </c>
+      <c r="C50">
+        <v>0.1914636373584715</v>
+      </c>
+      <c r="D50">
+        <v>6.125943637358471</v>
+      </c>
+      <c r="E50">
+        <v>6.30148</v>
+      </c>
+      <c r="F50">
+        <v>6.55248</v>
+      </c>
+      <c r="G50">
+        <v>0.618</v>
+      </c>
+      <c r="H50">
+        <v>13.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.034</v>
+      </c>
+      <c r="K50">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L50">
+        <v>0.025</v>
+      </c>
+      <c r="M50">
+        <v>1.564732224</v>
+      </c>
+      <c r="N50">
+        <v>-1.539732224</v>
+      </c>
+      <c r="O50">
+        <v>-0.3849330560000001</v>
+      </c>
+      <c r="P50">
+        <v>-1.154799168</v>
+      </c>
+      <c r="Q50">
+        <v>-1.145799168</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.20016384263507</v>
+      </c>
+      <c r="T50">
+        <v>1.442877777749326</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.003994293658772378</v>
+      </c>
+      <c r="W50">
+        <v>0.2378461626742852</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.01597717463508941</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2202513562538933</v>
+      </c>
+      <c r="C51">
+        <v>-0.01256797023741552</v>
+      </c>
+      <c r="D51">
+        <v>6.058422029762584</v>
+      </c>
+      <c r="E51">
+        <v>6.437989999999999</v>
+      </c>
+      <c r="F51">
+        <v>6.68899</v>
+      </c>
+      <c r="G51">
+        <v>0.618</v>
+      </c>
+      <c r="H51">
+        <v>13.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.034</v>
+      </c>
+      <c r="K51">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L51">
+        <v>0.025</v>
+      </c>
+      <c r="M51">
+        <v>1.597330812</v>
+      </c>
+      <c r="N51">
+        <v>-1.572330812</v>
+      </c>
+      <c r="O51">
+        <v>-0.393082703</v>
+      </c>
+      <c r="P51">
+        <v>-1.179248109</v>
+      </c>
+      <c r="Q51">
+        <v>-1.170248109</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2033278395494831</v>
+      </c>
+      <c r="T51">
+        <v>1.471169498881665</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.003912777461654574</v>
+      </c>
+      <c r="W51">
+        <v>0.2378656287421569</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.01565110984661822</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2222513562538933</v>
+      </c>
+      <c r="C52">
+        <v>-0.2151273269004195</v>
+      </c>
+      <c r="D52">
+        <v>5.99237267309958</v>
+      </c>
+      <c r="E52">
+        <v>6.5745</v>
+      </c>
+      <c r="F52">
+        <v>6.8255</v>
+      </c>
+      <c r="G52">
+        <v>0.618</v>
+      </c>
+      <c r="H52">
+        <v>13.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.034</v>
+      </c>
+      <c r="K52">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L52">
+        <v>0.025</v>
+      </c>
+      <c r="M52">
+        <v>1.6299294</v>
+      </c>
+      <c r="N52">
+        <v>-1.6049294</v>
+      </c>
+      <c r="O52">
+        <v>-0.40123235</v>
+      </c>
+      <c r="P52">
+        <v>-1.20369705</v>
+      </c>
+      <c r="Q52">
+        <v>-1.19469705</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2066183963404728</v>
+      </c>
+      <c r="T52">
+        <v>1.500592888859299</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.003834521912421483</v>
+      </c>
+      <c r="W52">
+        <v>0.2378843161673138</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.01533808764968592</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2242513562538933</v>
+      </c>
+      <c r="C53">
+        <v>-0.4162620650974898</v>
+      </c>
+      <c r="D53">
+        <v>5.92774793490251</v>
+      </c>
+      <c r="E53">
+        <v>6.71101</v>
+      </c>
+      <c r="F53">
+        <v>6.96201</v>
+      </c>
+      <c r="G53">
+        <v>0.618</v>
+      </c>
+      <c r="H53">
+        <v>13.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.034</v>
+      </c>
+      <c r="K53">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L53">
+        <v>0.025</v>
+      </c>
+      <c r="M53">
+        <v>1.662527988</v>
+      </c>
+      <c r="N53">
+        <v>-1.637527988</v>
+      </c>
+      <c r="O53">
+        <v>-0.4093819970000001</v>
+      </c>
+      <c r="P53">
+        <v>-1.228145991</v>
+      </c>
+      <c r="Q53">
+        <v>-1.219145991</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.210043261571911</v>
+      </c>
+      <c r="T53">
+        <v>1.531217233529897</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.003759335208256356</v>
+      </c>
+      <c r="W53">
+        <v>0.2379022707522684</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.01503734083302533</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2262513562538933</v>
+      </c>
+      <c r="C54">
+        <v>-0.6160177844495918</v>
+      </c>
+      <c r="D54">
+        <v>5.864502215550408</v>
+      </c>
+      <c r="E54">
+        <v>6.847519999999999</v>
+      </c>
+      <c r="F54">
+        <v>7.09852</v>
+      </c>
+      <c r="G54">
+        <v>0.618</v>
+      </c>
+      <c r="H54">
+        <v>13.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.034</v>
+      </c>
+      <c r="K54">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L54">
+        <v>0.025</v>
+      </c>
+      <c r="M54">
+        <v>1.695126576</v>
+      </c>
+      <c r="N54">
+        <v>-1.670126576</v>
+      </c>
+      <c r="O54">
+        <v>-0.417531644</v>
+      </c>
+      <c r="P54">
+        <v>-1.252594932</v>
+      </c>
+      <c r="Q54">
+        <v>-1.243594932</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2136108295213258</v>
+      </c>
+      <c r="T54">
+        <v>1.56311759256177</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.003687040300405272</v>
+      </c>
+      <c r="W54">
+        <v>0.2379195347762632</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.01474816120162104</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2282513562538933</v>
+      </c>
+      <c r="C55">
+        <v>-0.8144381590334628</v>
+      </c>
+      <c r="D55">
+        <v>5.802591840966537</v>
+      </c>
+      <c r="E55">
+        <v>6.98403</v>
+      </c>
+      <c r="F55">
+        <v>7.23503</v>
+      </c>
+      <c r="G55">
+        <v>0.618</v>
+      </c>
+      <c r="H55">
+        <v>13.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.034</v>
+      </c>
+      <c r="K55">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L55">
+        <v>0.025</v>
+      </c>
+      <c r="M55">
+        <v>1.727725164</v>
+      </c>
+      <c r="N55">
+        <v>-1.702725164</v>
+      </c>
+      <c r="O55">
+        <v>-0.4256812910000001</v>
+      </c>
+      <c r="P55">
+        <v>-1.277043873</v>
+      </c>
+      <c r="Q55">
+        <v>-1.268043873</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2173302088728434</v>
+      </c>
+      <c r="T55">
+        <v>1.596375413680105</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.003617473502284418</v>
+      </c>
+      <c r="W55">
+        <v>0.2379361473276545</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.01446989400913756</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2302513562538933</v>
+      </c>
+      <c r="C56">
+        <v>-1.011565037957752</v>
+      </c>
+      <c r="D56">
+        <v>5.741974962042248</v>
+      </c>
+      <c r="E56">
+        <v>7.12054</v>
+      </c>
+      <c r="F56">
+        <v>7.37154</v>
+      </c>
+      <c r="G56">
+        <v>0.618</v>
+      </c>
+      <c r="H56">
+        <v>13.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.034</v>
+      </c>
+      <c r="K56">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L56">
+        <v>0.025</v>
+      </c>
+      <c r="M56">
+        <v>1.760323752</v>
+      </c>
+      <c r="N56">
+        <v>-1.735323752</v>
+      </c>
+      <c r="O56">
+        <v>-0.4338309380000001</v>
+      </c>
+      <c r="P56">
+        <v>-1.301492814</v>
+      </c>
+      <c r="Q56">
+        <v>-1.292492814</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2212113003700791</v>
+      </c>
+      <c r="T56">
+        <v>1.631079227020977</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.003550483252242114</v>
+      </c>
+      <c r="W56">
+        <v>0.2379521445993646</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.01420193300896844</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2322513562538933</v>
+      </c>
+      <c r="C57">
+        <v>-1.207438539700343</v>
+      </c>
+      <c r="D57">
+        <v>5.682611460299658</v>
+      </c>
+      <c r="E57">
+        <v>7.25705</v>
+      </c>
+      <c r="F57">
+        <v>7.508050000000001</v>
+      </c>
+      <c r="G57">
+        <v>0.618</v>
+      </c>
+      <c r="H57">
+        <v>13.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.034</v>
+      </c>
+      <c r="K57">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L57">
+        <v>0.025</v>
+      </c>
+      <c r="M57">
+        <v>1.79292234</v>
+      </c>
+      <c r="N57">
+        <v>-1.76792234</v>
+      </c>
+      <c r="O57">
+        <v>-0.4419805850000001</v>
+      </c>
+      <c r="P57">
+        <v>-1.325941755</v>
+      </c>
+      <c r="Q57">
+        <v>-1.316941755</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2252648848227475</v>
+      </c>
+      <c r="T57">
+        <v>1.667325432065887</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.003485929011292257</v>
+      </c>
+      <c r="W57">
+        <v>0.2379675601521034</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.01394371604516897</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2342513562538933</v>
+      </c>
+      <c r="C58">
+        <v>-1.402097140653695</v>
+      </c>
+      <c r="D58">
+        <v>5.624462859346305</v>
+      </c>
+      <c r="E58">
+        <v>7.39356</v>
+      </c>
+      <c r="F58">
+        <v>7.64456</v>
+      </c>
+      <c r="G58">
+        <v>0.618</v>
+      </c>
+      <c r="H58">
+        <v>13.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.034</v>
+      </c>
+      <c r="K58">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L58">
+        <v>0.025</v>
+      </c>
+      <c r="M58">
+        <v>1.825520928</v>
+      </c>
+      <c r="N58">
+        <v>-1.800520928</v>
+      </c>
+      <c r="O58">
+        <v>-0.4501302320000001</v>
+      </c>
+      <c r="P58">
+        <v>-1.350390696</v>
+      </c>
+      <c r="Q58">
+        <v>-1.341390696</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2295027231141736</v>
+      </c>
+      <c r="T58">
+        <v>1.705219191885567</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.003423680278947752</v>
+      </c>
+      <c r="W58">
+        <v>0.2379824251493873</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.01369472111579095</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2362513562538933</v>
+      </c>
+      <c r="C59">
+        <v>-1.595577758288897</v>
+      </c>
+      <c r="D59">
+        <v>5.567492241711103</v>
+      </c>
+      <c r="E59">
+        <v>7.53007</v>
+      </c>
+      <c r="F59">
+        <v>7.781070000000001</v>
+      </c>
+      <c r="G59">
+        <v>0.618</v>
+      </c>
+      <c r="H59">
+        <v>13.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.034</v>
+      </c>
+      <c r="K59">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L59">
+        <v>0.025</v>
+      </c>
+      <c r="M59">
+        <v>1.858119516</v>
+      </c>
+      <c r="N59">
+        <v>-1.833119516</v>
+      </c>
+      <c r="O59">
+        <v>-0.4582798790000001</v>
+      </c>
+      <c r="P59">
+        <v>-1.374839637</v>
+      </c>
+      <c r="Q59">
+        <v>-1.365839637</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2339376701633405</v>
+      </c>
+      <c r="T59">
+        <v>1.744875452161975</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.003363615712650423</v>
+      </c>
+      <c r="W59">
+        <v>0.2379967685678191</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.0134544628506017</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2382513562538933</v>
+      </c>
+      <c r="C60">
+        <v>-1.787915829316138</v>
+      </c>
+      <c r="D60">
+        <v>5.51166417068386</v>
+      </c>
+      <c r="E60">
+        <v>7.666579999999999</v>
+      </c>
+      <c r="F60">
+        <v>7.917579999999999</v>
+      </c>
+      <c r="G60">
+        <v>0.618</v>
+      </c>
+      <c r="H60">
+        <v>13.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.034</v>
+      </c>
+      <c r="K60">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L60">
+        <v>0.025</v>
+      </c>
+      <c r="M60">
+        <v>1.890718104</v>
+      </c>
+      <c r="N60">
+        <v>-1.865718104</v>
+      </c>
+      <c r="O60">
+        <v>-0.466429526</v>
+      </c>
+      <c r="P60">
+        <v>-1.399288578</v>
+      </c>
+      <c r="Q60">
+        <v>-1.390288578</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2385838051672295</v>
+      </c>
+      <c r="T60">
+        <v>1.786420105784879</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.003305622338294382</v>
+      </c>
+      <c r="W60">
+        <v>0.2380106173856153</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.01322248935317749</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2402513562538933</v>
+      </c>
+      <c r="C61">
+        <v>-1.979145383189355</v>
+      </c>
+      <c r="D61">
+        <v>5.456944616810643</v>
+      </c>
+      <c r="E61">
+        <v>7.803089999999998</v>
+      </c>
+      <c r="F61">
+        <v>8.054089999999999</v>
+      </c>
+      <c r="G61">
+        <v>0.618</v>
+      </c>
+      <c r="H61">
+        <v>13.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.034</v>
+      </c>
+      <c r="K61">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L61">
+        <v>0.025</v>
+      </c>
+      <c r="M61">
+        <v>1.923316692</v>
+      </c>
+      <c r="N61">
+        <v>-1.898316692</v>
+      </c>
+      <c r="O61">
+        <v>-0.474579173</v>
+      </c>
+      <c r="P61">
+        <v>-1.423737519</v>
+      </c>
+      <c r="Q61">
+        <v>-1.414737519</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2434565809030156</v>
+      </c>
+      <c r="T61">
+        <v>1.829991327877193</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.003249594841035155</v>
+      </c>
+      <c r="W61">
+        <v>0.2380239967519608</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.01299837936414061</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2422513562538933</v>
+      </c>
+      <c r="C62">
+        <v>-2.169299111275405</v>
+      </c>
+      <c r="D62">
+        <v>5.403300888724595</v>
+      </c>
+      <c r="E62">
+        <v>7.9396</v>
+      </c>
+      <c r="F62">
+        <v>8.1906</v>
+      </c>
+      <c r="G62">
+        <v>0.618</v>
+      </c>
+      <c r="H62">
+        <v>13.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.034</v>
+      </c>
+      <c r="K62">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L62">
+        <v>0.025</v>
+      </c>
+      <c r="M62">
+        <v>1.95591528</v>
+      </c>
+      <c r="N62">
+        <v>-1.93091528</v>
+      </c>
+      <c r="O62">
+        <v>-0.4827288200000001</v>
+      </c>
+      <c r="P62">
+        <v>-1.44818646</v>
+      </c>
+      <c r="Q62">
+        <v>-1.43918646</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2485729954255909</v>
+      </c>
+      <c r="T62">
+        <v>1.875741111074123</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.003195434927017902</v>
+      </c>
+      <c r="W62">
+        <v>0.2380369301394281</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.01278173970807162</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2442513562538932</v>
+      </c>
+      <c r="C63">
+        <v>-2.358408431983193</v>
+      </c>
+      <c r="D63">
+        <v>5.350701568016806</v>
+      </c>
+      <c r="E63">
+        <v>8.07611</v>
+      </c>
+      <c r="F63">
+        <v>8.327109999999999</v>
+      </c>
+      <c r="G63">
+        <v>0.618</v>
+      </c>
+      <c r="H63">
+        <v>13.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.034</v>
+      </c>
+      <c r="K63">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L63">
+        <v>0.025</v>
+      </c>
+      <c r="M63">
+        <v>1.988513868</v>
+      </c>
+      <c r="N63">
+        <v>-1.963513868</v>
+      </c>
+      <c r="O63">
+        <v>-0.490878467</v>
+      </c>
+      <c r="P63">
+        <v>-1.472635401</v>
+      </c>
+      <c r="Q63">
+        <v>-1.463635401</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2539517901800933</v>
+      </c>
+      <c r="T63">
+        <v>1.923837036999101</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.003143050747886462</v>
+      </c>
+      <c r="W63">
+        <v>0.2380494394814047</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.01257220299154582</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2462513562538933</v>
+      </c>
+      <c r="C64">
+        <v>-2.546503552125465</v>
+      </c>
+      <c r="D64">
+        <v>5.299116447874535</v>
+      </c>
+      <c r="E64">
+        <v>8.212620000000001</v>
+      </c>
+      <c r="F64">
+        <v>8.463620000000001</v>
+      </c>
+      <c r="G64">
+        <v>0.618</v>
+      </c>
+      <c r="H64">
+        <v>13.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.034</v>
+      </c>
+      <c r="K64">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L64">
+        <v>0.025</v>
+      </c>
+      <c r="M64">
+        <v>2.021112456</v>
+      </c>
+      <c r="N64">
+        <v>-1.996112456000001</v>
+      </c>
+      <c r="O64">
+        <v>-0.4990281140000001</v>
+      </c>
+      <c r="P64">
+        <v>-1.497084342</v>
+      </c>
+      <c r="Q64">
+        <v>-1.488084342000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.259613679395359</v>
+      </c>
+      <c r="T64">
+        <v>1.974464327446446</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.003092356380985066</v>
+      </c>
+      <c r="W64">
+        <v>0.2380615452962208</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.01236942552394027</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2482513562538933</v>
+      </c>
+      <c r="C65">
+        <v>-2.733613524764945</v>
+      </c>
+      <c r="D65">
+        <v>5.248516475235054</v>
+      </c>
+      <c r="E65">
+        <v>8.349130000000001</v>
+      </c>
+      <c r="F65">
+        <v>8.60013</v>
+      </c>
+      <c r="G65">
+        <v>0.618</v>
+      </c>
+      <c r="H65">
+        <v>13.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.034</v>
+      </c>
+      <c r="K65">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L65">
+        <v>0.025</v>
+      </c>
+      <c r="M65">
+        <v>2.053711044</v>
+      </c>
+      <c r="N65">
+        <v>-2.028711044</v>
+      </c>
+      <c r="O65">
+        <v>-0.507177761</v>
+      </c>
+      <c r="P65">
+        <v>-1.521533283</v>
+      </c>
+      <c r="Q65">
+        <v>-1.512533283</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2655816166763145</v>
+      </c>
+      <c r="T65">
+        <v>2.027828228188241</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.003043271359064669</v>
+      </c>
+      <c r="W65">
+        <v>0.2380732667994554</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.01217308543625861</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2502513562538933</v>
+      </c>
+      <c r="C66">
+        <v>-2.91976630377775</v>
+      </c>
+      <c r="D66">
+        <v>5.198873696222249</v>
+      </c>
+      <c r="E66">
+        <v>8.48564</v>
+      </c>
+      <c r="F66">
+        <v>8.73664</v>
+      </c>
+      <c r="G66">
+        <v>0.618</v>
+      </c>
+      <c r="H66">
+        <v>13.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.034</v>
+      </c>
+      <c r="K66">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L66">
+        <v>0.025</v>
+      </c>
+      <c r="M66">
+        <v>2.086309632</v>
+      </c>
+      <c r="N66">
+        <v>-2.061309632</v>
+      </c>
+      <c r="O66">
+        <v>-0.515327408</v>
+      </c>
+      <c r="P66">
+        <v>-1.545982224</v>
+      </c>
+      <c r="Q66">
+        <v>-1.536982224</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2718811060284344</v>
+      </c>
+      <c r="T66">
+        <v>2.084156790082359</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.002995720244079284</v>
+      </c>
+      <c r="W66">
+        <v>0.2380846220057139</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.01198288097631706</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2522513562538933</v>
+      </c>
+      <c r="C67">
+        <v>-3.104988795349259</v>
+      </c>
+      <c r="D67">
+        <v>5.150161204650741</v>
+      </c>
+      <c r="E67">
+        <v>8.622150000000001</v>
+      </c>
+      <c r="F67">
+        <v>8.873150000000001</v>
+      </c>
+      <c r="G67">
+        <v>0.618</v>
+      </c>
+      <c r="H67">
+        <v>13.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.034</v>
+      </c>
+      <c r="K67">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L67">
+        <v>0.025</v>
+      </c>
+      <c r="M67">
+        <v>2.11890822</v>
+      </c>
+      <c r="N67">
+        <v>-2.09390822</v>
+      </c>
+      <c r="O67">
+        <v>-0.5234770550000001</v>
+      </c>
+      <c r="P67">
+        <v>-1.570431165</v>
+      </c>
+      <c r="Q67">
+        <v>-1.561431165</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2785405662006754</v>
+      </c>
+      <c r="T67">
+        <v>2.143704126941855</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.002949632240324217</v>
+      </c>
+      <c r="W67">
+        <v>0.2380956278210106</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.01179852896129685</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2542513562538933</v>
+      </c>
+      <c r="C68">
+        <v>-3.289306906601821</v>
+      </c>
+      <c r="D68">
+        <v>5.102353093398179</v>
+      </c>
+      <c r="E68">
+        <v>8.758660000000001</v>
+      </c>
+      <c r="F68">
+        <v>9.00966</v>
+      </c>
+      <c r="G68">
+        <v>0.618</v>
+      </c>
+      <c r="H68">
+        <v>13.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.034</v>
+      </c>
+      <c r="K68">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L68">
+        <v>0.025</v>
+      </c>
+      <c r="M68">
+        <v>2.151506808</v>
+      </c>
+      <c r="N68">
+        <v>-2.126506808</v>
+      </c>
+      <c r="O68">
+        <v>-0.5316267020000001</v>
+      </c>
+      <c r="P68">
+        <v>-1.594880106</v>
+      </c>
+      <c r="Q68">
+        <v>-1.585880106</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2855917593242247</v>
+      </c>
+      <c r="T68">
+        <v>2.206754248322498</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.002904940842743548</v>
+      </c>
+      <c r="W68">
+        <v>0.2381063001267529</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.01161976337097415</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2562513562538933</v>
+      </c>
+      <c r="C69">
+        <v>-3.472745591538976</v>
+      </c>
+      <c r="D69">
+        <v>5.055424408461024</v>
+      </c>
+      <c r="E69">
+        <v>8.89517</v>
+      </c>
+      <c r="F69">
+        <v>9.14617</v>
+      </c>
+      <c r="G69">
+        <v>0.618</v>
+      </c>
+      <c r="H69">
+        <v>13.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.034</v>
+      </c>
+      <c r="K69">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L69">
+        <v>0.025</v>
+      </c>
+      <c r="M69">
+        <v>2.184105396</v>
+      </c>
+      <c r="N69">
+        <v>-2.159105396</v>
+      </c>
+      <c r="O69">
+        <v>-0.539776349</v>
+      </c>
+      <c r="P69">
+        <v>-1.619329047</v>
+      </c>
+      <c r="Q69">
+        <v>-1.610329047</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2930702974855648</v>
+      </c>
+      <c r="T69">
+        <v>2.273625589180756</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.00286158351673245</v>
+      </c>
+      <c r="W69">
+        <v>0.2381166538562043</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.01144633406692974</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2582513562538933</v>
+      </c>
+      <c r="C70">
+        <v>-3.655328894477348</v>
+      </c>
+      <c r="D70">
+        <v>5.009351105522653</v>
+      </c>
+      <c r="E70">
+        <v>9.031680000000001</v>
+      </c>
+      <c r="F70">
+        <v>9.282680000000001</v>
+      </c>
+      <c r="G70">
+        <v>0.618</v>
+      </c>
+      <c r="H70">
+        <v>13.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.034</v>
+      </c>
+      <c r="K70">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L70">
+        <v>0.025</v>
+      </c>
+      <c r="M70">
+        <v>2.216703984</v>
+      </c>
+      <c r="N70">
+        <v>-2.191703984000001</v>
+      </c>
+      <c r="O70">
+        <v>-0.5479259960000001</v>
+      </c>
+      <c r="P70">
+        <v>-1.643777988000001</v>
+      </c>
+      <c r="Q70">
+        <v>-1.634777988000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3010162442819888</v>
+      </c>
+      <c r="T70">
+        <v>2.344676388842654</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.002819501406192266</v>
+      </c>
+      <c r="W70">
+        <v>0.2381267030642013</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.01127800562476899</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2602513562538933</v>
+      </c>
+      <c r="C71">
+        <v>-3.837079991125042</v>
+      </c>
+      <c r="D71">
+        <v>4.964110008874958</v>
+      </c>
+      <c r="E71">
+        <v>9.168190000000001</v>
+      </c>
+      <c r="F71">
+        <v>9.41919</v>
+      </c>
+      <c r="G71">
+        <v>0.618</v>
+      </c>
+      <c r="H71">
+        <v>13.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.034</v>
+      </c>
+      <c r="K71">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L71">
+        <v>0.025</v>
+      </c>
+      <c r="M71">
+        <v>2.249302572</v>
+      </c>
+      <c r="N71">
+        <v>-2.224302572</v>
+      </c>
+      <c r="O71">
+        <v>-0.5560756430000001</v>
+      </c>
+      <c r="P71">
+        <v>-1.668226929</v>
+      </c>
+      <c r="Q71">
+        <v>-1.659226929</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3094748328072142</v>
+      </c>
+      <c r="T71">
+        <v>2.420311111063385</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.002778639066972089</v>
+      </c>
+      <c r="W71">
+        <v>0.2381364609908071</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.01111455626788826</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2622513562538933</v>
+      </c>
+      <c r="C72">
+        <v>-4.018021227454033</v>
+      </c>
+      <c r="D72">
+        <v>4.919678772545969</v>
+      </c>
+      <c r="E72">
+        <v>9.304700000000002</v>
+      </c>
+      <c r="F72">
+        <v>9.555700000000002</v>
+      </c>
+      <c r="G72">
+        <v>0.618</v>
+      </c>
+      <c r="H72">
+        <v>13.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.034</v>
+      </c>
+      <c r="K72">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L72">
+        <v>0.025</v>
+      </c>
+      <c r="M72">
+        <v>2.28190116</v>
+      </c>
+      <c r="N72">
+        <v>-2.25690116</v>
+      </c>
+      <c r="O72">
+        <v>-0.5642252900000001</v>
+      </c>
+      <c r="P72">
+        <v>-1.69267587</v>
+      </c>
+      <c r="Q72">
+        <v>-1.683675870000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3184973272341213</v>
+      </c>
+      <c r="T72">
+        <v>2.500988148098831</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.002738944223158202</v>
+      </c>
+      <c r="W72">
+        <v>0.2381459401195098</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.01095577689263272</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2642513562538933</v>
+      </c>
+      <c r="C73">
+        <v>-4.198174156503485</v>
+      </c>
+      <c r="D73">
+        <v>4.876035843496514</v>
+      </c>
+      <c r="E73">
+        <v>9.44121</v>
+      </c>
+      <c r="F73">
+        <v>9.692209999999999</v>
+      </c>
+      <c r="G73">
+        <v>0.618</v>
+      </c>
+      <c r="H73">
+        <v>13.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.034</v>
+      </c>
+      <c r="K73">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L73">
+        <v>0.025</v>
+      </c>
+      <c r="M73">
+        <v>2.314499748</v>
+      </c>
+      <c r="N73">
+        <v>-2.289499748</v>
+      </c>
+      <c r="O73">
+        <v>-0.572374937</v>
+      </c>
+      <c r="P73">
+        <v>-1.717124811</v>
+      </c>
+      <c r="Q73">
+        <v>-1.708124811</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3281420626559876</v>
+      </c>
+      <c r="T73">
+        <v>2.587229118722929</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.002700367543958791</v>
+      </c>
+      <c r="W73">
+        <v>0.2381551522305027</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.0108014701758351</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2662513562538933</v>
+      </c>
+      <c r="C74">
+        <v>-4.377559573241415</v>
+      </c>
+      <c r="D74">
+        <v>4.833160426758583</v>
+      </c>
+      <c r="E74">
+        <v>9.577719999999999</v>
+      </c>
+      <c r="F74">
+        <v>9.828719999999999</v>
+      </c>
+      <c r="G74">
+        <v>0.618</v>
+      </c>
+      <c r="H74">
+        <v>13.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.034</v>
+      </c>
+      <c r="K74">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L74">
+        <v>0.025</v>
+      </c>
+      <c r="M74">
+        <v>2.347098336</v>
+      </c>
+      <c r="N74">
+        <v>-2.322098336</v>
+      </c>
+      <c r="O74">
+        <v>-0.580524584</v>
+      </c>
+      <c r="P74">
+        <v>-1.741573752</v>
+      </c>
+      <c r="Q74">
+        <v>-1.732573752</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3384757077508442</v>
+      </c>
+      <c r="T74">
+        <v>2.679630158677319</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.002662862439181586</v>
+      </c>
+      <c r="W74">
+        <v>0.2381641084495235</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.01065144975672627</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2682513562538932</v>
+      </c>
+      <c r="C75">
+        <v>-4.556197547603096</v>
+      </c>
+      <c r="D75">
+        <v>4.791032452396903</v>
+      </c>
+      <c r="E75">
+        <v>9.714230000000001</v>
+      </c>
+      <c r="F75">
+        <v>9.96523</v>
+      </c>
+      <c r="G75">
+        <v>0.618</v>
+      </c>
+      <c r="H75">
+        <v>13.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.034</v>
+      </c>
+      <c r="K75">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L75">
+        <v>0.025</v>
+      </c>
+      <c r="M75">
+        <v>2.379696924</v>
+      </c>
+      <c r="N75">
+        <v>-2.354696924</v>
+      </c>
+      <c r="O75">
+        <v>-0.588674231</v>
+      </c>
+      <c r="P75">
+        <v>-1.766022693</v>
+      </c>
+      <c r="Q75">
+        <v>-1.757022693</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3495748080379125</v>
+      </c>
+      <c r="T75">
+        <v>2.778875720109812</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.002626384871521564</v>
+      </c>
+      <c r="W75">
+        <v>0.2381728192926807</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.01050553948608624</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2702513562538932</v>
+      </c>
+      <c r="C76">
+        <v>-4.734107455816564</v>
+      </c>
+      <c r="D76">
+        <v>4.749632544183435</v>
+      </c>
+      <c r="E76">
+        <v>9.85074</v>
+      </c>
+      <c r="F76">
+        <v>10.10174</v>
+      </c>
+      <c r="G76">
+        <v>0.618</v>
+      </c>
+      <c r="H76">
+        <v>13.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.034</v>
+      </c>
+      <c r="K76">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L76">
+        <v>0.025</v>
+      </c>
+      <c r="M76">
+        <v>2.412295512</v>
+      </c>
+      <c r="N76">
+        <v>-2.387295512</v>
+      </c>
+      <c r="O76">
+        <v>-0.596823878</v>
+      </c>
+      <c r="P76">
+        <v>-1.790471634</v>
+      </c>
+      <c r="Q76">
+        <v>-1.781471634</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3615276852701399</v>
+      </c>
+      <c r="T76">
+        <v>2.885755555498651</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.00259089318406857</v>
+      </c>
+      <c r="W76">
+        <v>0.2381812947076444</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.0103635727362742</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2722513562538933</v>
+      </c>
+      <c r="C77">
+        <v>-4.91130801011789</v>
+      </c>
+      <c r="D77">
+        <v>4.708941989882111</v>
+      </c>
+      <c r="E77">
+        <v>9.987250000000001</v>
+      </c>
+      <c r="F77">
+        <v>10.23825</v>
+      </c>
+      <c r="G77">
+        <v>0.618</v>
+      </c>
+      <c r="H77">
+        <v>13.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.034</v>
+      </c>
+      <c r="K77">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L77">
+        <v>0.025</v>
+      </c>
+      <c r="M77">
+        <v>2.4448941</v>
+      </c>
+      <c r="N77">
+        <v>-2.4198941</v>
+      </c>
+      <c r="O77">
+        <v>-0.6049735250000001</v>
+      </c>
+      <c r="P77">
+        <v>-1.814920575</v>
+      </c>
+      <c r="Q77">
+        <v>-1.805920575</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3744367926809455</v>
+      </c>
+      <c r="T77">
+        <v>3.001185777718597</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.002556347941614322</v>
+      </c>
+      <c r="W77">
+        <v>0.2381895441115425</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.0102253917664572</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2742513562538932</v>
+      </c>
+      <c r="C78">
+        <v>-5.087817286951991</v>
+      </c>
+      <c r="D78">
+        <v>4.668942713048009</v>
+      </c>
+      <c r="E78">
+        <v>10.12376</v>
+      </c>
+      <c r="F78">
+        <v>10.37476</v>
+      </c>
+      <c r="G78">
+        <v>0.618</v>
+      </c>
+      <c r="H78">
+        <v>13.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.034</v>
+      </c>
+      <c r="K78">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L78">
+        <v>0.025</v>
+      </c>
+      <c r="M78">
+        <v>2.477492688</v>
+      </c>
+      <c r="N78">
+        <v>-2.452492688</v>
+      </c>
+      <c r="O78">
+        <v>-0.6131231720000001</v>
+      </c>
+      <c r="P78">
+        <v>-1.839369516</v>
+      </c>
+      <c r="Q78">
+        <v>-1.830369516</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3884216590426516</v>
+      </c>
+      <c r="T78">
+        <v>3.126235185123539</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.002522711784487818</v>
+      </c>
+      <c r="W78">
+        <v>0.2381975764258643</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.01009084713795128</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2762513562538933</v>
+      </c>
+      <c r="C79">
+        <v>-5.263652753748279</v>
+      </c>
+      <c r="D79">
+        <v>4.62961724625172</v>
+      </c>
+      <c r="E79">
+        <v>10.26027</v>
+      </c>
+      <c r="F79">
+        <v>10.51127</v>
+      </c>
+      <c r="G79">
+        <v>0.618</v>
+      </c>
+      <c r="H79">
+        <v>13.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.034</v>
+      </c>
+      <c r="K79">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L79">
+        <v>0.025</v>
+      </c>
+      <c r="M79">
+        <v>2.510091276</v>
+      </c>
+      <c r="N79">
+        <v>-2.485091276</v>
+      </c>
+      <c r="O79">
+        <v>-0.6212728190000001</v>
+      </c>
+      <c r="P79">
+        <v>-1.863818457</v>
+      </c>
+      <c r="Q79">
+        <v>-1.854818457</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4036226007401582</v>
+      </c>
+      <c r="T79">
+        <v>3.262158454041954</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.002489949293780183</v>
+      </c>
+      <c r="W79">
+        <v>0.2382054001086453</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.009959797175120744</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2782513562538932</v>
+      </c>
+      <c r="C80">
+        <v>-5.438831294354438</v>
+      </c>
+      <c r="D80">
+        <v>4.590948705645562</v>
+      </c>
+      <c r="E80">
+        <v>10.39678</v>
+      </c>
+      <c r="F80">
+        <v>10.64778</v>
+      </c>
+      <c r="G80">
+        <v>0.618</v>
+      </c>
+      <c r="H80">
+        <v>13.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.034</v>
+      </c>
+      <c r="K80">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L80">
+        <v>0.025</v>
+      </c>
+      <c r="M80">
+        <v>2.542689864</v>
+      </c>
+      <c r="N80">
+        <v>-2.517689864</v>
+      </c>
+      <c r="O80">
+        <v>-0.6294224660000001</v>
+      </c>
+      <c r="P80">
+        <v>-1.888267398</v>
+      </c>
+      <c r="Q80">
+        <v>-1.879267398</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4202054462283472</v>
+      </c>
+      <c r="T80">
+        <v>3.410438383771133</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.002458026866936848</v>
+      </c>
+      <c r="W80">
+        <v>0.2382130231841755</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.00983210746774732</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2802513562538933</v>
+      </c>
+      <c r="C81">
+        <v>-5.613369233206172</v>
+      </c>
+      <c r="D81">
+        <v>4.552920766793828</v>
+      </c>
+      <c r="E81">
+        <v>10.53329</v>
+      </c>
+      <c r="F81">
+        <v>10.78429</v>
+      </c>
+      <c r="G81">
+        <v>0.618</v>
+      </c>
+      <c r="H81">
+        <v>13.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.034</v>
+      </c>
+      <c r="K81">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L81">
+        <v>0.025</v>
+      </c>
+      <c r="M81">
+        <v>2.575288452</v>
+      </c>
+      <c r="N81">
+        <v>-2.550288452</v>
+      </c>
+      <c r="O81">
+        <v>-0.6375721130000001</v>
+      </c>
+      <c r="P81">
+        <v>-1.912716339</v>
+      </c>
+      <c r="Q81">
+        <v>-1.903716339</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4383676103344591</v>
+      </c>
+      <c r="T81">
+        <v>3.572840211569759</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.002426912602798407</v>
+      </c>
+      <c r="W81">
+        <v>0.2382204532704518</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.009707650411193591</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
         <v>0.8</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0.8</v>
-      </c>
-      <c r="AG3">
-        <v>0.763</v>
-      </c>
-      <c r="AH3">
-        <v>0.2684563758389262</v>
-      </c>
-      <c r="AI3">
-        <v>0.7858546168958743</v>
-      </c>
-      <c r="AJ3">
-        <v>0.2592592592592592</v>
-      </c>
-      <c r="AK3">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="AL3">
-        <v>0.035</v>
-      </c>
-      <c r="AM3">
-        <v>0.035</v>
-      </c>
-      <c r="AN3">
-        <v>-30.76923076923077</v>
-      </c>
-      <c r="AO3">
-        <v>-1.171428571428571</v>
-      </c>
-      <c r="AP3">
-        <v>-29.34615384615385</v>
-      </c>
-      <c r="AQ3">
-        <v>-1.171428571428571</v>
+      <c r="B82">
+        <v>0.2822513562538932</v>
+      </c>
+      <c r="C82">
+        <v>-5.787282358305589</v>
+      </c>
+      <c r="D82">
+        <v>4.515517641694411</v>
+      </c>
+      <c r="E82">
+        <v>10.6698</v>
+      </c>
+      <c r="F82">
+        <v>10.9208</v>
+      </c>
+      <c r="G82">
+        <v>0.618</v>
+      </c>
+      <c r="H82">
+        <v>13.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.034</v>
+      </c>
+      <c r="K82">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L82">
+        <v>0.025</v>
+      </c>
+      <c r="M82">
+        <v>2.60788704</v>
+      </c>
+      <c r="N82">
+        <v>-2.58288704</v>
+      </c>
+      <c r="O82">
+        <v>-0.64572176</v>
+      </c>
+      <c r="P82">
+        <v>-1.93716528</v>
+      </c>
+      <c r="Q82">
+        <v>-1.92816528</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.458345990851182</v>
+      </c>
+      <c r="T82">
+        <v>3.751482222148247</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.002396576195263427</v>
+      </c>
+      <c r="W82">
+        <v>0.2382276976045711</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.009586304781053712</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2842513562538933</v>
+      </c>
+      <c r="C83">
+        <v>-5.960585943076201</v>
+      </c>
+      <c r="D83">
+        <v>4.4787240569238</v>
+      </c>
+      <c r="E83">
+        <v>10.80631</v>
+      </c>
+      <c r="F83">
+        <v>11.05731</v>
+      </c>
+      <c r="G83">
+        <v>0.618</v>
+      </c>
+      <c r="H83">
+        <v>13.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.034</v>
+      </c>
+      <c r="K83">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L83">
+        <v>0.025</v>
+      </c>
+      <c r="M83">
+        <v>2.640485628</v>
+      </c>
+      <c r="N83">
+        <v>-2.615485628000001</v>
+      </c>
+      <c r="O83">
+        <v>-0.6538714070000001</v>
+      </c>
+      <c r="P83">
+        <v>-1.961614221</v>
+      </c>
+      <c r="Q83">
+        <v>-1.952614221000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4804273587907179</v>
+      </c>
+      <c r="T83">
+        <v>3.948928654892891</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.002366988834828076</v>
+      </c>
+      <c r="W83">
+        <v>0.2382347630662431</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.009467955339312217</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2862513562538933</v>
+      </c>
+      <c r="C84">
+        <v>-6.133294767158041</v>
+      </c>
+      <c r="D84">
+        <v>4.442525232841959</v>
+      </c>
+      <c r="E84">
+        <v>10.94282</v>
+      </c>
+      <c r="F84">
+        <v>11.19382</v>
+      </c>
+      <c r="G84">
+        <v>0.618</v>
+      </c>
+      <c r="H84">
+        <v>13.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.034</v>
+      </c>
+      <c r="K84">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L84">
+        <v>0.025</v>
+      </c>
+      <c r="M84">
+        <v>2.673084216</v>
+      </c>
+      <c r="N84">
+        <v>-2.648084216</v>
+      </c>
+      <c r="O84">
+        <v>-0.6620210540000001</v>
+      </c>
+      <c r="P84">
+        <v>-1.986063162</v>
+      </c>
+      <c r="Q84">
+        <v>-1.977063162</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5049622120568689</v>
+      </c>
+      <c r="T84">
+        <v>4.168313580164719</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.002338123117330172</v>
+      </c>
+      <c r="W84">
+        <v>0.2382416561995816</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.009352492469320683</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2882513562538933</v>
+      </c>
+      <c r="C85">
+        <v>-6.305423136202468</v>
+      </c>
+      <c r="D85">
+        <v>4.406906863797531</v>
+      </c>
+      <c r="E85">
+        <v>11.07933</v>
+      </c>
+      <c r="F85">
+        <v>11.33033</v>
+      </c>
+      <c r="G85">
+        <v>0.618</v>
+      </c>
+      <c r="H85">
+        <v>13.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.034</v>
+      </c>
+      <c r="K85">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L85">
+        <v>0.025</v>
+      </c>
+      <c r="M85">
+        <v>2.705682804</v>
+      </c>
+      <c r="N85">
+        <v>-2.680682804</v>
+      </c>
+      <c r="O85">
+        <v>-0.6701707010000001</v>
+      </c>
+      <c r="P85">
+        <v>-2.010512103</v>
+      </c>
+      <c r="Q85">
+        <v>-2.001512103</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5323835186484496</v>
+      </c>
+      <c r="T85">
+        <v>4.413508496644997</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.00230995295929005</v>
+      </c>
+      <c r="W85">
+        <v>0.2382483832333215</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.009239811837160161</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2902513562538933</v>
+      </c>
+      <c r="C86">
+        <v>-6.476984900722265</v>
+      </c>
+      <c r="D86">
+        <v>4.371855099277735</v>
+      </c>
+      <c r="E86">
+        <v>11.21584</v>
+      </c>
+      <c r="F86">
+        <v>11.46684</v>
+      </c>
+      <c r="G86">
+        <v>0.618</v>
+      </c>
+      <c r="H86">
+        <v>13.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.034</v>
+      </c>
+      <c r="K86">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L86">
+        <v>0.025</v>
+      </c>
+      <c r="M86">
+        <v>2.738281392</v>
+      </c>
+      <c r="N86">
+        <v>-2.713281392</v>
+      </c>
+      <c r="O86">
+        <v>-0.6783203480000001</v>
+      </c>
+      <c r="P86">
+        <v>-2.034961044</v>
+      </c>
+      <c r="Q86">
+        <v>-2.025961044</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5632324885639775</v>
+      </c>
+      <c r="T86">
+        <v>4.689352777685308</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.002282453519298502</v>
+      </c>
+      <c r="W86">
+        <v>0.2382549500995916</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.009129814077193932</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2922513562538933</v>
+      </c>
+      <c r="C87">
+        <v>-6.647993474049275</v>
+      </c>
+      <c r="D87">
+        <v>4.337356525950724</v>
+      </c>
+      <c r="E87">
+        <v>11.35235</v>
+      </c>
+      <c r="F87">
+        <v>11.60335</v>
+      </c>
+      <c r="G87">
+        <v>0.618</v>
+      </c>
+      <c r="H87">
+        <v>13.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.034</v>
+      </c>
+      <c r="K87">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L87">
+        <v>0.025</v>
+      </c>
+      <c r="M87">
+        <v>2.77087998</v>
+      </c>
+      <c r="N87">
+        <v>-2.74587998</v>
+      </c>
+      <c r="O87">
+        <v>-0.6864699949999999</v>
+      </c>
+      <c r="P87">
+        <v>-2.059409985</v>
+      </c>
+      <c r="Q87">
+        <v>-2.050409985</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5981946544682424</v>
+      </c>
+      <c r="T87">
+        <v>5.001976296197661</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.002255601124953814</v>
+      </c>
+      <c r="W87">
+        <v>0.238261362451361</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.009022404499815173</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2942513562538933</v>
+      </c>
+      <c r="C88">
+        <v>-6.818461849448465</v>
+      </c>
+      <c r="D88">
+        <v>4.303398150551534</v>
+      </c>
+      <c r="E88">
+        <v>11.48886</v>
+      </c>
+      <c r="F88">
+        <v>11.73986</v>
+      </c>
+      <c r="G88">
+        <v>0.618</v>
+      </c>
+      <c r="H88">
+        <v>13.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.034</v>
+      </c>
+      <c r="K88">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L88">
+        <v>0.025</v>
+      </c>
+      <c r="M88">
+        <v>2.803478568</v>
+      </c>
+      <c r="N88">
+        <v>-2.778478568</v>
+      </c>
+      <c r="O88">
+        <v>-0.694619642</v>
+      </c>
+      <c r="P88">
+        <v>-2.083858926</v>
+      </c>
+      <c r="Q88">
+        <v>-2.074858926</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6381514155016885</v>
+      </c>
+      <c r="T88">
+        <v>5.359260317354638</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.002229373204896211</v>
+      </c>
+      <c r="W88">
+        <v>0.2382676256786708</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.00891749281958476</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2962513562538933</v>
+      </c>
+      <c r="C89">
+        <v>-6.988402616434268</v>
+      </c>
+      <c r="D89">
+        <v>4.269967383565731</v>
+      </c>
+      <c r="E89">
+        <v>11.62537</v>
+      </c>
+      <c r="F89">
+        <v>11.87637</v>
+      </c>
+      <c r="G89">
+        <v>0.618</v>
+      </c>
+      <c r="H89">
+        <v>13.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.034</v>
+      </c>
+      <c r="K89">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L89">
+        <v>0.025</v>
+      </c>
+      <c r="M89">
+        <v>2.836077156</v>
+      </c>
+      <c r="N89">
+        <v>-2.811077156</v>
+      </c>
+      <c r="O89">
+        <v>-0.702769289</v>
+      </c>
+      <c r="P89">
+        <v>-2.108307867</v>
+      </c>
+      <c r="Q89">
+        <v>-2.099307867</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6842553705402799</v>
+      </c>
+      <c r="T89">
+        <v>5.771511110997301</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.002203748225529588</v>
+      </c>
+      <c r="W89">
+        <v>0.2382737449237435</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.00881499290211829</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2982513562538933</v>
+      </c>
+      <c r="C90">
+        <v>-7.157827976332307</v>
+      </c>
+      <c r="D90">
+        <v>4.237052023667692</v>
+      </c>
+      <c r="E90">
+        <v>11.76188</v>
+      </c>
+      <c r="F90">
+        <v>12.01288</v>
+      </c>
+      <c r="G90">
+        <v>0.618</v>
+      </c>
+      <c r="H90">
+        <v>13.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.034</v>
+      </c>
+      <c r="K90">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L90">
+        <v>0.025</v>
+      </c>
+      <c r="M90">
+        <v>2.868675744</v>
+      </c>
+      <c r="N90">
+        <v>-2.843675744</v>
+      </c>
+      <c r="O90">
+        <v>-0.710918936</v>
+      </c>
+      <c r="P90">
+        <v>-2.132756808</v>
+      </c>
+      <c r="Q90">
+        <v>-2.123756808</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7380433180853032</v>
+      </c>
+      <c r="T90">
+        <v>6.252470370247077</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.002178705632057661</v>
+      </c>
+      <c r="W90">
+        <v>0.2382797250950646</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.008714822528230637</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3002513562538933</v>
+      </c>
+      <c r="C91">
+        <v>-7.326749757126844</v>
+      </c>
+      <c r="D91">
+        <v>4.204640242873156</v>
+      </c>
+      <c r="E91">
+        <v>11.89839</v>
+      </c>
+      <c r="F91">
+        <v>12.14939</v>
+      </c>
+      <c r="G91">
+        <v>0.618</v>
+      </c>
+      <c r="H91">
+        <v>13.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.034</v>
+      </c>
+      <c r="K91">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L91">
+        <v>0.025</v>
+      </c>
+      <c r="M91">
+        <v>2.901274332</v>
+      </c>
+      <c r="N91">
+        <v>-2.876274332</v>
+      </c>
+      <c r="O91">
+        <v>-0.7190685830000001</v>
+      </c>
+      <c r="P91">
+        <v>-2.157205749</v>
+      </c>
+      <c r="Q91">
+        <v>-2.148205749</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.8016108924566945</v>
+      </c>
+      <c r="T91">
+        <v>6.820876767542266</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.002154225793495215</v>
+      </c>
+      <c r="W91">
+        <v>0.2382855708805134</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.008616903173980783</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3022513562538933</v>
+      </c>
+      <c r="C92">
+        <v>-7.495179427631945</v>
+      </c>
+      <c r="D92">
+        <v>4.172720572368054</v>
+      </c>
+      <c r="E92">
+        <v>12.0349</v>
+      </c>
+      <c r="F92">
+        <v>12.2859</v>
+      </c>
+      <c r="G92">
+        <v>0.618</v>
+      </c>
+      <c r="H92">
+        <v>13.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.034</v>
+      </c>
+      <c r="K92">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L92">
+        <v>0.025</v>
+      </c>
+      <c r="M92">
+        <v>2.93387292</v>
+      </c>
+      <c r="N92">
+        <v>-2.90887292</v>
+      </c>
+      <c r="O92">
+        <v>-0.7272182300000001</v>
+      </c>
+      <c r="P92">
+        <v>-2.18165469</v>
+      </c>
+      <c r="Q92">
+        <v>-2.17265469</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.877891981702364</v>
+      </c>
+      <c r="T92">
+        <v>7.502964444296494</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.002130289951345268</v>
+      </c>
+      <c r="W92">
+        <v>0.2382912867596188</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.00852115980538104</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3042513562538933</v>
+      </c>
+      <c r="C93">
+        <v>-7.663128111022036</v>
+      </c>
+      <c r="D93">
+        <v>4.141281888977965</v>
+      </c>
+      <c r="E93">
+        <v>12.17141</v>
+      </c>
+      <c r="F93">
+        <v>12.42241</v>
+      </c>
+      <c r="G93">
+        <v>0.618</v>
+      </c>
+      <c r="H93">
+        <v>13.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.034</v>
+      </c>
+      <c r="K93">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L93">
+        <v>0.025</v>
+      </c>
+      <c r="M93">
+        <v>2.966471508000001</v>
+      </c>
+      <c r="N93">
+        <v>-2.941471508000001</v>
+      </c>
+      <c r="O93">
+        <v>-0.7353678770000002</v>
+      </c>
+      <c r="P93">
+        <v>-2.206103631</v>
+      </c>
+      <c r="Q93">
+        <v>-2.197103631000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.9711244241137378</v>
+      </c>
+      <c r="T93">
+        <v>8.336627160329439</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.002106880171660155</v>
+      </c>
+      <c r="W93">
+        <v>0.2382968770150076</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.008427520686640544</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3062513562538933</v>
+      </c>
+      <c r="C94">
+        <v>-7.830606597755351</v>
+      </c>
+      <c r="D94">
+        <v>4.11031340224465</v>
+      </c>
+      <c r="E94">
+        <v>12.30792</v>
+      </c>
+      <c r="F94">
+        <v>12.55892</v>
+      </c>
+      <c r="G94">
+        <v>0.618</v>
+      </c>
+      <c r="H94">
+        <v>13.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.034</v>
+      </c>
+      <c r="K94">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L94">
+        <v>0.025</v>
+      </c>
+      <c r="M94">
+        <v>2.999070096</v>
+      </c>
+      <c r="N94">
+        <v>-2.974070096</v>
+      </c>
+      <c r="O94">
+        <v>-0.743517524</v>
+      </c>
+      <c r="P94">
+        <v>-2.230552572</v>
+      </c>
+      <c r="Q94">
+        <v>-2.221552572</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.087664977127955</v>
+      </c>
+      <c r="T94">
+        <v>9.378705555370621</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.002083979300229067</v>
+      </c>
+      <c r="W94">
+        <v>0.2383023457431053</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.008335917200916199</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3082513562538933</v>
+      </c>
+      <c r="C95">
+        <v>-7.997625357921855</v>
+      </c>
+      <c r="D95">
+        <v>4.079804642078145</v>
+      </c>
+      <c r="E95">
+        <v>12.44443</v>
+      </c>
+      <c r="F95">
+        <v>12.69543</v>
+      </c>
+      <c r="G95">
+        <v>0.618</v>
+      </c>
+      <c r="H95">
+        <v>13.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.034</v>
+      </c>
+      <c r="K95">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L95">
+        <v>0.025</v>
+      </c>
+      <c r="M95">
+        <v>3.031668684</v>
+      </c>
+      <c r="N95">
+        <v>-3.006668684</v>
+      </c>
+      <c r="O95">
+        <v>-0.751667171</v>
+      </c>
+      <c r="P95">
+        <v>-2.255001513</v>
+      </c>
+      <c r="Q95">
+        <v>-2.246001513</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.237502831003378</v>
+      </c>
+      <c r="T95">
+        <v>10.71852063470928</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.002061570920656711</v>
+      </c>
+      <c r="W95">
+        <v>0.2383076968641472</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.008246283682626809</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3102513562538932</v>
+      </c>
+      <c r="C96">
+        <v>-8.164194553045288</v>
+      </c>
+      <c r="D96">
+        <v>4.049745446954712</v>
+      </c>
+      <c r="E96">
+        <v>12.58094</v>
+      </c>
+      <c r="F96">
+        <v>12.83194</v>
+      </c>
+      <c r="G96">
+        <v>0.618</v>
+      </c>
+      <c r="H96">
+        <v>13.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.034</v>
+      </c>
+      <c r="K96">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L96">
+        <v>0.025</v>
+      </c>
+      <c r="M96">
+        <v>3.064267272</v>
+      </c>
+      <c r="N96">
+        <v>-3.039267272</v>
+      </c>
+      <c r="O96">
+        <v>-0.7598168180000001</v>
+      </c>
+      <c r="P96">
+        <v>-2.279450454</v>
+      </c>
+      <c r="Q96">
+        <v>-2.270450454000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.437286636170608</v>
+      </c>
+      <c r="T96">
+        <v>12.50494074049417</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.00203963931511781</v>
+      </c>
+      <c r="W96">
+        <v>0.2383129341315499</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.008158557260471211</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3122513562538933</v>
+      </c>
+      <c r="C97">
+        <v>-8.330324047367306</v>
+      </c>
+      <c r="D97">
+        <v>4.020125952632696</v>
+      </c>
+      <c r="E97">
+        <v>12.71745</v>
+      </c>
+      <c r="F97">
+        <v>12.96845</v>
+      </c>
+      <c r="G97">
+        <v>0.618</v>
+      </c>
+      <c r="H97">
+        <v>13.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.034</v>
+      </c>
+      <c r="K97">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L97">
+        <v>0.025</v>
+      </c>
+      <c r="M97">
+        <v>3.09686586</v>
+      </c>
+      <c r="N97">
+        <v>-3.07186586</v>
+      </c>
+      <c r="O97">
+        <v>-0.7679664650000001</v>
+      </c>
+      <c r="P97">
+        <v>-2.303899395</v>
+      </c>
+      <c r="Q97">
+        <v>-2.294899395</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.71698396340473</v>
+      </c>
+      <c r="T97">
+        <v>15.00592888859301</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.002018169427590254</v>
+      </c>
+      <c r="W97">
+        <v>0.2383180611406915</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.00807267771036102</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3142513562538933</v>
+      </c>
+      <c r="C98">
+        <v>-8.496023418640009</v>
+      </c>
+      <c r="D98">
+        <v>3.990936581359991</v>
+      </c>
+      <c r="E98">
+        <v>12.85396</v>
+      </c>
+      <c r="F98">
+        <v>13.10496</v>
+      </c>
+      <c r="G98">
+        <v>0.618</v>
+      </c>
+      <c r="H98">
+        <v>13.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.034</v>
+      </c>
+      <c r="K98">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L98">
+        <v>0.025</v>
+      </c>
+      <c r="M98">
+        <v>3.129464448</v>
+      </c>
+      <c r="N98">
+        <v>-3.104464448</v>
+      </c>
+      <c r="O98">
+        <v>-0.7761161120000001</v>
+      </c>
+      <c r="P98">
+        <v>-2.328348336</v>
+      </c>
+      <c r="Q98">
+        <v>-2.319348336</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.136529954255908</v>
+      </c>
+      <c r="T98">
+        <v>18.75741111074122</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.001997146829386189</v>
+      </c>
+      <c r="W98">
+        <v>0.2383230813371426</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.007988587317544704</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3162513562538933</v>
+      </c>
+      <c r="C99">
+        <v>-8.661301968451731</v>
+      </c>
+      <c r="D99">
+        <v>3.962168031548268</v>
+      </c>
+      <c r="E99">
+        <v>12.99047</v>
+      </c>
+      <c r="F99">
+        <v>13.24147</v>
+      </c>
+      <c r="G99">
+        <v>0.618</v>
+      </c>
+      <c r="H99">
+        <v>13.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.034</v>
+      </c>
+      <c r="K99">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L99">
+        <v>0.025</v>
+      </c>
+      <c r="M99">
+        <v>3.162063036</v>
+      </c>
+      <c r="N99">
+        <v>-3.137063036</v>
+      </c>
+      <c r="O99">
+        <v>-0.7842657590000001</v>
+      </c>
+      <c r="P99">
+        <v>-2.352797277</v>
+      </c>
+      <c r="Q99">
+        <v>-2.343797277</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.835773272341211</v>
+      </c>
+      <c r="T99">
+        <v>25.00988148098829</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.001976557686815197</v>
+      </c>
+      <c r="W99">
+        <v>0.2383279980243886</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.007906230747260712</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3182513562538933</v>
+      </c>
+      <c r="C100">
+        <v>-8.826168732109362</v>
+      </c>
+      <c r="D100">
+        <v>3.933811267890636</v>
+      </c>
+      <c r="E100">
+        <v>13.12698</v>
+      </c>
+      <c r="F100">
+        <v>13.37798</v>
+      </c>
+      <c r="G100">
+        <v>0.618</v>
+      </c>
+      <c r="H100">
+        <v>13.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.034</v>
+      </c>
+      <c r="K100">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L100">
+        <v>0.025</v>
+      </c>
+      <c r="M100">
+        <v>3.194661624</v>
+      </c>
+      <c r="N100">
+        <v>-3.169661624</v>
+      </c>
+      <c r="O100">
+        <v>-0.792415406</v>
+      </c>
+      <c r="P100">
+        <v>-2.377246218</v>
+      </c>
+      <c r="Q100">
+        <v>-2.368246218</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.234259908511816</v>
+      </c>
+      <c r="T100">
+        <v>37.51482222148243</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.001956388730827287</v>
+      </c>
+      <c r="W100">
+        <v>0.2383328143710784</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.007825554923309164</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3202513562538933</v>
+      </c>
+      <c r="C101">
+        <v>-8.990632488099383</v>
+      </c>
+      <c r="D101">
+        <v>3.905857511900617</v>
+      </c>
+      <c r="E101">
+        <v>13.26349</v>
+      </c>
+      <c r="F101">
+        <v>13.51449</v>
+      </c>
+      <c r="G101">
+        <v>0.618</v>
+      </c>
+      <c r="H101">
+        <v>13.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.034</v>
+      </c>
+      <c r="K101">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L101">
+        <v>0.025</v>
+      </c>
+      <c r="M101">
+        <v>3.227260212</v>
+      </c>
+      <c r="N101">
+        <v>-3.202260212000001</v>
+      </c>
+      <c r="O101">
+        <v>-0.8005650530000001</v>
+      </c>
+      <c r="P101">
+        <v>-2.401695159</v>
+      </c>
+      <c r="Q101">
+        <v>-2.392695159000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>8.429719817023631</v>
+      </c>
+      <c r="T101">
+        <v>75.02964444296487</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.001936627228495698</v>
+      </c>
+      <c r="W101">
+        <v>0.2383375334178352</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.007746508913982764</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jamaica/jamaica_education.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_education.xlsx
@@ -1385,7 +1385,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1522,22 +1522,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1235330208721424</v>
+        <v>0.1232819383199621</v>
       </c>
       <c r="C2">
-        <v>12.92242217151984</v>
+        <v>12.83522328303595</v>
       </c>
       <c r="D2">
-        <v>12.64642217151984</v>
+        <v>12.68740328303596</v>
       </c>
       <c r="E2">
-        <v>-0.718</v>
+        <v>-0.58982</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.12818</v>
       </c>
       <c r="G2">
         <v>0.276</v>
@@ -1558,45 +1558,45 @@
         <v>0.054</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.006857629999999999</v>
       </c>
       <c r="N2">
-        <v>0.054</v>
+        <v>0.04714237</v>
       </c>
       <c r="O2">
-        <v>0.0135</v>
+        <v>0.0117855925</v>
       </c>
       <c r="P2">
-        <v>0.0405</v>
+        <v>0.03535677750000001</v>
       </c>
       <c r="Q2">
-        <v>0.0905</v>
+        <v>0.08535677750000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1235330208721424</v>
+        <v>0.1241219073939011</v>
       </c>
       <c r="T2">
-        <v>0.7517377218129921</v>
+        <v>0.7574327045539997</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.03772499999999999</v>
+        <v>0.040125</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>7.87444058661666</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1604,22 +1604,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1232819383199621</v>
+        <v>0.1231898557677817</v>
       </c>
       <c r="C3">
-        <v>12.83522328303595</v>
+        <v>12.72213942791506</v>
       </c>
       <c r="D3">
-        <v>12.68740328303596</v>
+        <v>12.70249942791506</v>
       </c>
       <c r="E3">
-        <v>-0.58982</v>
+        <v>-0.46164</v>
       </c>
       <c r="F3">
-        <v>0.12818</v>
+        <v>0.25636</v>
       </c>
       <c r="G3">
         <v>0.276</v>
@@ -1640,45 +1640,45 @@
         <v>0.054</v>
       </c>
       <c r="M3">
-        <v>0.006857629999999999</v>
+        <v>0.016432676</v>
       </c>
       <c r="N3">
-        <v>0.04714237</v>
+        <v>0.037567324</v>
       </c>
       <c r="O3">
-        <v>0.0117855925</v>
+        <v>0.009391831</v>
       </c>
       <c r="P3">
-        <v>0.03535677750000001</v>
+        <v>0.028175493</v>
       </c>
       <c r="Q3">
-        <v>0.08535677750000001</v>
+        <v>0.078175493</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1241219073939011</v>
+        <v>0.1247228120079405</v>
       </c>
       <c r="T3">
-        <v>0.7574327045539997</v>
+        <v>0.7632439114325789</v>
       </c>
       <c r="U3">
-        <v>0.0535</v>
+        <v>0.0641</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.040125</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y3">
-        <v>7.87444058661666</v>
+        <v>3.28613550221522</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1686,22 +1686,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1231898557677817</v>
+        <v>0.1236010232156013</v>
       </c>
       <c r="C4">
-        <v>12.72213942791506</v>
+        <v>12.52682850784692</v>
       </c>
       <c r="D4">
-        <v>12.70249942791506</v>
+        <v>12.63536850784692</v>
       </c>
       <c r="E4">
-        <v>-0.46164</v>
+        <v>-0.33346</v>
       </c>
       <c r="F4">
-        <v>0.25636</v>
+        <v>0.38454</v>
       </c>
       <c r="G4">
         <v>0.276</v>
@@ -1722,45 +1722,45 @@
         <v>0.054</v>
       </c>
       <c r="M4">
-        <v>0.016432676</v>
+        <v>0.0346086</v>
       </c>
       <c r="N4">
-        <v>0.037567324</v>
+        <v>0.0193914</v>
       </c>
       <c r="O4">
-        <v>0.009391831</v>
+        <v>0.004847850000000001</v>
       </c>
       <c r="P4">
-        <v>0.028175493</v>
+        <v>0.01454355</v>
       </c>
       <c r="Q4">
-        <v>0.078175493</v>
+        <v>0.06454355000000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1247228120079405</v>
+        <v>0.1253361064078364</v>
       </c>
       <c r="T4">
-        <v>0.7632439114325789</v>
+        <v>0.7691749370096852</v>
       </c>
       <c r="U4">
-        <v>0.0641</v>
+        <v>0.09</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.04807500000000001</v>
+        <v>0.0675</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y4">
-        <v>3.28613550221522</v>
+        <v>1.560305819940708</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1768,22 +1768,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1236010232156013</v>
+        <v>0.1282721007121777</v>
       </c>
       <c r="C5">
-        <v>12.52682850784692</v>
+        <v>11.68300303515632</v>
       </c>
       <c r="D5">
-        <v>12.63536850784692</v>
+        <v>11.91972303515632</v>
       </c>
       <c r="E5">
-        <v>-0.33346</v>
+        <v>-0.20528</v>
       </c>
       <c r="F5">
-        <v>0.38454</v>
+        <v>0.51272</v>
       </c>
       <c r="G5">
         <v>0.276</v>
@@ -1804,45 +1804,45 @@
         <v>0.054</v>
       </c>
       <c r="M5">
-        <v>0.0346086</v>
+        <v>0.102954176</v>
       </c>
       <c r="N5">
-        <v>0.0193914</v>
+        <v>-0.048954176</v>
       </c>
       <c r="O5">
-        <v>0.004847850000000001</v>
+        <v>-0.012238544</v>
       </c>
       <c r="P5">
-        <v>0.01454355</v>
+        <v>-0.036715632</v>
       </c>
       <c r="Q5">
-        <v>0.06454355000000001</v>
+        <v>0.013284368</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1253361064078364</v>
+        <v>0.1263471949381642</v>
       </c>
       <c r="T5">
-        <v>0.7691749370096852</v>
+        <v>0.7789529358551186</v>
       </c>
       <c r="U5">
-        <v>0.09</v>
+        <v>0.2008</v>
       </c>
       <c r="V5">
-        <v>0.25</v>
+        <v>0.1311262983640411</v>
       </c>
       <c r="W5">
-        <v>0.0675</v>
+        <v>0.1744698392885005</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y5">
-        <v>1.560305819940708</v>
+        <v>0.5245051934561644</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1850,22 +1850,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1282721007121777</v>
+        <v>0.1316326180175325</v>
       </c>
       <c r="C6">
-        <v>11.68300303515632</v>
+        <v>11.08814222709222</v>
       </c>
       <c r="D6">
-        <v>11.91972303515632</v>
+        <v>11.45304222709222</v>
       </c>
       <c r="E6">
-        <v>-0.20528</v>
+        <v>-0.07709999999999995</v>
       </c>
       <c r="F6">
-        <v>0.51272</v>
+        <v>0.6409</v>
       </c>
       <c r="G6">
         <v>0.276</v>
@@ -1886,45 +1886,45 @@
         <v>0.054</v>
       </c>
       <c r="M6">
-        <v>0.102954176</v>
+        <v>0.15112422</v>
       </c>
       <c r="N6">
-        <v>-0.048954176</v>
+        <v>-0.09712422000000001</v>
       </c>
       <c r="O6">
-        <v>-0.012238544</v>
+        <v>-0.024281055</v>
       </c>
       <c r="P6">
-        <v>-0.036715632</v>
+        <v>-0.07284316500000002</v>
       </c>
       <c r="Q6">
-        <v>0.013284368</v>
+        <v>-0.02284316500000002</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1263471949381642</v>
+        <v>0.1272587625747289</v>
       </c>
       <c r="T6">
-        <v>0.7789529358551186</v>
+        <v>0.7877684915957959</v>
       </c>
       <c r="U6">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>0.1311262983640411</v>
+        <v>0.08933048587446804</v>
       </c>
       <c r="W6">
-        <v>0.1744698392885005</v>
+        <v>0.2147358714308004</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y6">
-        <v>0.5245051934561644</v>
+        <v>0.3573219434978721</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1932,22 +1932,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1316326180175325</v>
+        <v>0.1335326180175325</v>
       </c>
       <c r="C7">
-        <v>11.08814222709222</v>
+        <v>10.71192699546233</v>
       </c>
       <c r="D7">
-        <v>11.45304222709222</v>
+        <v>11.20500699546233</v>
       </c>
       <c r="E7">
-        <v>-0.07709999999999995</v>
+        <v>0.05108000000000001</v>
       </c>
       <c r="F7">
-        <v>0.6409</v>
+        <v>0.76908</v>
       </c>
       <c r="G7">
         <v>0.276</v>
@@ -1968,37 +1968,37 @@
         <v>0.054</v>
       </c>
       <c r="M7">
-        <v>0.15112422</v>
+        <v>0.181349064</v>
       </c>
       <c r="N7">
-        <v>-0.09712422000000001</v>
+        <v>-0.127349064</v>
       </c>
       <c r="O7">
-        <v>-0.024281055</v>
+        <v>-0.031837266</v>
       </c>
       <c r="P7">
-        <v>-0.07284316500000002</v>
+        <v>-0.09551179800000001</v>
       </c>
       <c r="Q7">
-        <v>-0.02284316500000002</v>
+        <v>-0.04551179800000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1272587625747289</v>
+        <v>0.1281253451553111</v>
       </c>
       <c r="T7">
-        <v>0.7877684915957959</v>
+        <v>0.7961490074638362</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>0.08933048587446804</v>
+        <v>0.07444207156205669</v>
       </c>
       <c r="W7">
-        <v>0.2147358714308004</v>
+        <v>0.218246559525667</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>0.3573219434978721</v>
+        <v>0.2977682862482267</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2014,22 +2014,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1335326180175325</v>
+        <v>0.1354326180175325</v>
       </c>
       <c r="C8">
-        <v>10.71192699546233</v>
+        <v>10.34622728709886</v>
       </c>
       <c r="D8">
-        <v>11.20500699546233</v>
+        <v>10.96748728709886</v>
       </c>
       <c r="E8">
-        <v>0.05108000000000001</v>
+        <v>0.1792599999999999</v>
       </c>
       <c r="F8">
-        <v>0.76908</v>
+        <v>0.8972599999999998</v>
       </c>
       <c r="G8">
         <v>0.276</v>
@@ -2050,37 +2050,37 @@
         <v>0.054</v>
       </c>
       <c r="M8">
-        <v>0.181349064</v>
+        <v>0.211573908</v>
       </c>
       <c r="N8">
-        <v>-0.127349064</v>
+        <v>-0.157573908</v>
       </c>
       <c r="O8">
-        <v>-0.031837266</v>
+        <v>-0.039393477</v>
       </c>
       <c r="P8">
-        <v>-0.09551179800000001</v>
+        <v>-0.118180431</v>
       </c>
       <c r="Q8">
-        <v>-0.04551179800000001</v>
+        <v>-0.06818043099999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1281253451553111</v>
+        <v>0.129010563920422</v>
       </c>
       <c r="T8">
-        <v>0.7961490074638362</v>
+        <v>0.8047097494795765</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>0.07444207156205669</v>
+        <v>0.06380748991033432</v>
       </c>
       <c r="W8">
-        <v>0.218246559525667</v>
+        <v>0.2207541938791432</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>0.2977682862482267</v>
+        <v>0.2552299596413372</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2096,22 +2096,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1354326180175325</v>
+        <v>0.1373326180175325</v>
       </c>
       <c r="C9">
-        <v>10.34622728709886</v>
+        <v>9.990388270053195</v>
       </c>
       <c r="D9">
-        <v>10.96748728709886</v>
+        <v>10.7398282700532</v>
       </c>
       <c r="E9">
-        <v>0.1792600000000001</v>
+        <v>0.3074399999999999</v>
       </c>
       <c r="F9">
-        <v>0.8972600000000001</v>
+        <v>1.02544</v>
       </c>
       <c r="G9">
         <v>0.276</v>
@@ -2132,37 +2132,37 @@
         <v>0.054</v>
       </c>
       <c r="M9">
-        <v>0.211573908</v>
+        <v>0.241798752</v>
       </c>
       <c r="N9">
-        <v>-0.157573908</v>
+        <v>-0.187798752</v>
       </c>
       <c r="O9">
-        <v>-0.03939347700000001</v>
+        <v>-0.046949688</v>
       </c>
       <c r="P9">
-        <v>-0.118180431</v>
+        <v>-0.140849064</v>
       </c>
       <c r="Q9">
-        <v>-0.06818043100000004</v>
+        <v>-0.09084906400000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.129010563920422</v>
+        <v>0.1299150265717309</v>
       </c>
       <c r="T9">
-        <v>0.8047097494795765</v>
+        <v>0.8134565945826154</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>0.0638074899103343</v>
+        <v>0.05583155367154253</v>
       </c>
       <c r="W9">
-        <v>0.2207541938791432</v>
+        <v>0.2226349196442503</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>0.2552299596413372</v>
+        <v>0.2233262146861701</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2178,22 +2178,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1373326180175325</v>
+        <v>0.1392326180175325</v>
       </c>
       <c r="C10">
-        <v>9.990388270053195</v>
+        <v>9.643808377745007</v>
       </c>
       <c r="D10">
-        <v>10.7398282700532</v>
+        <v>10.52142837774501</v>
       </c>
       <c r="E10">
-        <v>0.3074399999999999</v>
+        <v>0.4356199999999999</v>
       </c>
       <c r="F10">
-        <v>1.02544</v>
+        <v>1.15362</v>
       </c>
       <c r="G10">
         <v>0.276</v>
@@ -2214,37 +2214,37 @@
         <v>0.054</v>
       </c>
       <c r="M10">
-        <v>0.241798752</v>
+        <v>0.272023596</v>
       </c>
       <c r="N10">
-        <v>-0.187798752</v>
+        <v>-0.218023596</v>
       </c>
       <c r="O10">
-        <v>-0.046949688</v>
+        <v>-0.054505899</v>
       </c>
       <c r="P10">
-        <v>-0.140849064</v>
+        <v>-0.163517697</v>
       </c>
       <c r="Q10">
-        <v>-0.09084906400000001</v>
+        <v>-0.113517697</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1299150265717309</v>
+        <v>0.1308393675230687</v>
       </c>
       <c r="T10">
-        <v>0.8134565945826154</v>
+        <v>0.8223956780395673</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>0.05583155367154253</v>
+        <v>0.0496280477080378</v>
       </c>
       <c r="W10">
-        <v>0.2226349196442503</v>
+        <v>0.2240977063504447</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.2233262146861701</v>
+        <v>0.1985121908321512</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2260,22 +2260,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1392326180175325</v>
+        <v>0.1411326180175325</v>
       </c>
       <c r="C11">
-        <v>9.643808377745007</v>
+        <v>9.305934001009872</v>
       </c>
       <c r="D11">
-        <v>10.52142837774501</v>
+        <v>10.31173400100987</v>
       </c>
       <c r="E11">
-        <v>0.4356199999999999</v>
+        <v>0.5637999999999999</v>
       </c>
       <c r="F11">
-        <v>1.15362</v>
+        <v>1.2818</v>
       </c>
       <c r="G11">
         <v>0.276</v>
@@ -2296,37 +2296,37 @@
         <v>0.054</v>
       </c>
       <c r="M11">
-        <v>0.272023596</v>
+        <v>0.30224844</v>
       </c>
       <c r="N11">
-        <v>-0.218023596</v>
+        <v>-0.24824844</v>
       </c>
       <c r="O11">
-        <v>-0.054505899</v>
+        <v>-0.06206210999999999</v>
       </c>
       <c r="P11">
-        <v>-0.163517697</v>
+        <v>-0.18618633</v>
       </c>
       <c r="Q11">
-        <v>-0.113517697</v>
+        <v>-0.13618633</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1308393675230687</v>
+        <v>0.1317842493844361</v>
       </c>
       <c r="T11">
-        <v>0.8223956780395673</v>
+        <v>0.8315334077955623</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.0496280477080378</v>
+        <v>0.04466524293723403</v>
       </c>
       <c r="W11">
-        <v>0.2240977063504447</v>
+        <v>0.2252679357154002</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.1985121908321512</v>
+        <v>0.178660971748936</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2342,22 +2342,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1411326180175325</v>
+        <v>0.1430326180175325</v>
       </c>
       <c r="C12">
-        <v>9.305934001009872</v>
+        <v>8.97625480247563</v>
       </c>
       <c r="D12">
-        <v>10.31173400100987</v>
+        <v>10.11023480247563</v>
       </c>
       <c r="E12">
-        <v>0.5638000000000001</v>
+        <v>0.69198</v>
       </c>
       <c r="F12">
-        <v>1.2818</v>
+        <v>1.40998</v>
       </c>
       <c r="G12">
         <v>0.276</v>
@@ -2378,37 +2378,37 @@
         <v>0.054</v>
       </c>
       <c r="M12">
-        <v>0.30224844</v>
+        <v>0.332473284</v>
       </c>
       <c r="N12">
-        <v>-0.24824844</v>
+        <v>-0.278473284</v>
       </c>
       <c r="O12">
-        <v>-0.06206211</v>
+        <v>-0.06961832100000001</v>
       </c>
       <c r="P12">
-        <v>-0.18618633</v>
+        <v>-0.208854963</v>
       </c>
       <c r="Q12">
-        <v>-0.13618633</v>
+        <v>-0.158854963</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1317842493844361</v>
+        <v>0.1327503645460589</v>
       </c>
       <c r="T12">
-        <v>0.8315334077955623</v>
+        <v>0.8408764797932653</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.04466524293723402</v>
+        <v>0.04060476630657638</v>
       </c>
       <c r="W12">
-        <v>0.2252679357154002</v>
+        <v>0.2262253961049093</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.178660971748936</v>
+        <v>0.1624190652263054</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2424,22 +2424,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1430326180175325</v>
+        <v>0.1449326180175325</v>
       </c>
       <c r="C13">
-        <v>8.97625480247563</v>
+        <v>8.65429956977365</v>
       </c>
       <c r="D13">
-        <v>10.11023480247563</v>
+        <v>9.91645956977365</v>
       </c>
       <c r="E13">
-        <v>0.69198</v>
+        <v>0.82016</v>
       </c>
       <c r="F13">
-        <v>1.40998</v>
+        <v>1.53816</v>
       </c>
       <c r="G13">
         <v>0.276</v>
@@ -2460,37 +2460,37 @@
         <v>0.054</v>
       </c>
       <c r="M13">
-        <v>0.332473284</v>
+        <v>0.362698128</v>
       </c>
       <c r="N13">
-        <v>-0.278473284</v>
+        <v>-0.308698128</v>
       </c>
       <c r="O13">
-        <v>-0.06961832100000001</v>
+        <v>-0.077174532</v>
       </c>
       <c r="P13">
-        <v>-0.208854963</v>
+        <v>-0.231523596</v>
       </c>
       <c r="Q13">
-        <v>-0.158854963</v>
+        <v>-0.181523596</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1327503645460589</v>
+        <v>0.133738436870446</v>
       </c>
       <c r="T13">
-        <v>0.8408764797932653</v>
+        <v>0.8504318943363706</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.04060476630657638</v>
+        <v>0.03722103578102835</v>
       </c>
       <c r="W13">
-        <v>0.2262253961049093</v>
+        <v>0.2270232797628335</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.1624190652263054</v>
+        <v>0.1488841431241134</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2506,22 +2506,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1449326180175325</v>
+        <v>0.1468326180175325</v>
       </c>
       <c r="C14">
-        <v>8.65429956977365</v>
+        <v>8.339632536652323</v>
       </c>
       <c r="D14">
-        <v>9.91645956977365</v>
+        <v>9.729972536652323</v>
       </c>
       <c r="E14">
-        <v>0.82016</v>
+        <v>0.94834</v>
       </c>
       <c r="F14">
-        <v>1.53816</v>
+        <v>1.66634</v>
       </c>
       <c r="G14">
         <v>0.276</v>
@@ -2542,37 +2542,37 @@
         <v>0.054</v>
       </c>
       <c r="M14">
-        <v>0.362698128</v>
+        <v>0.392922972</v>
       </c>
       <c r="N14">
-        <v>-0.308698128</v>
+        <v>-0.338922972</v>
       </c>
       <c r="O14">
-        <v>-0.077174532</v>
+        <v>-0.084730743</v>
       </c>
       <c r="P14">
-        <v>-0.231523596</v>
+        <v>-0.254192229</v>
       </c>
       <c r="Q14">
-        <v>-0.181523596</v>
+        <v>-0.204192229</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.133738436870446</v>
+        <v>0.1347492235011408</v>
       </c>
       <c r="T14">
-        <v>0.8504318943363706</v>
+        <v>0.8602069735816164</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.03722103578102835</v>
+        <v>0.03435787918248771</v>
       </c>
       <c r="W14">
-        <v>0.2270232797628335</v>
+        <v>0.2276984120887694</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.1488841431241134</v>
+        <v>0.1374315167299508</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2588,22 +2588,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1468326180175325</v>
+        <v>0.1487326180175325</v>
       </c>
       <c r="C15">
-        <v>8.339632536652323</v>
+        <v>8.031850111534849</v>
       </c>
       <c r="D15">
-        <v>9.729972536652323</v>
+        <v>9.55037011153485</v>
       </c>
       <c r="E15">
-        <v>0.94834</v>
+        <v>1.07652</v>
       </c>
       <c r="F15">
-        <v>1.66634</v>
+        <v>1.79452</v>
       </c>
       <c r="G15">
         <v>0.276</v>
@@ -2624,37 +2624,37 @@
         <v>0.054</v>
       </c>
       <c r="M15">
-        <v>0.392922972</v>
+        <v>0.4231478160000001</v>
       </c>
       <c r="N15">
-        <v>-0.338922972</v>
+        <v>-0.3691478160000001</v>
       </c>
       <c r="O15">
-        <v>-0.084730743</v>
+        <v>-0.09228695400000002</v>
       </c>
       <c r="P15">
-        <v>-0.254192229</v>
+        <v>-0.276860862</v>
       </c>
       <c r="Q15">
-        <v>-0.204192229</v>
+        <v>-0.2268608620000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1347492235011408</v>
+        <v>0.1357835167976656</v>
       </c>
       <c r="T15">
-        <v>0.8602069735816164</v>
+        <v>0.8702093802511699</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.03435787918248771</v>
+        <v>0.03190374495516715</v>
       </c>
       <c r="W15">
-        <v>0.2276984120887694</v>
+        <v>0.2282770969395716</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.1374315167299508</v>
+        <v>0.1276149798206686</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2670,22 +2670,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1487326180175325</v>
+        <v>0.1506326180175325</v>
       </c>
       <c r="C16">
-        <v>8.031850111534849</v>
+        <v>7.730577961829294</v>
       </c>
       <c r="D16">
-        <v>9.55037011153485</v>
+        <v>9.377277961829295</v>
       </c>
       <c r="E16">
-        <v>1.07652</v>
+        <v>1.2047</v>
       </c>
       <c r="F16">
-        <v>1.79452</v>
+        <v>1.9227</v>
       </c>
       <c r="G16">
         <v>0.276</v>
@@ -2706,37 +2706,37 @@
         <v>0.054</v>
       </c>
       <c r="M16">
-        <v>0.4231478160000001</v>
+        <v>0.4533726600000001</v>
       </c>
       <c r="N16">
-        <v>-0.3691478160000001</v>
+        <v>-0.3993726600000001</v>
       </c>
       <c r="O16">
-        <v>-0.09228695400000002</v>
+        <v>-0.09984316500000003</v>
       </c>
       <c r="P16">
-        <v>-0.276860862</v>
+        <v>-0.2995294950000001</v>
       </c>
       <c r="Q16">
-        <v>-0.2268608620000001</v>
+        <v>-0.2495294950000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1357835167976656</v>
+        <v>0.1368421464070499</v>
       </c>
       <c r="T16">
-        <v>0.8702093802511699</v>
+        <v>0.8804471376658896</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.03190374495516715</v>
+        <v>0.02977682862482267</v>
       </c>
       <c r="W16">
-        <v>0.2282770969395716</v>
+        <v>0.2287786238102668</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.1276149798206686</v>
+        <v>0.1191073144992907</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2752,22 +2752,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1506326180175325</v>
+        <v>0.1525326180175325</v>
       </c>
       <c r="C17">
-        <v>7.730577961829295</v>
+        <v>7.435468409660444</v>
       </c>
       <c r="D17">
-        <v>9.377277961829295</v>
+        <v>9.210348409660444</v>
       </c>
       <c r="E17">
-        <v>1.2047</v>
+        <v>1.33288</v>
       </c>
       <c r="F17">
-        <v>1.9227</v>
+        <v>2.05088</v>
       </c>
       <c r="G17">
         <v>0.276</v>
@@ -2788,37 +2788,37 @@
         <v>0.054</v>
       </c>
       <c r="M17">
-        <v>0.45337266</v>
+        <v>0.483597504</v>
       </c>
       <c r="N17">
-        <v>-0.39937266</v>
+        <v>-0.429597504</v>
       </c>
       <c r="O17">
-        <v>-0.099843165</v>
+        <v>-0.107399376</v>
       </c>
       <c r="P17">
-        <v>-0.299529495</v>
+        <v>-0.322198128</v>
       </c>
       <c r="Q17">
-        <v>-0.249529495</v>
+        <v>-0.272198128</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1368421464070499</v>
+        <v>0.1379259814833244</v>
       </c>
       <c r="T17">
-        <v>0.8804471376658896</v>
+        <v>0.8909286512095311</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.02977682862482268</v>
+        <v>0.02791577683577126</v>
       </c>
       <c r="W17">
-        <v>0.2287786238102668</v>
+        <v>0.2292174598221251</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.1191073144992907</v>
+        <v>0.111663107343085</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2834,22 +2834,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1525326180175325</v>
+        <v>0.1544326180175325</v>
       </c>
       <c r="C18">
-        <v>7.435468409660444</v>
+        <v>7.146198100895807</v>
       </c>
       <c r="D18">
-        <v>9.210348409660444</v>
+        <v>9.049258100895807</v>
       </c>
       <c r="E18">
-        <v>1.33288</v>
+        <v>1.46106</v>
       </c>
       <c r="F18">
-        <v>2.05088</v>
+        <v>2.17906</v>
       </c>
       <c r="G18">
         <v>0.276</v>
@@ -2870,37 +2870,37 @@
         <v>0.054</v>
       </c>
       <c r="M18">
-        <v>0.483597504</v>
+        <v>0.513822348</v>
       </c>
       <c r="N18">
-        <v>-0.429597504</v>
+        <v>-0.459822348</v>
       </c>
       <c r="O18">
-        <v>-0.107399376</v>
+        <v>-0.114955587</v>
       </c>
       <c r="P18">
-        <v>-0.322198128</v>
+        <v>-0.344866761</v>
       </c>
       <c r="Q18">
-        <v>-0.272198128</v>
+        <v>-0.294866761</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1379259814833244</v>
+        <v>0.1390359330674608</v>
       </c>
       <c r="T18">
-        <v>0.8909286512095311</v>
+        <v>0.9016627313445857</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.02791577683577126</v>
+        <v>0.02627367231602001</v>
       </c>
       <c r="W18">
-        <v>0.2292174598221251</v>
+        <v>0.2296046680678825</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.111663107343085</v>
+        <v>0.1050946892640801</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2916,22 +2916,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1544326180175325</v>
+        <v>0.1563326180175325</v>
       </c>
       <c r="C19">
-        <v>7.146198100895807</v>
+        <v>6.862465914581225</v>
       </c>
       <c r="D19">
-        <v>9.049258100895807</v>
+        <v>8.893705914581226</v>
       </c>
       <c r="E19">
-        <v>1.46106</v>
+        <v>1.58924</v>
       </c>
       <c r="F19">
-        <v>2.17906</v>
+        <v>2.30724</v>
       </c>
       <c r="G19">
         <v>0.276</v>
@@ -2952,37 +2952,37 @@
         <v>0.054</v>
       </c>
       <c r="M19">
-        <v>0.513822348</v>
+        <v>0.5440471920000001</v>
       </c>
       <c r="N19">
-        <v>-0.459822348</v>
+        <v>-0.4900471920000001</v>
       </c>
       <c r="O19">
-        <v>-0.114955587</v>
+        <v>-0.122511798</v>
       </c>
       <c r="P19">
-        <v>-0.344866761</v>
+        <v>-0.3675353940000001</v>
       </c>
       <c r="Q19">
-        <v>-0.294866761</v>
+        <v>-0.3175353940000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1390359330674608</v>
+        <v>0.1401729566414542</v>
       </c>
       <c r="T19">
-        <v>0.9016627313445857</v>
+        <v>0.9126586183122026</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.02627367231602001</v>
+        <v>0.02481402385401889</v>
       </c>
       <c r="W19">
-        <v>0.2296046680678825</v>
+        <v>0.2299488531752223</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.1050946892640801</v>
+        <v>0.09925609541607561</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2998,22 +2998,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1563326180175325</v>
+        <v>0.1582326180175325</v>
       </c>
       <c r="C20">
-        <v>6.862465914581225</v>
+        <v>6.583991084347266</v>
       </c>
       <c r="D20">
-        <v>8.893705914581226</v>
+        <v>8.743411084347267</v>
       </c>
       <c r="E20">
-        <v>1.58924</v>
+        <v>1.71742</v>
       </c>
       <c r="F20">
-        <v>2.30724</v>
+        <v>2.43542</v>
       </c>
       <c r="G20">
         <v>0.276</v>
@@ -3034,37 +3034,37 @@
         <v>0.054</v>
       </c>
       <c r="M20">
-        <v>0.544047192</v>
+        <v>0.5742720360000001</v>
       </c>
       <c r="N20">
-        <v>-0.490047192</v>
+        <v>-0.520272036</v>
       </c>
       <c r="O20">
-        <v>-0.122511798</v>
+        <v>-0.130068009</v>
       </c>
       <c r="P20">
-        <v>-0.367535394</v>
+        <v>-0.390204027</v>
       </c>
       <c r="Q20">
-        <v>-0.317535394</v>
+        <v>-0.340204027</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1401729566414542</v>
+        <v>0.1413380548715956</v>
       </c>
       <c r="T20">
-        <v>0.9126586183122025</v>
+        <v>0.9239260086617359</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.0248140238540189</v>
+        <v>0.02350802259854422</v>
       </c>
       <c r="W20">
-        <v>0.2299488531752223</v>
+        <v>0.2302568082712633</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.09925609541607561</v>
+        <v>0.09403209039417693</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3080,22 +3080,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1582326180175325</v>
+        <v>0.1601326180175325</v>
       </c>
       <c r="C21">
-        <v>6.583991084347266</v>
+        <v>6.310511507128521</v>
       </c>
       <c r="D21">
-        <v>8.743411084347267</v>
+        <v>8.598111507128522</v>
       </c>
       <c r="E21">
-        <v>1.71742</v>
+        <v>1.8456</v>
       </c>
       <c r="F21">
-        <v>2.43542</v>
+        <v>2.5636</v>
       </c>
       <c r="G21">
         <v>0.276</v>
@@ -3116,37 +3116,37 @@
         <v>0.054</v>
       </c>
       <c r="M21">
-        <v>0.5742720360000001</v>
+        <v>0.60449688</v>
       </c>
       <c r="N21">
-        <v>-0.520272036</v>
+        <v>-0.55049688</v>
       </c>
       <c r="O21">
-        <v>-0.130068009</v>
+        <v>-0.13762422</v>
       </c>
       <c r="P21">
-        <v>-0.390204027</v>
+        <v>-0.41287266</v>
       </c>
       <c r="Q21">
-        <v>-0.340204027</v>
+        <v>-0.36287266</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1413380548715956</v>
+        <v>0.1425322805574906</v>
       </c>
       <c r="T21">
-        <v>0.9239260086617359</v>
+        <v>0.9354750837700075</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.02350802259854422</v>
+        <v>0.02233262146861701</v>
       </c>
       <c r="W21">
-        <v>0.2302568082712633</v>
+        <v>0.2305339678577001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.09403209039417693</v>
+        <v>0.08933048587446812</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3162,22 +3162,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1601326180175325</v>
+        <v>0.1620326180175325</v>
       </c>
       <c r="C22">
-        <v>6.310511507128521</v>
+        <v>6.041782217762261</v>
       </c>
       <c r="D22">
-        <v>8.598111507128522</v>
+        <v>8.457562217762261</v>
       </c>
       <c r="E22">
-        <v>1.8456</v>
+        <v>1.97378</v>
       </c>
       <c r="F22">
-        <v>2.5636</v>
+        <v>2.69178</v>
       </c>
       <c r="G22">
         <v>0.276</v>
@@ -3198,37 +3198,37 @@
         <v>0.054</v>
       </c>
       <c r="M22">
-        <v>0.60449688</v>
+        <v>0.634721724</v>
       </c>
       <c r="N22">
-        <v>-0.55049688</v>
+        <v>-0.580721724</v>
       </c>
       <c r="O22">
-        <v>-0.13762422</v>
+        <v>-0.145180431</v>
       </c>
       <c r="P22">
-        <v>-0.41287266</v>
+        <v>-0.435541293</v>
       </c>
       <c r="Q22">
-        <v>-0.36287266</v>
+        <v>-0.385541293</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1425322805574906</v>
+        <v>0.1437567398050537</v>
       </c>
       <c r="T22">
-        <v>0.9354750837700075</v>
+        <v>0.9473165405265901</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.02233262146861701</v>
+        <v>0.02126916330344477</v>
       </c>
       <c r="W22">
-        <v>0.2305339678577001</v>
+        <v>0.2307847312930477</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.08933048587446812</v>
+        <v>0.08507665321377911</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3244,22 +3244,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1620326180175325</v>
+        <v>0.1639326180175325</v>
       </c>
       <c r="C23">
-        <v>6.041782217762261</v>
+        <v>5.777574010790978</v>
       </c>
       <c r="D23">
-        <v>8.457562217762261</v>
+        <v>8.321534010790979</v>
       </c>
       <c r="E23">
-        <v>1.97378</v>
+        <v>2.10196</v>
       </c>
       <c r="F23">
-        <v>2.69178</v>
+        <v>2.81996</v>
       </c>
       <c r="G23">
         <v>0.276</v>
@@ -3280,37 +3280,37 @@
         <v>0.054</v>
       </c>
       <c r="M23">
-        <v>0.6347217239999999</v>
+        <v>0.6649465680000001</v>
       </c>
       <c r="N23">
-        <v>-0.5807217239999999</v>
+        <v>-0.610946568</v>
       </c>
       <c r="O23">
-        <v>-0.145180431</v>
+        <v>-0.152736642</v>
       </c>
       <c r="P23">
-        <v>-0.4355412929999999</v>
+        <v>-0.458209926</v>
       </c>
       <c r="Q23">
-        <v>-0.3855412929999999</v>
+        <v>-0.408209926</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1437567398050537</v>
+        <v>0.1450125954435801</v>
       </c>
       <c r="T23">
-        <v>0.9473165405265901</v>
+        <v>0.959461624379495</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.02126916330344477</v>
+        <v>0.02030238315328819</v>
       </c>
       <c r="W23">
-        <v>0.2307847312930477</v>
+        <v>0.2310126980524547</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.08507665321377922</v>
+        <v>0.08120953261315278</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3326,22 +3326,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1639326180175325</v>
+        <v>0.1658326180175325</v>
       </c>
       <c r="C24">
-        <v>5.777574010790978</v>
+        <v>5.517672193158099</v>
       </c>
       <c r="D24">
-        <v>8.321534010790979</v>
+        <v>8.189812193158099</v>
       </c>
       <c r="E24">
-        <v>2.10196</v>
+        <v>2.23014</v>
       </c>
       <c r="F24">
-        <v>2.81996</v>
+        <v>2.94814</v>
       </c>
       <c r="G24">
         <v>0.276</v>
@@ -3362,37 +3362,37 @@
         <v>0.054</v>
       </c>
       <c r="M24">
-        <v>0.6649465680000001</v>
+        <v>0.695171412</v>
       </c>
       <c r="N24">
-        <v>-0.610946568</v>
+        <v>-0.6411714119999999</v>
       </c>
       <c r="O24">
-        <v>-0.152736642</v>
+        <v>-0.160292853</v>
       </c>
       <c r="P24">
-        <v>-0.458209926</v>
+        <v>-0.480878559</v>
       </c>
       <c r="Q24">
-        <v>-0.408209926</v>
+        <v>-0.430878559</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1450125954435801</v>
+        <v>0.1463010707090811</v>
       </c>
       <c r="T24">
-        <v>0.959461624379495</v>
+        <v>0.9719221649558522</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.02030238315328819</v>
+        <v>0.01941967084227566</v>
       </c>
       <c r="W24">
-        <v>0.2310126980524547</v>
+        <v>0.2312208416153914</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.08120953261315278</v>
+        <v>0.07767868336910266</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3408,22 +3408,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1658326180175325</v>
+        <v>0.1677326180175325</v>
       </c>
       <c r="C25">
-        <v>5.517672193158099</v>
+        <v>5.261875453519465</v>
       </c>
       <c r="D25">
-        <v>8.189812193158099</v>
+        <v>8.062195453519465</v>
       </c>
       <c r="E25">
-        <v>2.23014</v>
+        <v>2.35832</v>
       </c>
       <c r="F25">
-        <v>2.94814</v>
+        <v>3.07632</v>
       </c>
       <c r="G25">
         <v>0.276</v>
@@ -3444,37 +3444,37 @@
         <v>0.054</v>
       </c>
       <c r="M25">
-        <v>0.695171412</v>
+        <v>0.725396256</v>
       </c>
       <c r="N25">
-        <v>-0.6411714119999999</v>
+        <v>-0.671396256</v>
       </c>
       <c r="O25">
-        <v>-0.160292853</v>
+        <v>-0.167849064</v>
       </c>
       <c r="P25">
-        <v>-0.480878559</v>
+        <v>-0.503547192</v>
       </c>
       <c r="Q25">
-        <v>-0.430878559</v>
+        <v>-0.453547192</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1463010707090811</v>
+        <v>0.1476234532184111</v>
       </c>
       <c r="T25">
-        <v>0.9719221649558522</v>
+        <v>0.9847106144947448</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.01941967084227566</v>
+        <v>0.01861051789051417</v>
       </c>
       <c r="W25">
-        <v>0.2312208416153914</v>
+        <v>0.2314116398814168</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.07767868336910266</v>
+        <v>0.07444207156205673</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3490,22 +3490,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1677326180175325</v>
+        <v>0.1696326180175325</v>
       </c>
       <c r="C26">
-        <v>5.261875453519465</v>
+        <v>5.009994835645761</v>
       </c>
       <c r="D26">
-        <v>8.062195453519465</v>
+        <v>7.938494835645761</v>
       </c>
       <c r="E26">
-        <v>2.35832</v>
+        <v>2.4865</v>
       </c>
       <c r="F26">
-        <v>3.07632</v>
+        <v>3.2045</v>
       </c>
       <c r="G26">
         <v>0.276</v>
@@ -3526,37 +3526,37 @@
         <v>0.054</v>
       </c>
       <c r="M26">
-        <v>0.725396256</v>
+        <v>0.7556211</v>
       </c>
       <c r="N26">
-        <v>-0.671396256</v>
+        <v>-0.7016211</v>
       </c>
       <c r="O26">
-        <v>-0.167849064</v>
+        <v>-0.175405275</v>
       </c>
       <c r="P26">
-        <v>-0.503547192</v>
+        <v>-0.526215825</v>
       </c>
       <c r="Q26">
-        <v>-0.453547192</v>
+        <v>-0.476215825</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1476234532184111</v>
+        <v>0.1489810992613233</v>
       </c>
       <c r="T26">
-        <v>0.9847106144947448</v>
+        <v>0.9978400893546748</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.01861051789051417</v>
+        <v>0.01786609717489361</v>
       </c>
       <c r="W26">
-        <v>0.2314116398814168</v>
+        <v>0.2315871742861601</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.07444207156205673</v>
+        <v>0.0714643886995745</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3572,22 +3572,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1696326180175325</v>
+        <v>0.1715326180175325</v>
       </c>
       <c r="C27">
-        <v>5.009994835645761</v>
+        <v>4.761852804905068</v>
       </c>
       <c r="D27">
-        <v>7.938494835645761</v>
+        <v>7.818532804905068</v>
       </c>
       <c r="E27">
-        <v>2.4865</v>
+        <v>2.61468</v>
       </c>
       <c r="F27">
-        <v>3.2045</v>
+        <v>3.33268</v>
       </c>
       <c r="G27">
         <v>0.276</v>
@@ -3608,37 +3608,37 @@
         <v>0.054</v>
       </c>
       <c r="M27">
-        <v>0.7556211</v>
+        <v>0.785845944</v>
       </c>
       <c r="N27">
-        <v>-0.7016211</v>
+        <v>-0.7318459439999999</v>
       </c>
       <c r="O27">
-        <v>-0.175405275</v>
+        <v>-0.182961486</v>
       </c>
       <c r="P27">
-        <v>-0.526215825</v>
+        <v>-0.548884458</v>
       </c>
       <c r="Q27">
-        <v>-0.476215825</v>
+        <v>-0.498884458</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1489810992613233</v>
+        <v>0.1503754384405304</v>
       </c>
       <c r="T27">
-        <v>0.9978400893546748</v>
+        <v>1.011324414886495</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.01786609717489361</v>
+        <v>0.01717893959124385</v>
       </c>
       <c r="W27">
-        <v>0.2315871742861601</v>
+        <v>0.2317492060443847</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.0714643886995745</v>
+        <v>0.06871575836497545</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3654,22 +3654,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1715326180175325</v>
+        <v>0.1734326180175325</v>
       </c>
       <c r="C28">
-        <v>4.761852804905068</v>
+        <v>4.517282398126142</v>
       </c>
       <c r="D28">
-        <v>7.818532804905068</v>
+        <v>7.702142398126142</v>
       </c>
       <c r="E28">
-        <v>2.61468</v>
+        <v>2.74286</v>
       </c>
       <c r="F28">
-        <v>3.33268</v>
+        <v>3.46086</v>
       </c>
       <c r="G28">
         <v>0.276</v>
@@ -3690,37 +3690,37 @@
         <v>0.054</v>
       </c>
       <c r="M28">
-        <v>0.785845944</v>
+        <v>0.8160707880000001</v>
       </c>
       <c r="N28">
-        <v>-0.7318459439999999</v>
+        <v>-0.7620707880000001</v>
       </c>
       <c r="O28">
-        <v>-0.182961486</v>
+        <v>-0.190517697</v>
       </c>
       <c r="P28">
-        <v>-0.548884458</v>
+        <v>-0.5715530910000001</v>
       </c>
       <c r="Q28">
-        <v>-0.498884458</v>
+        <v>-0.521553091</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1503754384405304</v>
+        <v>0.1518079786931404</v>
       </c>
       <c r="T28">
-        <v>1.011324414886495</v>
+        <v>1.025178173994529</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.01717893959124385</v>
+        <v>0.01654268256934593</v>
       </c>
       <c r="W28">
-        <v>0.2317492060443847</v>
+        <v>0.2318992354501483</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.06871575836497545</v>
+        <v>0.06617073027738374</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3736,22 +3736,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1734326180175325</v>
+        <v>0.1753326180175325</v>
       </c>
       <c r="C29">
-        <v>4.517282398126142</v>
+        <v>4.276126448281149</v>
       </c>
       <c r="D29">
-        <v>7.702142398126142</v>
+        <v>7.58916644828115</v>
       </c>
       <c r="E29">
-        <v>2.74286</v>
+        <v>2.87104</v>
       </c>
       <c r="F29">
-        <v>3.46086</v>
+        <v>3.58904</v>
       </c>
       <c r="G29">
         <v>0.276</v>
@@ -3772,37 +3772,37 @@
         <v>0.054</v>
       </c>
       <c r="M29">
-        <v>0.8160707880000001</v>
+        <v>0.8462956320000001</v>
       </c>
       <c r="N29">
-        <v>-0.7620707880000001</v>
+        <v>-0.7922956320000001</v>
       </c>
       <c r="O29">
-        <v>-0.190517697</v>
+        <v>-0.198073908</v>
       </c>
       <c r="P29">
-        <v>-0.5715530910000001</v>
+        <v>-0.5942217240000001</v>
       </c>
       <c r="Q29">
-        <v>-0.521553091</v>
+        <v>-0.544221724</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1518079786931404</v>
+        <v>0.1532803117305451</v>
       </c>
       <c r="T29">
-        <v>1.025178173994529</v>
+        <v>1.039416759744453</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.01654268256934593</v>
+        <v>0.01595187247758358</v>
       </c>
       <c r="W29">
-        <v>0.2318992354501483</v>
+        <v>0.2320385484697858</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.06617073027738374</v>
+        <v>0.06380748991033436</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3818,22 +3818,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1753326180175325</v>
+        <v>0.1772326180175325</v>
       </c>
       <c r="C30">
-        <v>4.276126448281149</v>
+        <v>4.038236876416646</v>
       </c>
       <c r="D30">
-        <v>7.58916644828115</v>
+        <v>7.479456876416647</v>
       </c>
       <c r="E30">
-        <v>2.87104</v>
+        <v>2.99922</v>
       </c>
       <c r="F30">
-        <v>3.58904</v>
+        <v>3.71722</v>
       </c>
       <c r="G30">
         <v>0.276</v>
@@ -3854,37 +3854,37 @@
         <v>0.054</v>
       </c>
       <c r="M30">
-        <v>0.8462956320000001</v>
+        <v>0.876520476</v>
       </c>
       <c r="N30">
-        <v>-0.7922956320000001</v>
+        <v>-0.822520476</v>
       </c>
       <c r="O30">
-        <v>-0.198073908</v>
+        <v>-0.205630119</v>
       </c>
       <c r="P30">
-        <v>-0.5942217240000001</v>
+        <v>-0.6168903569999999</v>
       </c>
       <c r="Q30">
-        <v>-0.544221724</v>
+        <v>-0.5668903569999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1532803117305451</v>
+        <v>0.1547941189380175</v>
       </c>
       <c r="T30">
-        <v>1.039416759744453</v>
+        <v>1.05405643241691</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.01595187247758358</v>
+        <v>0.01540180790939104</v>
       </c>
       <c r="W30">
-        <v>0.2320385484697858</v>
+        <v>0.2321682536949656</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.06380748991033436</v>
+        <v>0.06160723163756421</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3900,22 +3900,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1772326180175325</v>
+        <v>0.1791326180175325</v>
       </c>
       <c r="C31">
-        <v>4.038236876416647</v>
+        <v>3.803474044124831</v>
       </c>
       <c r="D31">
-        <v>7.479456876416647</v>
+        <v>7.372874044124831</v>
       </c>
       <c r="E31">
-        <v>2.99922</v>
+        <v>3.1274</v>
       </c>
       <c r="F31">
-        <v>3.71722</v>
+        <v>3.8454</v>
       </c>
       <c r="G31">
         <v>0.276</v>
@@ -3936,37 +3936,37 @@
         <v>0.054</v>
       </c>
       <c r="M31">
-        <v>0.8765204759999999</v>
+        <v>0.90674532</v>
       </c>
       <c r="N31">
-        <v>-0.8225204759999999</v>
+        <v>-0.8527453199999999</v>
       </c>
       <c r="O31">
-        <v>-0.205630119</v>
+        <v>-0.21318633</v>
       </c>
       <c r="P31">
-        <v>-0.6168903569999999</v>
+        <v>-0.6395589899999999</v>
       </c>
       <c r="Q31">
-        <v>-0.5668903569999999</v>
+        <v>-0.5895589899999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1547941189380175</v>
+        <v>0.1563511777799892</v>
       </c>
       <c r="T31">
-        <v>1.05405643241691</v>
+        <v>1.069114381451437</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.01540180790939104</v>
+        <v>0.01488841431241134</v>
       </c>
       <c r="W31">
-        <v>0.2321682536949656</v>
+        <v>0.2322893119051334</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.06160723163756421</v>
+        <v>0.05955365724964545</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3982,22 +3982,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1791326180175325</v>
+        <v>0.1810326180175325</v>
       </c>
       <c r="C32">
-        <v>3.803474044124831</v>
+        <v>3.571706160600895</v>
       </c>
       <c r="D32">
-        <v>7.372874044124831</v>
+        <v>7.269286160600894</v>
       </c>
       <c r="E32">
-        <v>3.1274</v>
+        <v>3.25558</v>
       </c>
       <c r="F32">
-        <v>3.8454</v>
+        <v>3.97358</v>
       </c>
       <c r="G32">
         <v>0.276</v>
@@ -4018,37 +4018,37 @@
         <v>0.054</v>
       </c>
       <c r="M32">
-        <v>0.90674532</v>
+        <v>0.936970164</v>
       </c>
       <c r="N32">
-        <v>-0.8527453199999999</v>
+        <v>-0.8829701639999999</v>
       </c>
       <c r="O32">
-        <v>-0.21318633</v>
+        <v>-0.220742541</v>
       </c>
       <c r="P32">
-        <v>-0.6395589899999999</v>
+        <v>-0.6622276229999999</v>
       </c>
       <c r="Q32">
-        <v>-0.5895589899999999</v>
+        <v>-0.6122276229999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1563511777799892</v>
+        <v>0.1579533687623079</v>
       </c>
       <c r="T32">
-        <v>1.069114381451437</v>
+        <v>1.08460879277682</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.01488841431241134</v>
+        <v>0.01440814288297871</v>
       </c>
       <c r="W32">
-        <v>0.2322893119051334</v>
+        <v>0.2324025599081936</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.05955365724964545</v>
+        <v>0.05763257153191492</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4064,22 +4064,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1810326180175325</v>
+        <v>0.1829326180175325</v>
       </c>
       <c r="C33">
-        <v>3.571706160600895</v>
+        <v>3.342808738992449</v>
       </c>
       <c r="D33">
-        <v>7.269286160600894</v>
+        <v>7.168568738992449</v>
       </c>
       <c r="E33">
-        <v>3.25558</v>
+        <v>3.38376</v>
       </c>
       <c r="F33">
-        <v>3.97358</v>
+        <v>4.10176</v>
       </c>
       <c r="G33">
         <v>0.276</v>
@@ -4100,37 +4100,37 @@
         <v>0.054</v>
       </c>
       <c r="M33">
-        <v>0.936970164</v>
+        <v>0.9671950079999999</v>
       </c>
       <c r="N33">
-        <v>-0.8829701639999999</v>
+        <v>-0.9131950079999999</v>
       </c>
       <c r="O33">
-        <v>-0.220742541</v>
+        <v>-0.228298752</v>
       </c>
       <c r="P33">
-        <v>-0.6622276229999999</v>
+        <v>-0.6848962559999999</v>
       </c>
       <c r="Q33">
-        <v>-0.6122276229999999</v>
+        <v>-0.6348962559999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1579533687623079</v>
+        <v>0.1596026830088124</v>
       </c>
       <c r="T33">
-        <v>1.08460879277682</v>
+        <v>1.100558922082362</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.01440814288297871</v>
+        <v>0.01395788841788563</v>
       </c>
       <c r="W33">
-        <v>0.2324025599081936</v>
+        <v>0.2325087299110626</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.05763257153191492</v>
+        <v>0.05583155367154258</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4146,22 +4146,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1829326180175325</v>
+        <v>0.1848326180175325</v>
       </c>
       <c r="C34">
-        <v>3.342808738992449</v>
+        <v>3.11666409732564</v>
       </c>
       <c r="D34">
-        <v>7.168568738992449</v>
+        <v>7.07060409732564</v>
       </c>
       <c r="E34">
-        <v>3.38376</v>
+        <v>3.51194</v>
       </c>
       <c r="F34">
-        <v>4.10176</v>
+        <v>4.22994</v>
       </c>
       <c r="G34">
         <v>0.276</v>
@@ -4182,37 +4182,37 @@
         <v>0.054</v>
       </c>
       <c r="M34">
-        <v>0.9671950079999999</v>
+        <v>0.9974198520000001</v>
       </c>
       <c r="N34">
-        <v>-0.9131950079999999</v>
+        <v>-0.943419852</v>
       </c>
       <c r="O34">
-        <v>-0.228298752</v>
+        <v>-0.235854963</v>
       </c>
       <c r="P34">
-        <v>-0.6848962559999999</v>
+        <v>-0.707564889</v>
       </c>
       <c r="Q34">
-        <v>-0.6348962559999999</v>
+        <v>-0.657564889</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1596026830088124</v>
+        <v>0.1613012305164067</v>
       </c>
       <c r="T34">
-        <v>1.100558922082362</v>
+        <v>1.116985174650756</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.01395788841788563</v>
+        <v>0.01353492210219213</v>
       </c>
       <c r="W34">
-        <v>0.2325087299110626</v>
+        <v>0.2326084653683031</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.05583155367154258</v>
+        <v>0.05413968840876859</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4228,22 +4228,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1848326180175325</v>
+        <v>0.1867326180175325</v>
       </c>
       <c r="C35">
-        <v>3.11666409732564</v>
+        <v>2.893160899801221</v>
       </c>
       <c r="D35">
-        <v>7.07060409732564</v>
+        <v>6.975280899801222</v>
       </c>
       <c r="E35">
-        <v>3.51194</v>
+        <v>3.64012</v>
       </c>
       <c r="F35">
-        <v>4.22994</v>
+        <v>4.35812</v>
       </c>
       <c r="G35">
         <v>0.276</v>
@@ -4264,37 +4264,37 @@
         <v>0.054</v>
       </c>
       <c r="M35">
-        <v>0.9974198520000001</v>
+        <v>1.027644696</v>
       </c>
       <c r="N35">
-        <v>-0.943419852</v>
+        <v>-0.973644696</v>
       </c>
       <c r="O35">
-        <v>-0.235854963</v>
+        <v>-0.243411174</v>
       </c>
       <c r="P35">
-        <v>-0.707564889</v>
+        <v>-0.730233522</v>
       </c>
       <c r="Q35">
-        <v>-0.657564889</v>
+        <v>-0.680233522</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1613012305164067</v>
+        <v>0.1630512491605947</v>
       </c>
       <c r="T35">
-        <v>1.116985174650756</v>
+        <v>1.133909192448494</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.01353492210219213</v>
+        <v>0.01313683615801001</v>
       </c>
       <c r="W35">
-        <v>0.2326084653683031</v>
+        <v>0.2327023340339412</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.05413968840876859</v>
+        <v>0.05254734463204003</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4310,22 +4310,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1867326180175325</v>
+        <v>0.1886326180175324</v>
       </c>
       <c r="C36">
-        <v>2.893160899801221</v>
+        <v>2.672193734701474</v>
       </c>
       <c r="D36">
-        <v>6.975280899801222</v>
+        <v>6.882493734701474</v>
       </c>
       <c r="E36">
-        <v>3.64012</v>
+        <v>3.7683</v>
       </c>
       <c r="F36">
-        <v>4.35812</v>
+        <v>4.4863</v>
       </c>
       <c r="G36">
         <v>0.276</v>
@@ -4346,37 +4346,37 @@
         <v>0.054</v>
       </c>
       <c r="M36">
-        <v>1.027644696</v>
+        <v>1.05786954</v>
       </c>
       <c r="N36">
-        <v>-0.973644696</v>
+        <v>-1.00386954</v>
       </c>
       <c r="O36">
-        <v>-0.243411174</v>
+        <v>-0.250967385</v>
       </c>
       <c r="P36">
-        <v>-0.730233522</v>
+        <v>-0.7529021549999999</v>
       </c>
       <c r="Q36">
-        <v>-0.680233522</v>
+        <v>-0.7029021549999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1630512491605947</v>
+        <v>0.1648551145322961</v>
       </c>
       <c r="T36">
-        <v>1.133909192448494</v>
+        <v>1.151353949255394</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.01313683615801001</v>
+        <v>0.01276149798206686</v>
       </c>
       <c r="W36">
-        <v>0.2327023340339412</v>
+        <v>0.2327908387758287</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.05254734463204003</v>
+        <v>0.05104599192826753</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4392,22 +4392,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1886326180175324</v>
+        <v>0.1905326180175325</v>
       </c>
       <c r="C37">
-        <v>2.672193734701474</v>
+        <v>2.453662725543682</v>
       </c>
       <c r="D37">
-        <v>6.882493734701474</v>
+        <v>6.792142725543683</v>
       </c>
       <c r="E37">
-        <v>3.7683</v>
+        <v>3.89648</v>
       </c>
       <c r="F37">
-        <v>4.4863</v>
+        <v>4.61448</v>
       </c>
       <c r="G37">
         <v>0.276</v>
@@ -4428,37 +4428,37 @@
         <v>0.054</v>
       </c>
       <c r="M37">
-        <v>1.05786954</v>
+        <v>1.088094384</v>
       </c>
       <c r="N37">
-        <v>-1.00386954</v>
+        <v>-1.034094384</v>
       </c>
       <c r="O37">
-        <v>-0.250967385</v>
+        <v>-0.258523596</v>
       </c>
       <c r="P37">
-        <v>-0.7529021549999999</v>
+        <v>-0.775570788</v>
       </c>
       <c r="Q37">
-        <v>-0.7029021549999999</v>
+        <v>-0.725570788</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1648551145322961</v>
+        <v>0.1667153506968632</v>
       </c>
       <c r="T37">
-        <v>1.151353949255394</v>
+        <v>1.16934385471251</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.01276149798206686</v>
+        <v>0.01240701192700945</v>
       </c>
       <c r="W37">
-        <v>0.2327908387758287</v>
+        <v>0.2328744265876112</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.05104599192826753</v>
+        <v>0.04962804770803786</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4474,22 +4474,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1905326180175325</v>
+        <v>0.1924326180175325</v>
       </c>
       <c r="C38">
-        <v>2.453662725543683</v>
+        <v>2.237473172464641</v>
       </c>
       <c r="D38">
-        <v>6.792142725543683</v>
+        <v>6.704133172464641</v>
       </c>
       <c r="E38">
-        <v>3.896479999999999</v>
+        <v>4.02466</v>
       </c>
       <c r="F38">
-        <v>4.614479999999999</v>
+        <v>4.74266</v>
       </c>
       <c r="G38">
         <v>0.276</v>
@@ -4510,37 +4510,37 @@
         <v>0.054</v>
       </c>
       <c r="M38">
-        <v>1.088094384</v>
+        <v>1.118319228</v>
       </c>
       <c r="N38">
-        <v>-1.034094384</v>
+        <v>-1.064319228</v>
       </c>
       <c r="O38">
-        <v>-0.258523596</v>
+        <v>-0.266079807</v>
       </c>
       <c r="P38">
-        <v>-0.7755707879999999</v>
+        <v>-0.798239421</v>
       </c>
       <c r="Q38">
-        <v>-0.7255707879999999</v>
+        <v>-0.748239421</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1667153506968632</v>
+        <v>0.1686346419777658</v>
       </c>
       <c r="T38">
-        <v>1.16934385471251</v>
+        <v>1.187904868279375</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.01240701192700945</v>
+        <v>0.01207168728033352</v>
       </c>
       <c r="W38">
-        <v>0.2328744265876112</v>
+        <v>0.2329534961392974</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.04962804770803786</v>
+        <v>0.04828674912133413</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4556,22 +4556,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1924326180175325</v>
+        <v>0.1943326180175325</v>
       </c>
       <c r="C39">
-        <v>2.237473172464641</v>
+        <v>2.023535221129134</v>
       </c>
       <c r="D39">
-        <v>6.704133172464641</v>
+        <v>6.618375221129134</v>
       </c>
       <c r="E39">
-        <v>4.02466</v>
+        <v>4.15284</v>
       </c>
       <c r="F39">
-        <v>4.74266</v>
+        <v>4.87084</v>
       </c>
       <c r="G39">
         <v>0.276</v>
@@ -4592,37 +4592,37 @@
         <v>0.054</v>
       </c>
       <c r="M39">
-        <v>1.118319228</v>
+        <v>1.148544072</v>
       </c>
       <c r="N39">
-        <v>-1.064319228</v>
+        <v>-1.094544072</v>
       </c>
       <c r="O39">
-        <v>-0.266079807</v>
+        <v>-0.273636018</v>
       </c>
       <c r="P39">
-        <v>-0.798239421</v>
+        <v>-0.8209080540000001</v>
       </c>
       <c r="Q39">
-        <v>-0.748239421</v>
+        <v>-0.7709080540000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1686346419777658</v>
+        <v>0.170615845880633</v>
       </c>
       <c r="T39">
-        <v>1.187904868279375</v>
+        <v>1.207064624219365</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.01207168728033352</v>
+        <v>0.01175401129927211</v>
       </c>
       <c r="W39">
-        <v>0.2329534961392974</v>
+        <v>0.2330284041356316</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.04828674912133413</v>
+        <v>0.04701604519708846</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4638,22 +4638,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1943326180175325</v>
+        <v>0.1962326180175325</v>
       </c>
       <c r="C40">
-        <v>2.023535221129134</v>
+        <v>1.811763556729066</v>
       </c>
       <c r="D40">
-        <v>6.618375221129134</v>
+        <v>6.534783556729066</v>
       </c>
       <c r="E40">
-        <v>4.15284</v>
+        <v>4.28102</v>
       </c>
       <c r="F40">
-        <v>4.87084</v>
+        <v>4.99902</v>
       </c>
       <c r="G40">
         <v>0.276</v>
@@ -4674,37 +4674,37 @@
         <v>0.054</v>
       </c>
       <c r="M40">
-        <v>1.148544072</v>
+        <v>1.178768916</v>
       </c>
       <c r="N40">
-        <v>-1.094544072</v>
+        <v>-1.124768916</v>
       </c>
       <c r="O40">
-        <v>-0.273636018</v>
+        <v>-0.281192229</v>
       </c>
       <c r="P40">
-        <v>-0.8209080540000001</v>
+        <v>-0.8435766870000001</v>
       </c>
       <c r="Q40">
-        <v>-0.7709080540000001</v>
+        <v>-0.7935766870000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.170615845880633</v>
+        <v>0.1726620072885122</v>
       </c>
       <c r="T40">
-        <v>1.207064624219365</v>
+        <v>1.226852568878699</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.01175401129927211</v>
+        <v>0.01145262639416257</v>
       </c>
       <c r="W40">
-        <v>0.2330284041356316</v>
+        <v>0.2330994706962565</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.04701604519708846</v>
+        <v>0.04581050557665034</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4720,22 +4720,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1962326180175325</v>
+        <v>0.1981326180175325</v>
       </c>
       <c r="C41">
-        <v>1.811763556729066</v>
+        <v>1.602077120882499</v>
       </c>
       <c r="D41">
-        <v>6.534783556729066</v>
+        <v>6.453277120882499</v>
       </c>
       <c r="E41">
-        <v>4.28102</v>
+        <v>4.4092</v>
       </c>
       <c r="F41">
-        <v>4.99902</v>
+        <v>5.1272</v>
       </c>
       <c r="G41">
         <v>0.276</v>
@@ -4756,37 +4756,37 @@
         <v>0.054</v>
       </c>
       <c r="M41">
-        <v>1.178768916</v>
+        <v>1.20899376</v>
       </c>
       <c r="N41">
-        <v>-1.124768916</v>
+        <v>-1.15499376</v>
       </c>
       <c r="O41">
-        <v>-0.281192229</v>
+        <v>-0.28874844</v>
       </c>
       <c r="P41">
-        <v>-0.8435766870000001</v>
+        <v>-0.86624532</v>
       </c>
       <c r="Q41">
-        <v>-0.7935766870000001</v>
+        <v>-0.8162453199999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1726620072885122</v>
+        <v>0.1747763740766541</v>
       </c>
       <c r="T41">
-        <v>1.226852568878699</v>
+        <v>1.247300111693344</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.01145262639416257</v>
+        <v>0.01116631073430851</v>
       </c>
       <c r="W41">
-        <v>0.2330994706962565</v>
+        <v>0.2331669839288501</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.04581050557665034</v>
+        <v>0.04466524293723406</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4802,22 +4802,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1981326180175325</v>
+        <v>0.2000326180175325</v>
       </c>
       <c r="C42">
-        <v>1.602077120882499</v>
+        <v>1.394398849457948</v>
       </c>
       <c r="D42">
-        <v>6.453277120882499</v>
+        <v>6.373778849457949</v>
       </c>
       <c r="E42">
-        <v>4.4092</v>
+        <v>4.537380000000001</v>
       </c>
       <c r="F42">
-        <v>5.1272</v>
+        <v>5.255380000000001</v>
       </c>
       <c r="G42">
         <v>0.276</v>
@@ -4838,37 +4838,37 @@
         <v>0.054</v>
       </c>
       <c r="M42">
-        <v>1.20899376</v>
+        <v>1.239218604</v>
       </c>
       <c r="N42">
-        <v>-1.15499376</v>
+        <v>-1.185218604</v>
       </c>
       <c r="O42">
-        <v>-0.28874844</v>
+        <v>-0.296304651</v>
       </c>
       <c r="P42">
-        <v>-0.86624532</v>
+        <v>-0.8889139530000001</v>
       </c>
       <c r="Q42">
-        <v>-0.8162453199999999</v>
+        <v>-0.838913953</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1747763740766541</v>
+        <v>0.1769624143152415</v>
       </c>
       <c r="T42">
-        <v>1.247300111693344</v>
+        <v>1.268440791552553</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.01116631073430851</v>
+        <v>0.0108939616920083</v>
       </c>
       <c r="W42">
-        <v>0.2331669839288501</v>
+        <v>0.2332312038330245</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.04466524293723406</v>
+        <v>0.04357584676803317</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4884,22 +4884,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2000326180175325</v>
+        <v>0.2019326180175325</v>
       </c>
       <c r="C43">
-        <v>1.394398849457948</v>
+        <v>1.188655429541362</v>
       </c>
       <c r="D43">
-        <v>6.373778849457949</v>
+        <v>6.296215429541363</v>
       </c>
       <c r="E43">
-        <v>4.537380000000001</v>
+        <v>4.66556</v>
       </c>
       <c r="F43">
-        <v>5.255380000000001</v>
+        <v>5.38356</v>
       </c>
       <c r="G43">
         <v>0.276</v>
@@ -4920,37 +4920,37 @@
         <v>0.054</v>
       </c>
       <c r="M43">
-        <v>1.239218604</v>
+        <v>1.269443448</v>
       </c>
       <c r="N43">
-        <v>-1.185218604</v>
+        <v>-1.215443448</v>
       </c>
       <c r="O43">
-        <v>-0.296304651</v>
+        <v>-0.303860862</v>
       </c>
       <c r="P43">
-        <v>-0.8889139530000001</v>
+        <v>-0.911582586</v>
       </c>
       <c r="Q43">
-        <v>-0.838913953</v>
+        <v>-0.8615825859999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1769624143152415</v>
+        <v>0.1792238352517111</v>
       </c>
       <c r="T43">
-        <v>1.268440791552553</v>
+        <v>1.290310460372424</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.0108939616920083</v>
+        <v>0.01063458165172238</v>
       </c>
       <c r="W43">
-        <v>0.2332312038330245</v>
+        <v>0.2332923656465239</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.04357584676803317</v>
+        <v>0.04253832660688961</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4966,22 +4966,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2019326180175325</v>
+        <v>0.2038326180175325</v>
       </c>
       <c r="C44">
-        <v>1.188655429541363</v>
+        <v>0.9847770739347919</v>
       </c>
       <c r="D44">
-        <v>6.296215429541363</v>
+        <v>6.220517073934792</v>
       </c>
       <c r="E44">
-        <v>4.665559999999999</v>
+        <v>4.79374</v>
       </c>
       <c r="F44">
-        <v>5.383559999999999</v>
+        <v>5.51174</v>
       </c>
       <c r="G44">
         <v>0.276</v>
@@ -5002,37 +5002,37 @@
         <v>0.054</v>
       </c>
       <c r="M44">
-        <v>1.269443448</v>
+        <v>1.299668292</v>
       </c>
       <c r="N44">
-        <v>-1.215443448</v>
+        <v>-1.245668292</v>
       </c>
       <c r="O44">
-        <v>-0.303860862</v>
+        <v>-0.311417073</v>
       </c>
       <c r="P44">
-        <v>-0.9115825859999999</v>
+        <v>-0.934251219</v>
       </c>
       <c r="Q44">
-        <v>-0.8615825859999998</v>
+        <v>-0.8842512189999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1792238352517111</v>
+        <v>0.1815646042912148</v>
       </c>
       <c r="T44">
-        <v>1.290310460372424</v>
+        <v>1.312947485992993</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.01063458165172239</v>
+        <v>0.01038726579935675</v>
       </c>
       <c r="W44">
-        <v>0.2332923656465239</v>
+        <v>0.2333506827245117</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.04253832660688961</v>
+        <v>0.04154906319742702</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5048,22 +5048,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2038326180175325</v>
+        <v>0.2057326180175325</v>
       </c>
       <c r="C45">
-        <v>0.9847770739347919</v>
+        <v>0.782697311728807</v>
       </c>
       <c r="D45">
-        <v>6.220517073934792</v>
+        <v>6.146617311728807</v>
       </c>
       <c r="E45">
-        <v>4.79374</v>
+        <v>4.92192</v>
       </c>
       <c r="F45">
-        <v>5.51174</v>
+        <v>5.63992</v>
       </c>
       <c r="G45">
         <v>0.276</v>
@@ -5084,37 +5084,37 @@
         <v>0.054</v>
       </c>
       <c r="M45">
-        <v>1.299668292</v>
+        <v>1.329893136</v>
       </c>
       <c r="N45">
-        <v>-1.245668292</v>
+        <v>-1.275893136</v>
       </c>
       <c r="O45">
-        <v>-0.311417073</v>
+        <v>-0.318973284</v>
       </c>
       <c r="P45">
-        <v>-0.934251219</v>
+        <v>-0.9569198520000001</v>
       </c>
       <c r="Q45">
-        <v>-0.8842512189999999</v>
+        <v>-0.906919852</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1815646042912148</v>
+        <v>0.1839889722249865</v>
       </c>
       <c r="T45">
-        <v>1.312947485992993</v>
+        <v>1.336392976814297</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.01038726579935675</v>
+        <v>0.01015119157664409</v>
       </c>
       <c r="W45">
-        <v>0.2333506827245117</v>
+        <v>0.2334063490262273</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.04154906319742702</v>
+        <v>0.04060476630657639</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5130,22 +5130,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2057326180175325</v>
+        <v>0.2076326180175325</v>
       </c>
       <c r="C46">
-        <v>0.782697311728807</v>
+        <v>0.5823527936276465</v>
       </c>
       <c r="D46">
-        <v>6.146617311728807</v>
+        <v>6.074452793627646</v>
       </c>
       <c r="E46">
-        <v>4.92192</v>
+        <v>5.0501</v>
       </c>
       <c r="F46">
-        <v>5.63992</v>
+        <v>5.7681</v>
       </c>
       <c r="G46">
         <v>0.276</v>
@@ -5166,37 +5166,37 @@
         <v>0.054</v>
       </c>
       <c r="M46">
-        <v>1.329893136</v>
+        <v>1.36011798</v>
       </c>
       <c r="N46">
-        <v>-1.275893136</v>
+        <v>-1.30611798</v>
       </c>
       <c r="O46">
-        <v>-0.318973284</v>
+        <v>-0.326529495</v>
       </c>
       <c r="P46">
-        <v>-0.9569198520000001</v>
+        <v>-0.9795884850000001</v>
       </c>
       <c r="Q46">
-        <v>-0.906919852</v>
+        <v>-0.929588485</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1839889722249865</v>
+        <v>0.1865014989927135</v>
       </c>
       <c r="T46">
-        <v>1.336392976814297</v>
+        <v>1.360691030938193</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.01015119157664409</v>
+        <v>0.009925609541607559</v>
       </c>
       <c r="W46">
-        <v>0.2334063490262273</v>
+        <v>0.2334595412700889</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.04060476630657639</v>
+        <v>0.03970243816643027</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5212,22 +5212,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2076326180175325</v>
+        <v>0.2095326180175325</v>
       </c>
       <c r="C47">
-        <v>0.5823527936276465</v>
+        <v>0.3836831108287253</v>
       </c>
       <c r="D47">
-        <v>6.074452793627646</v>
+        <v>6.003963110828725</v>
       </c>
       <c r="E47">
-        <v>5.0501</v>
+        <v>5.17828</v>
       </c>
       <c r="F47">
-        <v>5.7681</v>
+        <v>5.89628</v>
       </c>
       <c r="G47">
         <v>0.276</v>
@@ -5248,37 +5248,37 @@
         <v>0.054</v>
       </c>
       <c r="M47">
-        <v>1.36011798</v>
+        <v>1.390342824</v>
       </c>
       <c r="N47">
-        <v>-1.30611798</v>
+        <v>-1.336342824</v>
       </c>
       <c r="O47">
-        <v>-0.326529495</v>
+        <v>-0.334085706</v>
       </c>
       <c r="P47">
-        <v>-0.9795884850000001</v>
+        <v>-1.002257118</v>
       </c>
       <c r="Q47">
-        <v>-0.929588485</v>
+        <v>-0.9522571179999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1865014989927135</v>
+        <v>0.1891070823073935</v>
       </c>
       <c r="T47">
-        <v>1.360691030938193</v>
+        <v>1.385889012992604</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.009925609541607559</v>
+        <v>0.009709835421137829</v>
       </c>
       <c r="W47">
-        <v>0.2334595412700889</v>
+        <v>0.2335104208076957</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.03970243816643027</v>
+        <v>0.03883934168455139</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5294,22 +5294,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2095326180175325</v>
+        <v>0.2114326180175325</v>
       </c>
       <c r="C48">
-        <v>0.3836831108287253</v>
+        <v>0.1866306263681636</v>
       </c>
       <c r="D48">
-        <v>6.003963110828725</v>
+        <v>5.935090626368164</v>
       </c>
       <c r="E48">
-        <v>5.17828</v>
+        <v>5.30646</v>
       </c>
       <c r="F48">
-        <v>5.89628</v>
+        <v>6.02446</v>
       </c>
       <c r="G48">
         <v>0.276</v>
@@ -5330,37 +5330,37 @@
         <v>0.054</v>
       </c>
       <c r="M48">
-        <v>1.390342824</v>
+        <v>1.420567668</v>
       </c>
       <c r="N48">
-        <v>-1.336342824</v>
+        <v>-1.366567668</v>
       </c>
       <c r="O48">
-        <v>-0.334085706</v>
+        <v>-0.341641917</v>
       </c>
       <c r="P48">
-        <v>-1.002257118</v>
+        <v>-1.024925751</v>
       </c>
       <c r="Q48">
-        <v>-0.9522571179999999</v>
+        <v>-0.974925751</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1891070823073935</v>
+        <v>0.1918109895207405</v>
       </c>
       <c r="T48">
-        <v>1.385889012992604</v>
+        <v>1.412037862294351</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.009709835421137829</v>
+        <v>0.009503243178134897</v>
       </c>
       <c r="W48">
-        <v>0.2335104208076957</v>
+        <v>0.2335591352585958</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.03883934168455139</v>
+        <v>0.03801297271253967</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5376,22 +5376,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2114326180175325</v>
+        <v>0.2133326180175325</v>
       </c>
       <c r="C49">
-        <v>0.1866306263681636</v>
+        <v>-0.008859682057383189</v>
       </c>
       <c r="D49">
-        <v>5.935090626368164</v>
+        <v>5.867780317942617</v>
       </c>
       <c r="E49">
-        <v>5.30646</v>
+        <v>5.43464</v>
       </c>
       <c r="F49">
-        <v>6.02446</v>
+        <v>6.15264</v>
       </c>
       <c r="G49">
         <v>0.276</v>
@@ -5412,37 +5412,37 @@
         <v>0.054</v>
       </c>
       <c r="M49">
-        <v>1.420567668</v>
+        <v>1.450792512</v>
       </c>
       <c r="N49">
-        <v>-1.366567668</v>
+        <v>-1.396792512</v>
       </c>
       <c r="O49">
-        <v>-0.341641917</v>
+        <v>-0.349198128</v>
       </c>
       <c r="P49">
-        <v>-1.024925751</v>
+        <v>-1.047594384</v>
       </c>
       <c r="Q49">
-        <v>-0.974925751</v>
+        <v>-0.9975943839999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1918109895207405</v>
+        <v>0.1946188931653701</v>
       </c>
       <c r="T49">
-        <v>1.412037862294351</v>
+        <v>1.439192436569243</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.009503243178134897</v>
+        <v>0.009305258945257086</v>
       </c>
       <c r="W49">
-        <v>0.2335591352585958</v>
+        <v>0.2336058199407084</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.03801297271253967</v>
+        <v>0.03722103578102842</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5458,22 +5458,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2133326180175325</v>
+        <v>0.2152326180175325</v>
       </c>
       <c r="C50">
-        <v>-0.008859682057381413</v>
+        <v>-0.2028403686933951</v>
       </c>
       <c r="D50">
-        <v>5.867780317942619</v>
+        <v>5.801979631306605</v>
       </c>
       <c r="E50">
-        <v>5.43464</v>
+        <v>5.562819999999999</v>
       </c>
       <c r="F50">
-        <v>6.15264</v>
+        <v>6.280819999999999</v>
       </c>
       <c r="G50">
         <v>0.276</v>
@@ -5494,37 +5494,37 @@
         <v>0.054</v>
       </c>
       <c r="M50">
-        <v>1.450792512</v>
+        <v>1.481017356</v>
       </c>
       <c r="N50">
-        <v>-1.396792512</v>
+        <v>-1.427017356</v>
       </c>
       <c r="O50">
-        <v>-0.349198128</v>
+        <v>-0.356754339</v>
       </c>
       <c r="P50">
-        <v>-1.047594384</v>
+        <v>-1.070263017</v>
       </c>
       <c r="Q50">
-        <v>-0.9975943839999999</v>
+        <v>-1.020263017</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1946188931653701</v>
+        <v>0.1975369106784166</v>
       </c>
       <c r="T50">
-        <v>1.439192436569243</v>
+        <v>1.467411896109816</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.009305258945257086</v>
+        <v>0.00911535570147633</v>
       </c>
       <c r="W50">
-        <v>0.2336058199407084</v>
+        <v>0.2336505991255919</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.03722103578102842</v>
+        <v>0.03646142280590536</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5540,22 +5540,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2152326180175325</v>
+        <v>0.2171326180175325</v>
       </c>
       <c r="C51">
-        <v>-0.2028403686933951</v>
+        <v>-0.3953616565756279</v>
       </c>
       <c r="D51">
-        <v>5.801979631306605</v>
+        <v>5.737638343424372</v>
       </c>
       <c r="E51">
-        <v>5.562819999999999</v>
+        <v>5.691</v>
       </c>
       <c r="F51">
-        <v>6.280819999999999</v>
+        <v>6.409</v>
       </c>
       <c r="G51">
         <v>0.276</v>
@@ -5576,37 +5576,37 @@
         <v>0.054</v>
       </c>
       <c r="M51">
-        <v>1.481017356</v>
+        <v>1.5112422</v>
       </c>
       <c r="N51">
-        <v>-1.427017356</v>
+        <v>-1.4572422</v>
       </c>
       <c r="O51">
-        <v>-0.356754339</v>
+        <v>-0.36431055</v>
       </c>
       <c r="P51">
-        <v>-1.070263017</v>
+        <v>-1.09293165</v>
       </c>
       <c r="Q51">
-        <v>-1.020263017</v>
+        <v>-1.04293165</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1975369106784166</v>
+        <v>0.2005716488919849</v>
       </c>
       <c r="T51">
-        <v>1.467411896109816</v>
+        <v>1.496760134032012</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.00911535570147633</v>
+        <v>0.008933048587446804</v>
       </c>
       <c r="W51">
-        <v>0.2336505991255919</v>
+        <v>0.2336935871430801</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.03646142280590536</v>
+        <v>0.03573219434978725</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5622,22 +5622,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2171326180175325</v>
+        <v>0.2190326180175325</v>
       </c>
       <c r="C52">
-        <v>-0.3953616565756279</v>
+        <v>-0.5864715653726131</v>
       </c>
       <c r="D52">
-        <v>5.737638343424372</v>
+        <v>5.674708434627387</v>
       </c>
       <c r="E52">
-        <v>5.691</v>
+        <v>5.81918</v>
       </c>
       <c r="F52">
-        <v>6.409</v>
+        <v>6.53718</v>
       </c>
       <c r="G52">
         <v>0.276</v>
@@ -5658,37 +5658,37 @@
         <v>0.054</v>
       </c>
       <c r="M52">
-        <v>1.5112422</v>
+        <v>1.541467044</v>
       </c>
       <c r="N52">
-        <v>-1.4572422</v>
+        <v>-1.487467044</v>
       </c>
       <c r="O52">
-        <v>-0.36431055</v>
+        <v>-0.371866761</v>
       </c>
       <c r="P52">
-        <v>-1.09293165</v>
+        <v>-1.115600283</v>
       </c>
       <c r="Q52">
-        <v>-1.04293165</v>
+        <v>-1.065600283</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2005716488919849</v>
+        <v>0.2037302539714132</v>
       </c>
       <c r="T52">
-        <v>1.496760134032012</v>
+        <v>1.527306259216339</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.008933048587446804</v>
+        <v>0.008757890772006669</v>
       </c>
       <c r="W52">
-        <v>0.2336935871430801</v>
+        <v>0.2337348893559608</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.03573219434978725</v>
+        <v>0.03503156308802668</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5704,22 +5704,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2190326180175325</v>
+        <v>0.2209326180175325</v>
       </c>
       <c r="C53">
-        <v>-0.5864715653726131</v>
+        <v>-0.7762160309064567</v>
       </c>
       <c r="D53">
-        <v>5.674708434627387</v>
+        <v>5.613143969093543</v>
       </c>
       <c r="E53">
-        <v>5.81918</v>
+        <v>5.94736</v>
       </c>
       <c r="F53">
-        <v>6.53718</v>
+        <v>6.66536</v>
       </c>
       <c r="G53">
         <v>0.276</v>
@@ -5740,37 +5740,37 @@
         <v>0.054</v>
       </c>
       <c r="M53">
-        <v>1.541467044</v>
+        <v>1.571691888</v>
       </c>
       <c r="N53">
-        <v>-1.487467044</v>
+        <v>-1.517691888</v>
       </c>
       <c r="O53">
-        <v>-0.371866761</v>
+        <v>-0.379422972</v>
       </c>
       <c r="P53">
-        <v>-1.115600283</v>
+        <v>-1.138268916</v>
       </c>
       <c r="Q53">
-        <v>-1.065600283</v>
+        <v>-1.088268916</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2037302539714132</v>
+        <v>0.2070204675958176</v>
       </c>
       <c r="T53">
-        <v>1.527306259216339</v>
+        <v>1.559125139616679</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.008757890772006669</v>
+        <v>0.008589469795621927</v>
       </c>
       <c r="W53">
-        <v>0.2337348893559608</v>
+        <v>0.2337746030221924</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.03503156308802668</v>
+        <v>0.03435787918248778</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5786,22 +5786,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2209326180175325</v>
+        <v>0.2228326180175325</v>
       </c>
       <c r="C54">
-        <v>-0.7762160309064567</v>
+        <v>-0.9646390169770891</v>
       </c>
       <c r="D54">
-        <v>5.613143969093543</v>
+        <v>5.552900983022911</v>
       </c>
       <c r="E54">
-        <v>5.94736</v>
+        <v>6.07554</v>
       </c>
       <c r="F54">
-        <v>6.66536</v>
+        <v>6.79354</v>
       </c>
       <c r="G54">
         <v>0.276</v>
@@ -5822,37 +5822,37 @@
         <v>0.054</v>
       </c>
       <c r="M54">
-        <v>1.571691888</v>
+        <v>1.601916732</v>
       </c>
       <c r="N54">
-        <v>-1.517691888</v>
+        <v>-1.547916732</v>
       </c>
       <c r="O54">
-        <v>-0.379422972</v>
+        <v>-0.386979183</v>
       </c>
       <c r="P54">
-        <v>-1.138268916</v>
+        <v>-1.160937549</v>
       </c>
       <c r="Q54">
-        <v>-1.088268916</v>
+        <v>-1.110937549</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2070204675958176</v>
+        <v>0.2104506903106222</v>
       </c>
       <c r="T54">
-        <v>1.559125139616679</v>
+        <v>1.592298014927672</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.008589469795621927</v>
+        <v>0.008427404327780002</v>
       </c>
       <c r="W54">
-        <v>0.2337746030221924</v>
+        <v>0.2338128180595095</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.03435787918248778</v>
+        <v>0.03370961731111999</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5868,22 +5868,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2228326180175325</v>
+        <v>0.2247326180175325</v>
       </c>
       <c r="C55">
-        <v>-0.9646390169770891</v>
+        <v>-1.151782620062077</v>
       </c>
       <c r="D55">
-        <v>5.552900983022911</v>
+        <v>5.493937379937924</v>
       </c>
       <c r="E55">
-        <v>6.07554</v>
+        <v>6.203720000000001</v>
       </c>
       <c r="F55">
-        <v>6.79354</v>
+        <v>6.921720000000001</v>
       </c>
       <c r="G55">
         <v>0.276</v>
@@ -5904,37 +5904,37 @@
         <v>0.054</v>
       </c>
       <c r="M55">
-        <v>1.601916732</v>
+        <v>1.632141576</v>
       </c>
       <c r="N55">
-        <v>-1.547916732</v>
+        <v>-1.578141576</v>
       </c>
       <c r="O55">
-        <v>-0.386979183</v>
+        <v>-0.394535394</v>
       </c>
       <c r="P55">
-        <v>-1.160937549</v>
+        <v>-1.183606182</v>
       </c>
       <c r="Q55">
-        <v>-1.110937549</v>
+        <v>-1.133606182</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2104506903106222</v>
+        <v>0.2140300531434619</v>
       </c>
       <c r="T55">
-        <v>1.592298014927672</v>
+        <v>1.626913189165231</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.008427404327780002</v>
+        <v>0.008271341284672966</v>
       </c>
       <c r="W55">
-        <v>0.2338128180595095</v>
+        <v>0.2338496177250741</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.03370961731111999</v>
+        <v>0.03308536513869187</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5950,22 +5950,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2247326180175325</v>
+        <v>0.2266326180175325</v>
       </c>
       <c r="C56">
-        <v>-1.151782620062077</v>
+        <v>-1.337687167415972</v>
       </c>
       <c r="D56">
-        <v>5.493937379937924</v>
+        <v>5.436212832584028</v>
       </c>
       <c r="E56">
-        <v>6.203720000000001</v>
+        <v>6.3319</v>
       </c>
       <c r="F56">
-        <v>6.921720000000001</v>
+        <v>7.0499</v>
       </c>
       <c r="G56">
         <v>0.276</v>
@@ -5986,37 +5986,37 @@
         <v>0.054</v>
       </c>
       <c r="M56">
-        <v>1.632141576</v>
+        <v>1.66236642</v>
       </c>
       <c r="N56">
-        <v>-1.578141576</v>
+        <v>-1.60836642</v>
       </c>
       <c r="O56">
-        <v>-0.394535394</v>
+        <v>-0.402091605</v>
       </c>
       <c r="P56">
-        <v>-1.183606182</v>
+        <v>-1.206274815</v>
       </c>
       <c r="Q56">
-        <v>-1.133606182</v>
+        <v>-1.156274815</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2140300531434619</v>
+        <v>0.2177684987688722</v>
       </c>
       <c r="T56">
-        <v>1.626913189165231</v>
+        <v>1.663066815591125</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.008271341284672966</v>
+        <v>0.008120953261315275</v>
       </c>
       <c r="W56">
-        <v>0.2338496177250741</v>
+        <v>0.2338850792209819</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.03308536513869187</v>
+        <v>0.03248381304526116</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6032,22 +6032,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2266326180175325</v>
+        <v>0.2285326180175325</v>
       </c>
       <c r="C57">
-        <v>-1.337687167415972</v>
+        <v>-1.522391309049617</v>
       </c>
       <c r="D57">
-        <v>5.436212832584028</v>
+        <v>5.379688690950384</v>
       </c>
       <c r="E57">
-        <v>6.3319</v>
+        <v>6.46008</v>
       </c>
       <c r="F57">
-        <v>7.0499</v>
+        <v>7.17808</v>
       </c>
       <c r="G57">
         <v>0.276</v>
@@ -6068,37 +6068,37 @@
         <v>0.054</v>
       </c>
       <c r="M57">
-        <v>1.66236642</v>
+        <v>1.692591264</v>
       </c>
       <c r="N57">
-        <v>-1.60836642</v>
+        <v>-1.638591264</v>
       </c>
       <c r="O57">
-        <v>-0.402091605</v>
+        <v>-0.4096478160000001</v>
       </c>
       <c r="P57">
-        <v>-1.206274815</v>
+        <v>-1.228943448</v>
       </c>
       <c r="Q57">
-        <v>-1.156274815</v>
+        <v>-1.178943448</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2177684987688722</v>
+        <v>0.221676873740892</v>
       </c>
       <c r="T57">
-        <v>1.663066815591125</v>
+        <v>1.700863788672741</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.008120953261315275</v>
+        <v>0.007975936238791788</v>
       </c>
       <c r="W57">
-        <v>0.2338850792209819</v>
+        <v>0.2339192742348929</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.03248381304526116</v>
+        <v>0.03190374495516723</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6114,22 +6114,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2285326180175325</v>
+        <v>0.2304326180175325</v>
       </c>
       <c r="C58">
-        <v>-1.522391309049617</v>
+        <v>-1.705932104030249</v>
       </c>
       <c r="D58">
-        <v>5.379688690950384</v>
+        <v>5.324327895969752</v>
       </c>
       <c r="E58">
-        <v>6.46008</v>
+        <v>6.588260000000001</v>
       </c>
       <c r="F58">
-        <v>7.17808</v>
+        <v>7.306260000000001</v>
       </c>
       <c r="G58">
         <v>0.276</v>
@@ -6150,37 +6150,37 @@
         <v>0.054</v>
       </c>
       <c r="M58">
-        <v>1.692591264</v>
+        <v>1.722816108</v>
       </c>
       <c r="N58">
-        <v>-1.638591264</v>
+        <v>-1.668816108</v>
       </c>
       <c r="O58">
-        <v>-0.4096478160000001</v>
+        <v>-0.417204027</v>
       </c>
       <c r="P58">
-        <v>-1.228943448</v>
+        <v>-1.251612081</v>
       </c>
       <c r="Q58">
-        <v>-1.178943448</v>
+        <v>-1.201612081</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.221676873740892</v>
+        <v>0.2257670335953313</v>
       </c>
       <c r="T58">
-        <v>1.700863788672741</v>
+        <v>1.74041876050234</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.007975936238791788</v>
+        <v>0.007836007532848072</v>
       </c>
       <c r="W58">
-        <v>0.2339192742348929</v>
+        <v>0.2339522694237544</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.03190374495516723</v>
+        <v>0.03134403013139231</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6196,22 +6196,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2304326180175325</v>
+        <v>0.2323326180175325</v>
       </c>
       <c r="C59">
-        <v>-1.705932104030249</v>
+        <v>-1.888345101507353</v>
       </c>
       <c r="D59">
-        <v>5.324327895969752</v>
+        <v>5.270094898492648</v>
       </c>
       <c r="E59">
-        <v>6.588260000000001</v>
+        <v>6.71644</v>
       </c>
       <c r="F59">
-        <v>7.306260000000001</v>
+        <v>7.43444</v>
       </c>
       <c r="G59">
         <v>0.276</v>
@@ -6232,37 +6232,37 @@
         <v>0.054</v>
       </c>
       <c r="M59">
-        <v>1.722816108</v>
+        <v>1.753040952</v>
       </c>
       <c r="N59">
-        <v>-1.668816108</v>
+        <v>-1.699040952</v>
       </c>
       <c r="O59">
-        <v>-0.417204027</v>
+        <v>-0.424760238</v>
       </c>
       <c r="P59">
-        <v>-1.251612081</v>
+        <v>-1.274280714</v>
       </c>
       <c r="Q59">
-        <v>-1.201612081</v>
+        <v>-1.224280714</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2257670335953313</v>
+        <v>0.2300519629666487</v>
       </c>
       <c r="T59">
-        <v>1.74041876050234</v>
+        <v>1.781857302419062</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.007836007532848072</v>
+        <v>0.00770090395469552</v>
       </c>
       <c r="W59">
-        <v>0.2339522694237544</v>
+        <v>0.2339841268474828</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.03134403013139231</v>
+        <v>0.0308036158187821</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6278,22 +6278,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2323326180175325</v>
+        <v>0.2342326180175325</v>
       </c>
       <c r="C60">
-        <v>-1.888345101507352</v>
+        <v>-2.069664416836527</v>
       </c>
       <c r="D60">
-        <v>5.270094898492648</v>
+        <v>5.216955583163473</v>
       </c>
       <c r="E60">
-        <v>6.71644</v>
+        <v>6.844619999999999</v>
       </c>
       <c r="F60">
-        <v>7.434439999999999</v>
+        <v>7.562619999999999</v>
       </c>
       <c r="G60">
         <v>0.276</v>
@@ -6314,37 +6314,37 @@
         <v>0.054</v>
       </c>
       <c r="M60">
-        <v>1.753040952</v>
+        <v>1.783265796</v>
       </c>
       <c r="N60">
-        <v>-1.699040952</v>
+        <v>-1.729265796</v>
       </c>
       <c r="O60">
-        <v>-0.424760238</v>
+        <v>-0.4323164489999999</v>
       </c>
       <c r="P60">
-        <v>-1.274280714</v>
+        <v>-1.296949347</v>
       </c>
       <c r="Q60">
-        <v>-1.224280714</v>
+        <v>-1.246949347</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2300519629666487</v>
+        <v>0.2345459132829084</v>
       </c>
       <c r="T60">
-        <v>1.781857302419062</v>
+        <v>1.825317236624405</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.007700903954695521</v>
+        <v>0.007570380158853225</v>
       </c>
       <c r="W60">
-        <v>0.2339841268474828</v>
+        <v>0.2340149043585424</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.0308036158187821</v>
+        <v>0.0302815206354129</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6360,22 +6360,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2342326180175325</v>
+        <v>0.2361326180175325</v>
       </c>
       <c r="C61">
-        <v>-2.069664416836527</v>
+        <v>-2.2499228031439</v>
       </c>
       <c r="D61">
-        <v>5.216955583163473</v>
+        <v>5.1648771968561</v>
       </c>
       <c r="E61">
-        <v>6.844619999999999</v>
+        <v>6.972799999999999</v>
       </c>
       <c r="F61">
-        <v>7.562619999999999</v>
+        <v>7.690799999999999</v>
       </c>
       <c r="G61">
         <v>0.276</v>
@@ -6396,37 +6396,37 @@
         <v>0.054</v>
       </c>
       <c r="M61">
-        <v>1.783265796</v>
+        <v>1.81349064</v>
       </c>
       <c r="N61">
-        <v>-1.729265796</v>
+        <v>-1.75949064</v>
       </c>
       <c r="O61">
-        <v>-0.4323164489999999</v>
+        <v>-0.43987266</v>
       </c>
       <c r="P61">
-        <v>-1.296949347</v>
+        <v>-1.31961798</v>
       </c>
       <c r="Q61">
-        <v>-1.246949347</v>
+        <v>-1.26961798</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2345459132829084</v>
+        <v>0.2392645611149811</v>
       </c>
       <c r="T61">
-        <v>1.825317236624405</v>
+        <v>1.870950167540015</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.007570380158853225</v>
+        <v>0.00744420715620567</v>
       </c>
       <c r="W61">
-        <v>0.2340149043585424</v>
+        <v>0.2340446559525667</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.0302815206354129</v>
+        <v>0.02977682862482267</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6442,22 +6442,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2361326180175325</v>
+        <v>0.2380326180175325</v>
       </c>
       <c r="C62">
-        <v>-2.2499228031439</v>
+        <v>-2.429151718646533</v>
       </c>
       <c r="D62">
-        <v>5.1648771968561</v>
+        <v>5.113828281353467</v>
       </c>
       <c r="E62">
-        <v>6.972799999999999</v>
+        <v>7.10098</v>
       </c>
       <c r="F62">
-        <v>7.690799999999999</v>
+        <v>7.81898</v>
       </c>
       <c r="G62">
         <v>0.276</v>
@@ -6478,37 +6478,37 @@
         <v>0.054</v>
       </c>
       <c r="M62">
-        <v>1.81349064</v>
+        <v>1.843715484</v>
       </c>
       <c r="N62">
-        <v>-1.75949064</v>
+        <v>-1.789715484</v>
       </c>
       <c r="O62">
-        <v>-0.43987266</v>
+        <v>-0.447428871</v>
       </c>
       <c r="P62">
-        <v>-1.31961798</v>
+        <v>-1.342286613</v>
       </c>
       <c r="Q62">
-        <v>-1.26961798</v>
+        <v>-1.292286613</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2392645611149811</v>
+        <v>0.2442251908871602</v>
       </c>
       <c r="T62">
-        <v>1.870950167540015</v>
+        <v>1.91892324875899</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.00744420715620567</v>
+        <v>0.007322170973317052</v>
       </c>
       <c r="W62">
-        <v>0.2340446559525667</v>
+        <v>0.2340734320844919</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.02977682862482267</v>
+        <v>0.02928868389326822</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6524,22 +6524,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2380326180175325</v>
+        <v>0.2399326180175325</v>
       </c>
       <c r="C63">
-        <v>-2.429151718646533</v>
+        <v>-2.607381390019603</v>
       </c>
       <c r="D63">
-        <v>5.113828281353467</v>
+        <v>5.063778609980397</v>
       </c>
       <c r="E63">
-        <v>7.10098</v>
+        <v>7.229159999999999</v>
       </c>
       <c r="F63">
-        <v>7.81898</v>
+        <v>7.947159999999999</v>
       </c>
       <c r="G63">
         <v>0.276</v>
@@ -6560,37 +6560,37 @@
         <v>0.054</v>
       </c>
       <c r="M63">
-        <v>1.843715484</v>
+        <v>1.873940328</v>
       </c>
       <c r="N63">
-        <v>-1.789715484</v>
+        <v>-1.819940328</v>
       </c>
       <c r="O63">
-        <v>-0.447428871</v>
+        <v>-0.454985082</v>
       </c>
       <c r="P63">
-        <v>-1.342286613</v>
+        <v>-1.364955246</v>
       </c>
       <c r="Q63">
-        <v>-1.292286613</v>
+        <v>-1.314955246</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2442251908871602</v>
+        <v>0.2494469064368222</v>
       </c>
       <c r="T63">
-        <v>1.91892324875899</v>
+        <v>1.96942122898949</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.007322170973317052</v>
+        <v>0.007204071441489357</v>
       </c>
       <c r="W63">
-        <v>0.2340734320844919</v>
+        <v>0.2341012799540968</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.02928868389326822</v>
+        <v>0.02881628576595741</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6606,22 +6606,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2399326180175325</v>
+        <v>0.2418326180175325</v>
       </c>
       <c r="C64">
-        <v>-2.607381390019603</v>
+        <v>-2.784640872078565</v>
       </c>
       <c r="D64">
-        <v>5.063778609980397</v>
+        <v>5.014699127921435</v>
       </c>
       <c r="E64">
-        <v>7.229159999999999</v>
+        <v>7.357340000000001</v>
       </c>
       <c r="F64">
-        <v>7.947159999999999</v>
+        <v>8.075340000000001</v>
       </c>
       <c r="G64">
         <v>0.276</v>
@@ -6642,37 +6642,37 @@
         <v>0.054</v>
       </c>
       <c r="M64">
-        <v>1.873940328</v>
+        <v>1.904165172</v>
       </c>
       <c r="N64">
-        <v>-1.819940328</v>
+        <v>-1.850165172</v>
       </c>
       <c r="O64">
-        <v>-0.454985082</v>
+        <v>-0.462541293</v>
       </c>
       <c r="P64">
-        <v>-1.364955246</v>
+        <v>-1.387623879</v>
       </c>
       <c r="Q64">
-        <v>-1.314955246</v>
+        <v>-1.337623879</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2494469064368222</v>
+        <v>0.2549508768810607</v>
       </c>
       <c r="T64">
-        <v>1.96942122898949</v>
+        <v>2.022648829772989</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.007204071441489357</v>
+        <v>0.007089721101148257</v>
       </c>
       <c r="W64">
-        <v>0.2341012799540968</v>
+        <v>0.2341282437643493</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.02881628576595741</v>
+        <v>0.028358884404593</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6688,22 +6688,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2418326180175325</v>
+        <v>0.2437326180175325</v>
       </c>
       <c r="C65">
-        <v>-2.784640872078565</v>
+        <v>-2.960958104023867</v>
       </c>
       <c r="D65">
-        <v>5.014699127921435</v>
+        <v>4.966561895976133</v>
       </c>
       <c r="E65">
-        <v>7.357340000000001</v>
+        <v>7.485519999999999</v>
       </c>
       <c r="F65">
-        <v>8.075340000000001</v>
+        <v>8.203519999999999</v>
       </c>
       <c r="G65">
         <v>0.276</v>
@@ -6724,37 +6724,37 @@
         <v>0.054</v>
       </c>
       <c r="M65">
-        <v>1.904165172</v>
+        <v>1.934390016</v>
       </c>
       <c r="N65">
-        <v>-1.850165172</v>
+        <v>-1.880390016</v>
       </c>
       <c r="O65">
-        <v>-0.462541293</v>
+        <v>-0.4700975039999999</v>
       </c>
       <c r="P65">
-        <v>-1.387623879</v>
+        <v>-1.410292512</v>
       </c>
       <c r="Q65">
-        <v>-1.337623879</v>
+        <v>-1.360292512</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2549508768810607</v>
+        <v>0.2607606234610902</v>
       </c>
       <c r="T65">
-        <v>2.022648829772989</v>
+        <v>2.078833519488906</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.007089721101148257</v>
+        <v>0.006978944208942816</v>
       </c>
       <c r="W65">
-        <v>0.2341282437643493</v>
+        <v>0.2341543649555313</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.028358884404593</v>
+        <v>0.02791577683577129</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6770,22 +6770,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2437326180175325</v>
+        <v>0.2456326180175325</v>
       </c>
       <c r="C66">
-        <v>-2.960958104023867</v>
+        <v>-3.136359962477058</v>
       </c>
       <c r="D66">
-        <v>4.966561895976133</v>
+        <v>4.919340037522942</v>
       </c>
       <c r="E66">
-        <v>7.485519999999999</v>
+        <v>7.6137</v>
       </c>
       <c r="F66">
-        <v>8.203519999999999</v>
+        <v>8.3317</v>
       </c>
       <c r="G66">
         <v>0.276</v>
@@ -6806,37 +6806,37 @@
         <v>0.054</v>
       </c>
       <c r="M66">
-        <v>1.934390016</v>
+        <v>1.96461486</v>
       </c>
       <c r="N66">
-        <v>-1.880390016</v>
+        <v>-1.91061486</v>
       </c>
       <c r="O66">
-        <v>-0.4700975039999999</v>
+        <v>-0.477653715</v>
       </c>
       <c r="P66">
-        <v>-1.410292512</v>
+        <v>-1.432961145</v>
       </c>
       <c r="Q66">
-        <v>-1.360292512</v>
+        <v>-1.382961145</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2607606234610902</v>
+        <v>0.2669023555599784</v>
       </c>
       <c r="T66">
-        <v>2.078833519488906</v>
+        <v>2.138228762902874</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.006978944208942816</v>
+        <v>0.006871575836497541</v>
       </c>
       <c r="W66">
-        <v>0.2341543649555313</v>
+        <v>0.2341796824177539</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.02791577683577129</v>
+        <v>0.02748630334599023</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6852,22 +6852,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2456326180175325</v>
+        <v>0.2475326180175325</v>
       </c>
       <c r="C67">
-        <v>-3.136359962477058</v>
+        <v>-3.310872311519797</v>
       </c>
       <c r="D67">
-        <v>4.919340037522942</v>
+        <v>4.873007688480203</v>
       </c>
       <c r="E67">
-        <v>7.6137</v>
+        <v>7.74188</v>
       </c>
       <c r="F67">
-        <v>8.3317</v>
+        <v>8.45988</v>
       </c>
       <c r="G67">
         <v>0.276</v>
@@ -6888,37 +6888,37 @@
         <v>0.054</v>
       </c>
       <c r="M67">
-        <v>1.96461486</v>
+        <v>1.994839704</v>
       </c>
       <c r="N67">
-        <v>-1.91061486</v>
+        <v>-1.940839704</v>
       </c>
       <c r="O67">
-        <v>-0.477653715</v>
+        <v>-0.485209926</v>
       </c>
       <c r="P67">
-        <v>-1.432961145</v>
+        <v>-1.455629778</v>
       </c>
       <c r="Q67">
-        <v>-1.382961145</v>
+        <v>-1.405629778</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2669023555599784</v>
+        <v>0.2734053660176249</v>
       </c>
       <c r="T67">
-        <v>2.138228762902874</v>
+        <v>2.201117844164724</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.006871575836497541</v>
+        <v>0.006767461051096063</v>
       </c>
       <c r="W67">
-        <v>0.2341796824177539</v>
+        <v>0.2342042326841516</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.02748630334599023</v>
+        <v>0.0270698442043843</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6934,22 +6934,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2475326180175325</v>
+        <v>0.2494326180175325</v>
       </c>
       <c r="C68">
-        <v>-3.310872311519797</v>
+        <v>-3.484520049931506</v>
       </c>
       <c r="D68">
-        <v>4.873007688480203</v>
+        <v>4.827539950068495</v>
       </c>
       <c r="E68">
-        <v>7.74188</v>
+        <v>7.87006</v>
       </c>
       <c r="F68">
-        <v>8.45988</v>
+        <v>8.58806</v>
       </c>
       <c r="G68">
         <v>0.276</v>
@@ -6970,37 +6970,37 @@
         <v>0.054</v>
       </c>
       <c r="M68">
-        <v>1.994839704</v>
+        <v>2.025064548</v>
       </c>
       <c r="N68">
-        <v>-1.940839704</v>
+        <v>-1.971064548</v>
       </c>
       <c r="O68">
-        <v>-0.485209926</v>
+        <v>-0.492766137</v>
       </c>
       <c r="P68">
-        <v>-1.455629778</v>
+        <v>-1.478298411</v>
       </c>
       <c r="Q68">
-        <v>-1.405629778</v>
+        <v>-1.428298411</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2734053660176249</v>
+        <v>0.2803024983211893</v>
       </c>
       <c r="T68">
-        <v>2.201117844164724</v>
+        <v>2.267818384896989</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.006767461051096063</v>
+        <v>0.006666454169736421</v>
       </c>
       <c r="W68">
-        <v>0.2342042326841516</v>
+        <v>0.2342280501067762</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.0270698442043843</v>
+        <v>0.02666581667894574</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7016,22 +7016,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2494326180175325</v>
+        <v>0.2513326180175325</v>
       </c>
       <c r="C69">
-        <v>-3.484520049931506</v>
+        <v>-3.657327155806972</v>
       </c>
       <c r="D69">
-        <v>4.827539950068495</v>
+        <v>4.782912844193029</v>
       </c>
       <c r="E69">
-        <v>7.87006</v>
+        <v>7.998240000000001</v>
       </c>
       <c r="F69">
-        <v>8.58806</v>
+        <v>8.716240000000001</v>
       </c>
       <c r="G69">
         <v>0.276</v>
@@ -7052,37 +7052,37 @@
         <v>0.054</v>
       </c>
       <c r="M69">
-        <v>2.025064548</v>
+        <v>2.055289392</v>
       </c>
       <c r="N69">
-        <v>-1.971064548</v>
+        <v>-2.001289392</v>
       </c>
       <c r="O69">
-        <v>-0.492766137</v>
+        <v>-0.5003223480000001</v>
       </c>
       <c r="P69">
-        <v>-1.478298411</v>
+        <v>-1.500967044</v>
       </c>
       <c r="Q69">
-        <v>-1.428298411</v>
+        <v>-1.450967044</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2803024983211893</v>
+        <v>0.2876307013937265</v>
       </c>
       <c r="T69">
-        <v>2.267818384896989</v>
+        <v>2.33868770942502</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.006666454169736421</v>
+        <v>0.006568418079005003</v>
       </c>
       <c r="W69">
-        <v>0.2342280501067762</v>
+        <v>0.2342511670169706</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.02666581667894574</v>
+        <v>0.02627367231601996</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7098,22 +7098,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2513326180175325</v>
+        <v>0.2532326180175325</v>
       </c>
       <c r="C70">
-        <v>-3.657327155806972</v>
+        <v>-3.829316728721869</v>
       </c>
       <c r="D70">
-        <v>4.782912844193029</v>
+        <v>4.739103271278132</v>
       </c>
       <c r="E70">
-        <v>7.998240000000001</v>
+        <v>8.126420000000001</v>
       </c>
       <c r="F70">
-        <v>8.716240000000001</v>
+        <v>8.844420000000001</v>
       </c>
       <c r="G70">
         <v>0.276</v>
@@ -7134,37 +7134,37 @@
         <v>0.054</v>
       </c>
       <c r="M70">
-        <v>2.055289392</v>
+        <v>2.085514236</v>
       </c>
       <c r="N70">
-        <v>-2.001289392</v>
+        <v>-2.031514236</v>
       </c>
       <c r="O70">
-        <v>-0.5003223480000001</v>
+        <v>-0.5078785590000001</v>
       </c>
       <c r="P70">
-        <v>-1.500967044</v>
+        <v>-1.523635677</v>
       </c>
       <c r="Q70">
-        <v>-1.450967044</v>
+        <v>-1.473635677</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2876307013937265</v>
+        <v>0.295431691761266</v>
       </c>
       <c r="T70">
-        <v>2.33868770942502</v>
+        <v>2.41412924843873</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.006568418079005003</v>
+        <v>0.006473223614091886</v>
       </c>
       <c r="W70">
-        <v>0.2342511670169706</v>
+        <v>0.2342736138717972</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.02627367231601996</v>
+        <v>0.02589289445636744</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7180,22 +7180,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2532326180175325</v>
+        <v>0.2551326180175325</v>
       </c>
       <c r="C71">
-        <v>-3.829316728721869</v>
+        <v>-4.000511029601983</v>
       </c>
       <c r="D71">
-        <v>4.739103271278132</v>
+        <v>4.696088970398018</v>
       </c>
       <c r="E71">
-        <v>8.126420000000001</v>
+        <v>8.2546</v>
       </c>
       <c r="F71">
-        <v>8.844420000000001</v>
+        <v>8.9726</v>
       </c>
       <c r="G71">
         <v>0.276</v>
@@ -7216,37 +7216,37 @@
         <v>0.054</v>
       </c>
       <c r="M71">
-        <v>2.085514236</v>
+        <v>2.11573908</v>
       </c>
       <c r="N71">
-        <v>-2.031514236</v>
+        <v>-2.06173908</v>
       </c>
       <c r="O71">
-        <v>-0.5078785590000001</v>
+        <v>-0.51543477</v>
       </c>
       <c r="P71">
-        <v>-1.523635677</v>
+        <v>-1.54630431</v>
       </c>
       <c r="Q71">
-        <v>-1.473635677</v>
+        <v>-1.49630431</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.295431691761266</v>
+        <v>0.3037527481533083</v>
       </c>
       <c r="T71">
-        <v>2.41412924843873</v>
+        <v>2.494600223386688</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.006473223614091886</v>
+        <v>0.006380748991033431</v>
       </c>
       <c r="W71">
-        <v>0.2342736138717972</v>
+        <v>0.2342954193879143</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.02589289445636744</v>
+        <v>0.02552299596413365</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7262,22 +7262,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2551326180175325</v>
+        <v>0.2570326180175325</v>
       </c>
       <c r="C72">
-        <v>-4.000511029601983</v>
+        <v>-4.170931518440765</v>
       </c>
       <c r="D72">
-        <v>4.696088970398018</v>
+        <v>4.653848481559235</v>
       </c>
       <c r="E72">
-        <v>8.2546</v>
+        <v>8.38278</v>
       </c>
       <c r="F72">
-        <v>8.9726</v>
+        <v>9.10078</v>
       </c>
       <c r="G72">
         <v>0.276</v>
@@ -7298,37 +7298,37 @@
         <v>0.054</v>
       </c>
       <c r="M72">
-        <v>2.11573908</v>
+        <v>2.145963924</v>
       </c>
       <c r="N72">
-        <v>-2.06173908</v>
+        <v>-2.091963924</v>
       </c>
       <c r="O72">
-        <v>-0.51543477</v>
+        <v>-0.5229909810000001</v>
       </c>
       <c r="P72">
-        <v>-1.54630431</v>
+        <v>-1.568972943</v>
       </c>
       <c r="Q72">
-        <v>-1.49630431</v>
+        <v>-1.518972943</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3037527481533083</v>
+        <v>0.3126476705034223</v>
       </c>
       <c r="T72">
-        <v>2.494600223386688</v>
+        <v>2.580620920744849</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.006380748991033431</v>
+        <v>0.006290879286934369</v>
       </c>
       <c r="W72">
-        <v>0.2342954193879143</v>
+        <v>0.2343166106641409</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.02552299596413365</v>
+        <v>0.02516351714773735</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7344,22 +7344,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2570326180175325</v>
+        <v>0.2589326180175325</v>
       </c>
       <c r="C73">
-        <v>-4.170931518440762</v>
+        <v>-4.340598889999419</v>
       </c>
       <c r="D73">
-        <v>4.653848481559237</v>
+        <v>4.61236111000058</v>
       </c>
       <c r="E73">
-        <v>8.382779999999999</v>
+        <v>8.510959999999999</v>
       </c>
       <c r="F73">
-        <v>9.100779999999999</v>
+        <v>9.228959999999999</v>
       </c>
       <c r="G73">
         <v>0.276</v>
@@ -7380,37 +7380,37 @@
         <v>0.054</v>
       </c>
       <c r="M73">
-        <v>2.145963924</v>
+        <v>2.176188768</v>
       </c>
       <c r="N73">
-        <v>-2.091963924</v>
+        <v>-2.122188768</v>
       </c>
       <c r="O73">
-        <v>-0.522990981</v>
+        <v>-0.530547192</v>
       </c>
       <c r="P73">
-        <v>-1.568972943</v>
+        <v>-1.591641576</v>
       </c>
       <c r="Q73">
-        <v>-1.518972943</v>
+        <v>-1.541641576</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3126476705034222</v>
+        <v>0.3221779444499731</v>
       </c>
       <c r="T73">
-        <v>2.580620920744849</v>
+        <v>2.672785953628593</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.00629087928693437</v>
+        <v>0.006203505963504725</v>
       </c>
       <c r="W73">
-        <v>0.2343166106641409</v>
+        <v>0.2343372132938056</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.02516351714773735</v>
+        <v>0.02481402385401887</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7426,22 +7426,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2589326180175325</v>
+        <v>0.2608326180175325</v>
       </c>
       <c r="C74">
-        <v>-4.340598889999419</v>
+        <v>-4.509533107614381</v>
       </c>
       <c r="D74">
-        <v>4.61236111000058</v>
+        <v>4.571606892385619</v>
       </c>
       <c r="E74">
-        <v>8.510959999999999</v>
+        <v>8.639139999999999</v>
       </c>
       <c r="F74">
-        <v>9.228959999999999</v>
+        <v>9.357139999999999</v>
       </c>
       <c r="G74">
         <v>0.276</v>
@@ -7462,37 +7462,37 @@
         <v>0.054</v>
       </c>
       <c r="M74">
-        <v>2.176188768</v>
+        <v>2.206413612</v>
       </c>
       <c r="N74">
-        <v>-2.122188768</v>
+        <v>-2.152413612</v>
       </c>
       <c r="O74">
-        <v>-0.530547192</v>
+        <v>-0.538103403</v>
       </c>
       <c r="P74">
-        <v>-1.591641576</v>
+        <v>-1.614310209</v>
       </c>
       <c r="Q74">
-        <v>-1.541641576</v>
+        <v>-1.564310209</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3221779444499731</v>
+        <v>0.3324141646147868</v>
       </c>
       <c r="T74">
-        <v>2.672785953628593</v>
+        <v>2.771778025985208</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.006203505963504725</v>
+        <v>0.006118526429758085</v>
       </c>
       <c r="W74">
-        <v>0.2343372132938056</v>
+        <v>0.234357251467863</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.02481402385401887</v>
+        <v>0.0244741057190323</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7508,22 +7508,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2608326180175325</v>
+        <v>0.2627326180175325</v>
       </c>
       <c r="C75">
-        <v>-4.509533107614381</v>
+        <v>-4.677753435228141</v>
       </c>
       <c r="D75">
-        <v>4.571606892385619</v>
+        <v>4.531566564771859</v>
       </c>
       <c r="E75">
-        <v>8.639139999999999</v>
+        <v>8.76732</v>
       </c>
       <c r="F75">
-        <v>9.357139999999999</v>
+        <v>9.48532</v>
       </c>
       <c r="G75">
         <v>0.276</v>
@@ -7544,37 +7544,37 @@
         <v>0.054</v>
       </c>
       <c r="M75">
-        <v>2.206413612</v>
+        <v>2.236638456</v>
       </c>
       <c r="N75">
-        <v>-2.152413612</v>
+        <v>-2.182638456</v>
       </c>
       <c r="O75">
-        <v>-0.538103403</v>
+        <v>-0.5456596140000001</v>
       </c>
       <c r="P75">
-        <v>-1.614310209</v>
+        <v>-1.636978842</v>
       </c>
       <c r="Q75">
-        <v>-1.564310209</v>
+        <v>-1.586978842</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3324141646147868</v>
+        <v>0.3434377863307402</v>
       </c>
       <c r="T75">
-        <v>2.771778025985208</v>
+        <v>2.878384873138485</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.006118526429758085</v>
+        <v>0.006035843640166759</v>
       </c>
       <c r="W75">
-        <v>0.234357251467863</v>
+        <v>0.2343767480696487</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.0244741057190323</v>
+        <v>0.02414337456066695</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7590,22 +7590,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2627326180175325</v>
+        <v>0.2646326180175325</v>
       </c>
       <c r="C76">
-        <v>-4.677753435228141</v>
+        <v>-4.845278467751477</v>
       </c>
       <c r="D76">
-        <v>4.531566564771859</v>
+        <v>4.492221532248523</v>
       </c>
       <c r="E76">
-        <v>8.76732</v>
+        <v>8.8955</v>
       </c>
       <c r="F76">
-        <v>9.48532</v>
+        <v>9.6135</v>
       </c>
       <c r="G76">
         <v>0.276</v>
@@ -7626,37 +7626,37 @@
         <v>0.054</v>
       </c>
       <c r="M76">
-        <v>2.236638456</v>
+        <v>2.2668633</v>
       </c>
       <c r="N76">
-        <v>-2.182638456</v>
+        <v>-2.2128633</v>
       </c>
       <c r="O76">
-        <v>-0.5456596140000001</v>
+        <v>-0.5532158250000001</v>
       </c>
       <c r="P76">
-        <v>-1.636978842</v>
+        <v>-1.659647475</v>
       </c>
       <c r="Q76">
-        <v>-1.586978842</v>
+        <v>-1.609647475</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3434377863307402</v>
+        <v>0.3553432977839698</v>
       </c>
       <c r="T76">
-        <v>2.878384873138485</v>
+        <v>2.993520268064024</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.006035843640166759</v>
+        <v>0.005955365724964535</v>
       </c>
       <c r="W76">
-        <v>0.2343767480696487</v>
+        <v>0.2343957247620534</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.02414337456066695</v>
+        <v>0.02382146289985809</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7672,22 +7672,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2646326180175325</v>
+        <v>0.2665326180175325</v>
       </c>
       <c r="C77">
-        <v>-4.845278467751477</v>
+        <v>-5.012126159857563</v>
       </c>
       <c r="D77">
-        <v>4.492221532248523</v>
+        <v>4.453553840142438</v>
       </c>
       <c r="E77">
-        <v>8.8955</v>
+        <v>9.023680000000001</v>
       </c>
       <c r="F77">
-        <v>9.6135</v>
+        <v>9.741680000000001</v>
       </c>
       <c r="G77">
         <v>0.276</v>
@@ -7708,37 +7708,37 @@
         <v>0.054</v>
       </c>
       <c r="M77">
-        <v>2.2668633</v>
+        <v>2.297088144</v>
       </c>
       <c r="N77">
-        <v>-2.2128633</v>
+        <v>-2.243088144000001</v>
       </c>
       <c r="O77">
-        <v>-0.5532158250000001</v>
+        <v>-0.5607720360000001</v>
       </c>
       <c r="P77">
-        <v>-1.659647475</v>
+        <v>-1.682316108</v>
       </c>
       <c r="Q77">
-        <v>-1.609647475</v>
+        <v>-1.632316108</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3553432977839698</v>
+        <v>0.3682409351916353</v>
       </c>
       <c r="T77">
-        <v>2.993520268064024</v>
+        <v>3.118250279233359</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.005955365724964535</v>
+        <v>0.005877005649636054</v>
       </c>
       <c r="W77">
-        <v>0.2343957247620534</v>
+        <v>0.2344142020678159</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.02382146289985809</v>
+        <v>0.02350802259854412</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7754,22 +7754,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2665326180175325</v>
+        <v>0.2684326180175325</v>
       </c>
       <c r="C78">
-        <v>-5.012126159857563</v>
+        <v>-5.178313853301675</v>
       </c>
       <c r="D78">
-        <v>4.453553840142438</v>
+        <v>4.415546146698325</v>
       </c>
       <c r="E78">
-        <v>9.023680000000001</v>
+        <v>9.151859999999999</v>
       </c>
       <c r="F78">
-        <v>9.741680000000001</v>
+        <v>9.869859999999999</v>
       </c>
       <c r="G78">
         <v>0.276</v>
@@ -7790,37 +7790,37 @@
         <v>0.054</v>
       </c>
       <c r="M78">
-        <v>2.297088144</v>
+        <v>2.327312988</v>
       </c>
       <c r="N78">
-        <v>-2.243088144000001</v>
+        <v>-2.273312988</v>
       </c>
       <c r="O78">
-        <v>-0.5607720360000001</v>
+        <v>-0.5683282470000001</v>
       </c>
       <c r="P78">
-        <v>-1.682316108</v>
+        <v>-1.704984741</v>
       </c>
       <c r="Q78">
-        <v>-1.632316108</v>
+        <v>-1.654984741</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3682409351916353</v>
+        <v>0.3822601062869238</v>
       </c>
       <c r="T78">
-        <v>3.118250279233359</v>
+        <v>3.253826378330462</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.005877005649636054</v>
+        <v>0.005800680900939483</v>
       </c>
       <c r="W78">
-        <v>0.2344142020678159</v>
+        <v>0.2344321994435585</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.02350802259854412</v>
+        <v>0.02320272360375786</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7836,22 +7836,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2684326180175325</v>
+        <v>0.2703326180175325</v>
       </c>
       <c r="C79">
-        <v>-5.178313853301675</v>
+        <v>-5.343858302853818</v>
       </c>
       <c r="D79">
-        <v>4.415546146698325</v>
+        <v>4.378181697146181</v>
       </c>
       <c r="E79">
-        <v>9.151859999999999</v>
+        <v>9.28004</v>
       </c>
       <c r="F79">
-        <v>9.869859999999999</v>
+        <v>9.99804</v>
       </c>
       <c r="G79">
         <v>0.276</v>
@@ -7872,37 +7872,37 @@
         <v>0.054</v>
       </c>
       <c r="M79">
-        <v>2.327312988</v>
+        <v>2.357537832</v>
       </c>
       <c r="N79">
-        <v>-2.273312988</v>
+        <v>-2.303537832</v>
       </c>
       <c r="O79">
-        <v>-0.5683282470000001</v>
+        <v>-0.5758844580000001</v>
       </c>
       <c r="P79">
-        <v>-1.704984741</v>
+        <v>-1.727653374</v>
       </c>
       <c r="Q79">
-        <v>-1.654984741</v>
+        <v>-1.677653374</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3822601062869238</v>
+        <v>0.3975537474817839</v>
       </c>
       <c r="T79">
-        <v>3.253826378330462</v>
+        <v>3.401727577345482</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.005800680900939483</v>
+        <v>0.005726313197081284</v>
       </c>
       <c r="W79">
-        <v>0.2344321994435585</v>
+        <v>0.2344497353481282</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.02320272360375786</v>
+        <v>0.02290525278832511</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7918,22 +7918,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2703326180175325</v>
+        <v>0.2722326180175325</v>
       </c>
       <c r="C80">
-        <v>-5.343858302853818</v>
+        <v>-5.508775700925741</v>
       </c>
       <c r="D80">
-        <v>4.378181697146181</v>
+        <v>4.341444299074259</v>
       </c>
       <c r="E80">
-        <v>9.28004</v>
+        <v>9.40822</v>
       </c>
       <c r="F80">
-        <v>9.99804</v>
+        <v>10.12622</v>
       </c>
       <c r="G80">
         <v>0.276</v>
@@ -7954,37 +7954,37 @@
         <v>0.054</v>
       </c>
       <c r="M80">
-        <v>2.357537832</v>
+        <v>2.387762676</v>
       </c>
       <c r="N80">
-        <v>-2.303537832</v>
+        <v>-2.333762676</v>
       </c>
       <c r="O80">
-        <v>-0.5758844580000001</v>
+        <v>-0.583440669</v>
       </c>
       <c r="P80">
-        <v>-1.727653374</v>
+        <v>-1.750322007</v>
       </c>
       <c r="Q80">
-        <v>-1.677653374</v>
+        <v>-1.700322007</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3975537474817839</v>
+        <v>0.4143039259332975</v>
       </c>
       <c r="T80">
-        <v>3.401727577345482</v>
+        <v>3.563714604838125</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.005726313197081284</v>
+        <v>0.005653828219903041</v>
       </c>
       <c r="W80">
-        <v>0.2344497353481282</v>
+        <v>0.2344668273057469</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.02290525278832511</v>
+        <v>0.02261531287961205</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8000,22 +8000,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2722326180175325</v>
+        <v>0.2741326180175325</v>
       </c>
       <c r="C81">
-        <v>-5.508775700925741</v>
+        <v>-5.673081700968399</v>
       </c>
       <c r="D81">
-        <v>4.341444299074259</v>
+        <v>4.305318299031602</v>
       </c>
       <c r="E81">
-        <v>9.40822</v>
+        <v>9.5364</v>
       </c>
       <c r="F81">
-        <v>10.12622</v>
+        <v>10.2544</v>
       </c>
       <c r="G81">
         <v>0.276</v>
@@ -8036,37 +8036,37 @@
         <v>0.054</v>
       </c>
       <c r="M81">
-        <v>2.387762676</v>
+        <v>2.41798752</v>
       </c>
       <c r="N81">
-        <v>-2.333762676</v>
+        <v>-2.36398752</v>
       </c>
       <c r="O81">
-        <v>-0.583440669</v>
+        <v>-0.5909968800000001</v>
       </c>
       <c r="P81">
-        <v>-1.750322007</v>
+        <v>-1.77299064</v>
       </c>
       <c r="Q81">
-        <v>-1.700322007</v>
+        <v>-1.72299064</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4143039259332975</v>
+        <v>0.4327291222299624</v>
       </c>
       <c r="T81">
-        <v>3.563714604838125</v>
+        <v>3.741900335080032</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.005653828219903041</v>
+        <v>0.005583155367154253</v>
       </c>
       <c r="W81">
-        <v>0.2344668273057469</v>
+        <v>0.234483491964425</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.02261531287961205</v>
+        <v>0.02233262146861692</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8082,22 +8082,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2741326180175325</v>
+        <v>0.2760326180175325</v>
       </c>
       <c r="C82">
-        <v>-5.673081700968399</v>
+        <v>-5.836791439710878</v>
       </c>
       <c r="D82">
-        <v>4.305318299031602</v>
+        <v>4.269788560289123</v>
       </c>
       <c r="E82">
-        <v>9.5364</v>
+        <v>9.664580000000001</v>
       </c>
       <c r="F82">
-        <v>10.2544</v>
+        <v>10.38258</v>
       </c>
       <c r="G82">
         <v>0.276</v>
@@ -8118,37 +8118,37 @@
         <v>0.054</v>
       </c>
       <c r="M82">
-        <v>2.41798752</v>
+        <v>2.448212364</v>
       </c>
       <c r="N82">
-        <v>-2.36398752</v>
+        <v>-2.394212364</v>
       </c>
       <c r="O82">
-        <v>-0.5909968800000001</v>
+        <v>-0.5985530910000001</v>
       </c>
       <c r="P82">
-        <v>-1.77299064</v>
+        <v>-1.795659273</v>
       </c>
       <c r="Q82">
-        <v>-1.72299064</v>
+        <v>-1.745659273</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4327291222299624</v>
+        <v>0.4530938128736446</v>
       </c>
       <c r="T82">
-        <v>3.741900335080032</v>
+        <v>3.938842457978981</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.005583155367154253</v>
+        <v>0.005514227523115311</v>
       </c>
       <c r="W82">
-        <v>0.234483491964425</v>
+        <v>0.2344997451500494</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.02233262146861692</v>
+        <v>0.02205691009246113</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8164,22 +8164,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2760326180175325</v>
+        <v>0.2779326180175325</v>
       </c>
       <c r="C83">
-        <v>-5.836791439710878</v>
+        <v>-5.999919558307191</v>
       </c>
       <c r="D83">
-        <v>4.269788560289123</v>
+        <v>4.23484044169281</v>
       </c>
       <c r="E83">
-        <v>9.664580000000001</v>
+        <v>9.792760000000001</v>
       </c>
       <c r="F83">
-        <v>10.38258</v>
+        <v>10.51076</v>
       </c>
       <c r="G83">
         <v>0.276</v>
@@ -8200,37 +8200,37 @@
         <v>0.054</v>
       </c>
       <c r="M83">
-        <v>2.448212364</v>
+        <v>2.478437208</v>
       </c>
       <c r="N83">
-        <v>-2.394212364</v>
+        <v>-2.424437208000001</v>
       </c>
       <c r="O83">
-        <v>-0.5985530910000001</v>
+        <v>-0.6061093020000001</v>
       </c>
       <c r="P83">
-        <v>-1.795659273</v>
+        <v>-1.818327906</v>
       </c>
       <c r="Q83">
-        <v>-1.745659273</v>
+        <v>-1.768327906</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4530938128736446</v>
+        <v>0.4757212469221804</v>
       </c>
       <c r="T83">
-        <v>3.938842457978981</v>
+        <v>4.157667038977813</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.005514227523115311</v>
+        <v>0.005446980846004148</v>
       </c>
       <c r="W83">
-        <v>0.2344997451500494</v>
+        <v>0.2345156019165122</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.02205691009246113</v>
+        <v>0.02178792338401647</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8246,22 +8246,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2779326180175325</v>
+        <v>0.2798326180175325</v>
       </c>
       <c r="C84">
-        <v>-5.999919558307191</v>
+        <v>-6.162480222452961</v>
       </c>
       <c r="D84">
-        <v>4.23484044169281</v>
+        <v>4.200459777547039</v>
       </c>
       <c r="E84">
-        <v>9.792760000000001</v>
+        <v>9.92094</v>
       </c>
       <c r="F84">
-        <v>10.51076</v>
+        <v>10.63894</v>
       </c>
       <c r="G84">
         <v>0.276</v>
@@ -8282,37 +8282,37 @@
         <v>0.054</v>
       </c>
       <c r="M84">
-        <v>2.478437208</v>
+        <v>2.508662052</v>
       </c>
       <c r="N84">
-        <v>-2.424437208000001</v>
+        <v>-2.454662052</v>
       </c>
       <c r="O84">
-        <v>-0.6061093020000001</v>
+        <v>-0.6136655130000001</v>
       </c>
       <c r="P84">
-        <v>-1.818327906</v>
+        <v>-1.840996539</v>
       </c>
       <c r="Q84">
-        <v>-1.768327906</v>
+        <v>-1.790996539</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4757212469221804</v>
+        <v>0.5010107320352499</v>
       </c>
       <c r="T84">
-        <v>4.157667038977813</v>
+        <v>4.40223568832945</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.005446980846004148</v>
+        <v>0.005381354570751087</v>
       </c>
       <c r="W84">
-        <v>0.2345156019165122</v>
+        <v>0.2345310765922169</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.02178792338401647</v>
+        <v>0.02152541828300425</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8328,22 +8328,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2798326180175325</v>
+        <v>0.2817326180175325</v>
       </c>
       <c r="C85">
-        <v>-6.162480222452961</v>
+        <v>-6.324487141530113</v>
       </c>
       <c r="D85">
-        <v>4.200459777547039</v>
+        <v>4.166632858469887</v>
       </c>
       <c r="E85">
-        <v>9.92094</v>
+        <v>10.04912</v>
       </c>
       <c r="F85">
-        <v>10.63894</v>
+        <v>10.76712</v>
       </c>
       <c r="G85">
         <v>0.276</v>
@@ -8364,37 +8364,37 @@
         <v>0.054</v>
       </c>
       <c r="M85">
-        <v>2.508662052</v>
+        <v>2.538886896</v>
       </c>
       <c r="N85">
-        <v>-2.454662052</v>
+        <v>-2.484886896</v>
       </c>
       <c r="O85">
-        <v>-0.6136655130000001</v>
+        <v>-0.6212217240000001</v>
       </c>
       <c r="P85">
-        <v>-1.840996539</v>
+        <v>-1.863665172</v>
       </c>
       <c r="Q85">
-        <v>-1.790996539</v>
+        <v>-1.813665172</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5010107320352499</v>
+        <v>0.5294614027874531</v>
       </c>
       <c r="T85">
-        <v>4.40223568832945</v>
+        <v>4.677375418850041</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.005381354570751087</v>
+        <v>0.005317290825861192</v>
       </c>
       <c r="W85">
-        <v>0.2345310765922169</v>
+        <v>0.234546182823262</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.02152541828300425</v>
+        <v>0.02126916330344475</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8410,22 +8410,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2817326180175325</v>
+        <v>0.2836326180175325</v>
       </c>
       <c r="C86">
-        <v>-6.32448714153011</v>
+        <v>-6.48595358683388</v>
       </c>
       <c r="D86">
-        <v>4.166632858469889</v>
+        <v>4.133346413166119</v>
       </c>
       <c r="E86">
-        <v>10.04912</v>
+        <v>10.1773</v>
       </c>
       <c r="F86">
-        <v>10.76712</v>
+        <v>10.8953</v>
       </c>
       <c r="G86">
         <v>0.276</v>
@@ -8446,37 +8446,37 @@
         <v>0.054</v>
       </c>
       <c r="M86">
-        <v>2.538886896</v>
+        <v>2.56911174</v>
       </c>
       <c r="N86">
-        <v>-2.484886896</v>
+        <v>-2.51511174</v>
       </c>
       <c r="O86">
-        <v>-0.621221724</v>
+        <v>-0.628777935</v>
       </c>
       <c r="P86">
-        <v>-1.863665172</v>
+        <v>-1.886333805</v>
       </c>
       <c r="Q86">
-        <v>-1.813665172</v>
+        <v>-1.836333805</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5294614027874528</v>
+        <v>0.5617054963066163</v>
       </c>
       <c r="T86">
-        <v>4.677375418850038</v>
+        <v>4.989200446773373</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.005317290825861193</v>
+        <v>0.005254734463204003</v>
       </c>
       <c r="W86">
-        <v>0.234546182823262</v>
+        <v>0.2345609336135765</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.02126916330344475</v>
+        <v>0.02101893785281594</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8492,22 +8492,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2836326180175325</v>
+        <v>0.2855326180175325</v>
       </c>
       <c r="C87">
-        <v>-6.48595358683388</v>
+        <v>-6.646892408933096</v>
       </c>
       <c r="D87">
-        <v>4.133346413166119</v>
+        <v>4.100587591066904</v>
       </c>
       <c r="E87">
-        <v>10.1773</v>
+        <v>10.30548</v>
       </c>
       <c r="F87">
-        <v>10.8953</v>
+        <v>11.02348</v>
       </c>
       <c r="G87">
         <v>0.276</v>
@@ -8528,37 +8528,37 @@
         <v>0.054</v>
       </c>
       <c r="M87">
-        <v>2.56911174</v>
+        <v>2.599336584</v>
       </c>
       <c r="N87">
-        <v>-2.51511174</v>
+        <v>-2.545336584</v>
       </c>
       <c r="O87">
-        <v>-0.628777935</v>
+        <v>-0.636334146</v>
       </c>
       <c r="P87">
-        <v>-1.886333805</v>
+        <v>-1.909002438</v>
       </c>
       <c r="Q87">
-        <v>-1.836333805</v>
+        <v>-1.859002438</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5617054963066163</v>
+        <v>0.598555888899946</v>
       </c>
       <c r="T87">
-        <v>4.989200446773373</v>
+        <v>5.345571907257186</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.005254734463204003</v>
+        <v>0.005193632899678374</v>
       </c>
       <c r="W87">
-        <v>0.2345609336135765</v>
+        <v>0.2345753413622559</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.02101893785281594</v>
+        <v>0.02077453159871345</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8574,22 +8574,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2855326180175325</v>
+        <v>0.2874326180175324</v>
       </c>
       <c r="C88">
-        <v>-6.646892408933096</v>
+        <v>-6.807316054211408</v>
       </c>
       <c r="D88">
-        <v>4.100587591066904</v>
+        <v>4.068343945788592</v>
       </c>
       <c r="E88">
-        <v>10.30548</v>
+        <v>10.43366</v>
       </c>
       <c r="F88">
-        <v>11.02348</v>
+        <v>11.15166</v>
       </c>
       <c r="G88">
         <v>0.276</v>
@@ -8610,37 +8610,37 @@
         <v>0.054</v>
       </c>
       <c r="M88">
-        <v>2.599336584</v>
+        <v>2.629561428</v>
       </c>
       <c r="N88">
-        <v>-2.545336584</v>
+        <v>-2.575561428</v>
       </c>
       <c r="O88">
-        <v>-0.636334146</v>
+        <v>-0.6438903570000001</v>
       </c>
       <c r="P88">
-        <v>-1.909002438</v>
+        <v>-1.931671071</v>
       </c>
       <c r="Q88">
-        <v>-1.859002438</v>
+        <v>-1.881671071</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.598555888899946</v>
+        <v>0.6410755726614803</v>
       </c>
       <c r="T88">
-        <v>5.345571907257186</v>
+        <v>5.756769746276969</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.005193632899678374</v>
+        <v>0.005133935969797014</v>
       </c>
       <c r="W88">
-        <v>0.2345753413622559</v>
+        <v>0.2345894178983219</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.02077453159871345</v>
+        <v>0.020535743879188</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8656,22 +8656,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2874326180175324</v>
+        <v>0.2893326180175325</v>
       </c>
       <c r="C89">
-        <v>-6.807316054211408</v>
+        <v>-6.967236580634204</v>
       </c>
       <c r="D89">
-        <v>4.068343945788592</v>
+        <v>4.036603419365796</v>
       </c>
       <c r="E89">
-        <v>10.43366</v>
+        <v>10.56184</v>
       </c>
       <c r="F89">
-        <v>11.15166</v>
+        <v>11.27984</v>
       </c>
       <c r="G89">
         <v>0.276</v>
@@ -8692,37 +8692,37 @@
         <v>0.054</v>
       </c>
       <c r="M89">
-        <v>2.629561428</v>
+        <v>2.659786272</v>
       </c>
       <c r="N89">
-        <v>-2.575561428</v>
+        <v>-2.605786272</v>
       </c>
       <c r="O89">
-        <v>-0.6438903570000001</v>
+        <v>-0.6514465680000001</v>
       </c>
       <c r="P89">
-        <v>-1.931671071</v>
+        <v>-1.954339704</v>
       </c>
       <c r="Q89">
-        <v>-1.881671071</v>
+        <v>-1.904339704</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6410755726614803</v>
+        <v>0.6906818703832704</v>
       </c>
       <c r="T89">
-        <v>5.756769746276969</v>
+        <v>6.236500558466718</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.005133935969797014</v>
+        <v>0.005075595788322047</v>
       </c>
       <c r="W89">
-        <v>0.2345894178983219</v>
+        <v>0.2346031745131137</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.020535743879188</v>
+        <v>0.02030238315328814</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8738,22 +8738,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2893326180175325</v>
+        <v>0.2912326180175325</v>
       </c>
       <c r="C90">
-        <v>-6.967236580634204</v>
+        <v>-7.126665672783185</v>
       </c>
       <c r="D90">
-        <v>4.036603419365796</v>
+        <v>4.005354327216816</v>
       </c>
       <c r="E90">
-        <v>10.56184</v>
+        <v>10.69002</v>
       </c>
       <c r="F90">
-        <v>11.27984</v>
+        <v>11.40802</v>
       </c>
       <c r="G90">
         <v>0.276</v>
@@ -8774,37 +8774,37 @@
         <v>0.054</v>
       </c>
       <c r="M90">
-        <v>2.659786272</v>
+        <v>2.690011116</v>
       </c>
       <c r="N90">
-        <v>-2.605786272</v>
+        <v>-2.636011116000001</v>
       </c>
       <c r="O90">
-        <v>-0.6514465680000001</v>
+        <v>-0.6590027790000001</v>
       </c>
       <c r="P90">
-        <v>-1.954339704</v>
+        <v>-1.977008337</v>
       </c>
       <c r="Q90">
-        <v>-1.904339704</v>
+        <v>-1.927008337</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6906818703832704</v>
+        <v>0.7493074949635677</v>
       </c>
       <c r="T90">
-        <v>6.236500558466718</v>
+        <v>6.803455154690965</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.005075595788322047</v>
+        <v>0.005018566622161125</v>
       </c>
       <c r="W90">
-        <v>0.2346031745131137</v>
+        <v>0.2346166219904944</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.02030238315328814</v>
+        <v>0.02007426648864441</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8820,22 +8820,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2912326180175325</v>
+        <v>0.2931326180175325</v>
       </c>
       <c r="C91">
-        <v>-7.126665672783185</v>
+        <v>-7.285614656197948</v>
       </c>
       <c r="D91">
-        <v>4.005354327216816</v>
+        <v>3.974585343802051</v>
       </c>
       <c r="E91">
-        <v>10.69002</v>
+        <v>10.8182</v>
       </c>
       <c r="F91">
-        <v>11.40802</v>
+        <v>11.5362</v>
       </c>
       <c r="G91">
         <v>0.276</v>
@@ -8856,37 +8856,37 @@
         <v>0.054</v>
       </c>
       <c r="M91">
-        <v>2.690011116</v>
+        <v>2.72023596</v>
       </c>
       <c r="N91">
-        <v>-2.636011116000001</v>
+        <v>-2.66623596</v>
       </c>
       <c r="O91">
-        <v>-0.6590027790000001</v>
+        <v>-0.6665589900000001</v>
       </c>
       <c r="P91">
-        <v>-1.977008337</v>
+        <v>-1.99967697</v>
       </c>
       <c r="Q91">
-        <v>-1.927008337</v>
+        <v>-1.94967697</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7493074949635677</v>
+        <v>0.8196582444599246</v>
       </c>
       <c r="T91">
-        <v>6.803455154690965</v>
+        <v>7.483800670160062</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.005018566622161125</v>
+        <v>0.00496280477080378</v>
       </c>
       <c r="W91">
-        <v>0.2346166219904944</v>
+        <v>0.2346297706350445</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.02007426648864441</v>
+        <v>0.01985121908321508</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8902,22 +8902,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2931326180175325</v>
+        <v>0.2950326180175324</v>
       </c>
       <c r="C92">
-        <v>-7.285614656197948</v>
+        <v>-7.444094511061619</v>
       </c>
       <c r="D92">
-        <v>3.974585343802051</v>
+        <v>3.94428548893838</v>
       </c>
       <c r="E92">
-        <v>10.8182</v>
+        <v>10.94638</v>
       </c>
       <c r="F92">
-        <v>11.5362</v>
+        <v>11.66438</v>
       </c>
       <c r="G92">
         <v>0.276</v>
@@ -8938,37 +8938,37 @@
         <v>0.054</v>
       </c>
       <c r="M92">
-        <v>2.72023596</v>
+        <v>2.750460804</v>
       </c>
       <c r="N92">
-        <v>-2.66623596</v>
+        <v>-2.696460804</v>
       </c>
       <c r="O92">
-        <v>-0.6665589900000001</v>
+        <v>-0.674115201</v>
       </c>
       <c r="P92">
-        <v>-1.99967697</v>
+        <v>-2.022345603</v>
       </c>
       <c r="Q92">
-        <v>-1.94967697</v>
+        <v>-1.972345603</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8196582444599246</v>
+        <v>0.9056424938443608</v>
       </c>
       <c r="T92">
-        <v>7.483800670160062</v>
+        <v>8.315334077955626</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.00496280477080378</v>
+        <v>0.004908268454641101</v>
       </c>
       <c r="W92">
-        <v>0.2346297706350445</v>
+        <v>0.2346426302983956</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.01985121908321508</v>
+        <v>0.01963307381856438</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8984,22 +8984,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2950326180175324</v>
+        <v>0.2969326180175325</v>
       </c>
       <c r="C93">
-        <v>-7.444094511061619</v>
+        <v>-7.602115885265188</v>
       </c>
       <c r="D93">
-        <v>3.94428548893838</v>
+        <v>3.914444114734812</v>
       </c>
       <c r="E93">
-        <v>10.94638</v>
+        <v>11.07456</v>
       </c>
       <c r="F93">
-        <v>11.66438</v>
+        <v>11.79256</v>
       </c>
       <c r="G93">
         <v>0.276</v>
@@ -9020,37 +9020,37 @@
         <v>0.054</v>
       </c>
       <c r="M93">
-        <v>2.750460804</v>
+        <v>2.780685648</v>
       </c>
       <c r="N93">
-        <v>-2.696460804</v>
+        <v>-2.726685648</v>
       </c>
       <c r="O93">
-        <v>-0.674115201</v>
+        <v>-0.681671412</v>
       </c>
       <c r="P93">
-        <v>-2.022345603</v>
+        <v>-2.045014236</v>
       </c>
       <c r="Q93">
-        <v>-1.972345603</v>
+        <v>-1.995014236</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9056424938443608</v>
+        <v>1.013122805574906</v>
       </c>
       <c r="T93">
-        <v>8.315334077955626</v>
+        <v>9.354750837700083</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.004908268454641101</v>
+        <v>0.004854917710568915</v>
       </c>
       <c r="W93">
-        <v>0.2346426302983956</v>
+        <v>0.2346552104038479</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.01963307381856438</v>
+        <v>0.01941967084227558</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9066,22 +9066,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2969326180175325</v>
+        <v>0.2988326180175325</v>
       </c>
       <c r="C94">
-        <v>-7.602115885265188</v>
+        <v>-7.759689106883284</v>
       </c>
       <c r="D94">
-        <v>3.914444114734812</v>
+        <v>3.885050893116716</v>
       </c>
       <c r="E94">
-        <v>11.07456</v>
+        <v>11.20274</v>
       </c>
       <c r="F94">
-        <v>11.79256</v>
+        <v>11.92074</v>
       </c>
       <c r="G94">
         <v>0.276</v>
@@ -9102,37 +9102,37 @@
         <v>0.054</v>
       </c>
       <c r="M94">
-        <v>2.780685648</v>
+        <v>2.810910492</v>
       </c>
       <c r="N94">
-        <v>-2.726685648</v>
+        <v>-2.756910492</v>
       </c>
       <c r="O94">
-        <v>-0.681671412</v>
+        <v>-0.6892276230000001</v>
       </c>
       <c r="P94">
-        <v>-2.045014236</v>
+        <v>-2.067682869</v>
       </c>
       <c r="Q94">
-        <v>-1.995014236</v>
+        <v>-2.017682869000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.013122805574906</v>
+        <v>1.151311777799893</v>
       </c>
       <c r="T94">
-        <v>9.354750837700083</v>
+        <v>10.69114381451438</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.004854917710568915</v>
+        <v>0.004802714294326238</v>
       </c>
       <c r="W94">
-        <v>0.2346552104038479</v>
+        <v>0.2346675199693979</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.01941967084227558</v>
+        <v>0.01921085717730486</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9148,22 +9148,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2988326180175325</v>
+        <v>0.3007326180175325</v>
       </c>
       <c r="C95">
-        <v>-7.759689106883284</v>
+        <v>-7.916824196092049</v>
       </c>
       <c r="D95">
-        <v>3.885050893116716</v>
+        <v>3.856095803907952</v>
       </c>
       <c r="E95">
-        <v>11.20274</v>
+        <v>11.33092</v>
       </c>
       <c r="F95">
-        <v>11.92074</v>
+        <v>12.04892</v>
       </c>
       <c r="G95">
         <v>0.276</v>
@@ -9184,37 +9184,37 @@
         <v>0.054</v>
       </c>
       <c r="M95">
-        <v>2.810910492</v>
+        <v>2.841135336</v>
       </c>
       <c r="N95">
-        <v>-2.756910492</v>
+        <v>-2.787135336</v>
       </c>
       <c r="O95">
-        <v>-0.6892276230000001</v>
+        <v>-0.6967838340000001</v>
       </c>
       <c r="P95">
-        <v>-2.067682869</v>
+        <v>-2.090351502</v>
       </c>
       <c r="Q95">
-        <v>-2.017682869000001</v>
+        <v>-2.040351502</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.151311777799893</v>
+        <v>1.335563740766542</v>
       </c>
       <c r="T95">
-        <v>10.69114381451438</v>
+        <v>12.47300111693345</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.004802714294326238</v>
+        <v>0.004751621589067449</v>
       </c>
       <c r="W95">
-        <v>0.2346675199693979</v>
+        <v>0.2346795676292979</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.01921085717730486</v>
+        <v>0.01900648635626978</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9230,22 +9230,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3007326180175325</v>
+        <v>0.3026326180175325</v>
       </c>
       <c r="C96">
-        <v>-7.916824196092049</v>
+        <v>-8.073530876558021</v>
       </c>
       <c r="D96">
-        <v>3.856095803907952</v>
+        <v>3.827569123441979</v>
       </c>
       <c r="E96">
-        <v>11.33092</v>
+        <v>11.4591</v>
       </c>
       <c r="F96">
-        <v>12.04892</v>
+        <v>12.1771</v>
       </c>
       <c r="G96">
         <v>0.276</v>
@@ -9266,37 +9266,37 @@
         <v>0.054</v>
       </c>
       <c r="M96">
-        <v>2.841135336</v>
+        <v>2.87136018</v>
       </c>
       <c r="N96">
-        <v>-2.787135336</v>
+        <v>-2.817360180000001</v>
       </c>
       <c r="O96">
-        <v>-0.6967838340000001</v>
+        <v>-0.7043400450000001</v>
       </c>
       <c r="P96">
-        <v>-2.090351502</v>
+        <v>-2.113020135</v>
       </c>
       <c r="Q96">
-        <v>-2.040351502</v>
+        <v>-2.063020135</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.335563740766542</v>
+        <v>1.593516488919852</v>
       </c>
       <c r="T96">
-        <v>12.47300111693345</v>
+        <v>14.96760134032015</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.004751621589067449</v>
+        <v>0.004701604519708844</v>
       </c>
       <c r="W96">
-        <v>0.2346795676292979</v>
+        <v>0.2346913616542527</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.01900648635626978</v>
+        <v>0.01880641807883532</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9312,22 +9312,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3026326180175325</v>
+        <v>0.3045326180175325</v>
       </c>
       <c r="C97">
-        <v>-8.073530876558021</v>
+        <v>-8.229818586325202</v>
       </c>
       <c r="D97">
-        <v>3.827569123441979</v>
+        <v>3.799461413674798</v>
       </c>
       <c r="E97">
-        <v>11.4591</v>
+        <v>11.58728</v>
       </c>
       <c r="F97">
-        <v>12.1771</v>
+        <v>12.30528</v>
       </c>
       <c r="G97">
         <v>0.276</v>
@@ -9348,37 +9348,37 @@
         <v>0.054</v>
       </c>
       <c r="M97">
-        <v>2.87136018</v>
+        <v>2.901585024</v>
       </c>
       <c r="N97">
-        <v>-2.817360180000001</v>
+        <v>-2.847585024</v>
       </c>
       <c r="O97">
-        <v>-0.7043400450000001</v>
+        <v>-0.7118962560000001</v>
       </c>
       <c r="P97">
-        <v>-2.113020135</v>
+        <v>-2.135688768</v>
       </c>
       <c r="Q97">
-        <v>-2.063020135</v>
+        <v>-2.085688768</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.593516488919852</v>
+        <v>1.980445611149815</v>
       </c>
       <c r="T97">
-        <v>14.96760134032015</v>
+        <v>18.70950167540019</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.004701604519708844</v>
+        <v>0.004652629472628543</v>
       </c>
       <c r="W97">
-        <v>0.2346913616542527</v>
+        <v>0.2347029099703542</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.01880641807883532</v>
+        <v>0.01861051789051416</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9394,22 +9394,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3045326180175325</v>
+        <v>0.3064326180175325</v>
       </c>
       <c r="C98">
-        <v>-8.229818586325202</v>
+        <v>-8.385696488225939</v>
       </c>
       <c r="D98">
-        <v>3.799461413674798</v>
+        <v>3.77176351177406</v>
       </c>
       <c r="E98">
-        <v>11.58728</v>
+        <v>11.71546</v>
       </c>
       <c r="F98">
-        <v>12.30528</v>
+        <v>12.43346</v>
       </c>
       <c r="G98">
         <v>0.276</v>
@@ -9430,37 +9430,37 @@
         <v>0.054</v>
       </c>
       <c r="M98">
-        <v>2.901585024</v>
+        <v>2.931809868</v>
       </c>
       <c r="N98">
-        <v>-2.847585024</v>
+        <v>-2.877809868</v>
       </c>
       <c r="O98">
-        <v>-0.7118962560000001</v>
+        <v>-0.719452467</v>
       </c>
       <c r="P98">
-        <v>-2.135688768</v>
+        <v>-2.158357401</v>
       </c>
       <c r="Q98">
-        <v>-2.085688768</v>
+        <v>-2.108357401</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.98044561114981</v>
+        <v>2.62532748153308</v>
       </c>
       <c r="T98">
-        <v>18.70950167540014</v>
+        <v>24.94600223386685</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.004652629472628543</v>
+        <v>0.004604664220333404</v>
       </c>
       <c r="W98">
-        <v>0.2347029099703542</v>
+        <v>0.2347142201768454</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.01861051789051416</v>
+        <v>0.01841865688133359</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9476,22 +9476,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3064326180175325</v>
+        <v>0.3083326180175325</v>
       </c>
       <c r="C99">
-        <v>-8.385696488225939</v>
+        <v>-8.541173479839728</v>
       </c>
       <c r="D99">
-        <v>3.77176351177406</v>
+        <v>3.744466520160271</v>
       </c>
       <c r="E99">
-        <v>11.71546</v>
+        <v>11.84364</v>
       </c>
       <c r="F99">
-        <v>12.43346</v>
+        <v>12.56164</v>
       </c>
       <c r="G99">
         <v>0.276</v>
@@ -9512,37 +9512,37 @@
         <v>0.054</v>
       </c>
       <c r="M99">
-        <v>2.931809868</v>
+        <v>2.962034712</v>
       </c>
       <c r="N99">
-        <v>-2.877809868</v>
+        <v>-2.908034712</v>
       </c>
       <c r="O99">
-        <v>-0.719452467</v>
+        <v>-0.727008678</v>
       </c>
       <c r="P99">
-        <v>-2.158357401</v>
+        <v>-2.181026034</v>
       </c>
       <c r="Q99">
-        <v>-2.108357401</v>
+        <v>-2.131026034</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.62532748153308</v>
+        <v>3.915091222299619</v>
       </c>
       <c r="T99">
-        <v>24.94600223386685</v>
+        <v>37.41900335080027</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.004604664220333404</v>
+        <v>0.004557677850738165</v>
       </c>
       <c r="W99">
-        <v>0.2347142201768454</v>
+        <v>0.2347252995627959</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.01841865688133359</v>
+        <v>0.01823071140295263</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9558,22 +9558,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3083326180175325</v>
+        <v>0.3102326180175325</v>
       </c>
       <c r="C100">
-        <v>-8.541173479839728</v>
+        <v>-8.696258203022678</v>
       </c>
       <c r="D100">
-        <v>3.744466520160271</v>
+        <v>3.717561796977321</v>
       </c>
       <c r="E100">
-        <v>11.84364</v>
+        <v>11.97182</v>
       </c>
       <c r="F100">
-        <v>12.56164</v>
+        <v>12.68982</v>
       </c>
       <c r="G100">
         <v>0.276</v>
@@ -9594,37 +9594,37 @@
         <v>0.054</v>
       </c>
       <c r="M100">
-        <v>2.962034712</v>
+        <v>2.992259556</v>
       </c>
       <c r="N100">
-        <v>-2.908034712</v>
+        <v>-2.938259556</v>
       </c>
       <c r="O100">
-        <v>-0.727008678</v>
+        <v>-0.7345648890000001</v>
       </c>
       <c r="P100">
-        <v>-2.181026034</v>
+        <v>-2.203694667</v>
       </c>
       <c r="Q100">
-        <v>-2.131026034</v>
+        <v>-2.153694667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.915091222299619</v>
+        <v>7.784382444599239</v>
       </c>
       <c r="T100">
-        <v>37.41900335080027</v>
+        <v>74.83800670160055</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.004557677850738165</v>
+        <v>0.004511640700730709</v>
       </c>
       <c r="W100">
-        <v>0.2347252995627959</v>
+        <v>0.2347361551227677</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9632,91 +9632,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.01823071140295263</v>
+        <v>0.01804656280292283</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3102326180175325</v>
-      </c>
-      <c r="C101">
-        <v>-8.696258203022678</v>
-      </c>
-      <c r="D101">
-        <v>3.717561796977321</v>
-      </c>
-      <c r="E101">
-        <v>11.97182</v>
-      </c>
-      <c r="F101">
-        <v>12.68982</v>
-      </c>
-      <c r="G101">
-        <v>0.276</v>
-      </c>
-      <c r="H101">
-        <v>12.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.104</v>
-      </c>
-      <c r="K101">
-        <v>0.05</v>
-      </c>
-      <c r="L101">
-        <v>0.054</v>
-      </c>
-      <c r="M101">
-        <v>2.992259556</v>
-      </c>
-      <c r="N101">
-        <v>-2.938259556</v>
-      </c>
-      <c r="O101">
-        <v>-0.7345648890000001</v>
-      </c>
-      <c r="P101">
-        <v>-2.203694667</v>
-      </c>
-      <c r="Q101">
-        <v>-2.153694667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.784382444599239</v>
-      </c>
-      <c r="T101">
-        <v>74.83800670160055</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.004511640700730709</v>
-      </c>
-      <c r="W101">
-        <v>0.2347361551227677</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.01804656280292283</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
